--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670EB7E1-1E5A-4FC0-A0C3-08786977EC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329BE5FB-58B2-4FA1-B3C0-834C373EB05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.900000000000006</v>
+        <v>80.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19316.714592</v>
+        <v>19634.987455999999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18286439476770147</v>
+        <v>0.17735100790092828</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.78</v>
+        <v>7.8105001449584961</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>107.72963362225431</v>
+        <v>108.15196902608523</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,13 +5561,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.318713567603893</v>
+        <v>61.513338177664224</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5576,13 +5576,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.649206757307198</v>
+        <v>75.893155005007358</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.607777436665899</v>
+        <v>92.91049072669982</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>103.99185122875511</v>
+        <v>104.3341974879629</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11426548736455498</v>
+        <v>0.11285400057661392</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.0856780735107728E-2</v>
+        <v>7.9546134663341636E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-33.923398760128038</v>
+        <v>-34.05638958013688</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.612025216520266</v>
+        <v>21.696751424997203</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.67873205740845</v>
+        <v>22.767640105637994</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.367358513800676</v>
+        <v>10.408001950498313</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.13591175715187</v>
+        <v>-19.210930790893016</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.17 HKD</v>
+        <v>116.62 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.144806821685827E-2</v>
+        <v>3.1228517914408276E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>111.86 HKD</v>
+        <v>112.29 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5280470973363067E-2</v>
+        <v>4.5055141365783064E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>107.69 HKD</v>
+        <v>108.12 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9339967078495599E-2</v>
+        <v>5.9108665329586307E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.68 HKD</v>
+        <v>104.09 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3628108975324416E-2</v>
+        <v>7.3390636051479871E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>85.71 HKD</v>
+        <v>86.04 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14853470727805468</v>
+        <v>0.1482631713897552</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>107.72963362225431</v>
+        <v>108.15196902608523</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6585,19 +6585,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>11.673721114952121</v>
+        <v>11.673721114952119</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.644992452651771</v>
+        <v>49.839617062712101</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.318713567603893</v>
+        <v>61.513338177664224</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6606,19 +6606,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>13.422703581997817</v>
+        <v>13.42270358199781</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.226503175309375</v>
+        <v>62.470451423009543</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.649206757307198</v>
+        <v>75.893155005007358</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.216334534427688</v>
+        <v>77.519047824461609</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.607777436665899</v>
+        <v>92.91049072669982</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.325942229482138</v>
+        <v>87.668288488689925</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>103.99185122875511</v>
+        <v>104.3341974879629</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.12886920827785</v>
+        <v>115.58021203601052</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.13591175715187</v>
+        <v>-19.210930790893016</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8305305.6000000006</v>
+        <v>-8337865.1147460938</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-33.923398760128045</v>
+        <v>-34.05638958013688</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5291170.1250016345</v>
+        <v>5311913.2427153382</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.612025216520266</v>
+        <v>21.696751424997203</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5552326.926</v>
+        <v>5574093.8638020512</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.67873205740845</v>
+        <v>22.767640105637994</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2538191.4510016339</v>
+        <v>2548141.9917712957</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.367358513800671</v>
+        <v>10.408001950498317</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.0856780735107728E-2</v>
+        <v>7.9546134663341636E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.0856780735107728E-2</v>
+        <v>7.9546134663341636E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.0856780735107728E-2</v>
+        <v>7.9546134663341636E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.3814955640050703E-2</v>
+        <v>8.2456359102244386E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0155469530633887</v>
+        <v>9.0508908462444371</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.136031858223761</v>
+        <v>10.175768418761004</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.6667584815320451</v>
+        <v>7.6968146826950923</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.749802259520758</v>
+        <v>10.79194500080489</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11426548736455498</v>
+        <v>0.11285400057661392</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.12846681696101092</v>
+        <v>0.12687990547083547</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.7170576445273063E-2</v>
+        <v>9.5970257888966237E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13624590949962936</v>
+        <v>0.13456290524694375</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.605371340571702E-2</v>
+        <v>1.5793491118591931E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.850702914811695E-2</v>
+        <v>1.8207039897586375E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0634386885080093E-3</v>
+        <v>4.9813629990434153E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.367358513800676</v>
+        <v>10.408001950498313</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.78</v>
+        <v>7.8105001449584961</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>25922938.813100588</v>
+        <v>26024565.213042717</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>107.72976150997809</v>
+        <v>108.1520974151707</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>96.576888024652206</v>
+        <v>96.955501017504702</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.11423168311806</v>
+        <v>101.51063254734713</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.02170041481122</v>
+        <v>102.42165885331559</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>102.92916914650439</v>
+        <v>103.33268515928408</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>103.83663787819761</v>
+        <v>104.2437114652526</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>92.768221072172565</v>
+        <v>93.131902844697379</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.2278267687344</v>
+        <v>101.62467296285777</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>102.96922052636866</v>
+        <v>103.37289355365884</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>104.72710515677689</v>
+        <v>105.13766966684956</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.50148065995904</v>
+        <v>106.91900130242989</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.394576685360775</v>
+        <v>89.745032668317947</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.33374293247925</v>
+        <v>101.73100435261134</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>103.86152384820828</v>
+        <v>104.2686949964063</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.43703031339962</v>
+        <v>106.85429828942925</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.06072361120779</v>
+        <v>109.48827732321554</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.406266972100852</v>
+        <v>86.745007803459671</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.43249926231127</v>
+        <v>101.83014783956101</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>104.70182814196865</v>
+        <v>105.11229355787476</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.06325283997786</v>
+        <v>108.48689614027425</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>111.51855134061219</v>
+        <v>111.95574054131272</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>85.706969367689155</v>
+        <v>86.042968723687608</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>103.68268504207478</v>
+        <v>104.08915508365182</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>107.69464685603256</v>
+        <v>108.11684510029517</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>111.8551628073442</v>
+        <v>112.29367163510514</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.16851653083671</v>
+        <v>116.62393511615855</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.362318324743697</v>
+        <v>83.689125881682131</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>103.76854098055112</v>
+        <v>104.17534760549179</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.43986724502412</v>
+        <v>108.8649869969847</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.32607149977865</v>
+        <v>113.77034677077094</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.43541091904378</v>
+        <v>118.89971647190366</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.010697838561612</v>
+        <v>83.336126928173698</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>105.86081251828911</v>
+        <v>106.27582153207214</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.21485151252301</v>
+        <v>111.65085011055253</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>116.86036097330856</v>
+        <v>117.31849181515793</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>122.81128144065913</v>
+        <v>123.29274183737877</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.171066394473996</v>
+        <v>81.489283527053317</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>105.93545322419817</v>
+        <v>106.35075485396449</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>111.87574713365986</v>
+        <v>112.31433665871342</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.19078921797906</v>
+        <v>118.65413577375122</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>124.90207491076539</v>
+        <v>125.39173190181876</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.069728762798249</v>
+        <v>81.387548618712287</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>107.88124351469661</v>
+        <v>108.30417327889982</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.45050530042239</v>
+        <v>114.89918871973293</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>121.48694565635228</v>
+        <v>121.96321422358668</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.02169068212604</v>
+        <v>129.52749791459325</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.626339623822403</v>
+        <v>79.93850092215672</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>107.94613401705995</v>
+        <v>108.36931817325912</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.0366178497971</v>
+        <v>115.48759902202767</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>122.69031016383072</v>
+        <v>123.17129631357361</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>130.95006341857996</v>
+        <v>131.46343050297469</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.151248225927105</v>
+        <v>78.457626683456439</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.11175228092</v>
+        <v>113.55518735046724</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>122.69356763498985</v>
+        <v>123.17456655508525</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>133.39445209889664</v>
+        <v>133.91740198651559</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>145.35056136529548</v>
+        <v>145.92038311226725</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.149868400681228</v>
+        <v>77.452321121728744</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.03822701761155</v>
+        <v>116.49313482542183</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>127.49447046632731</v>
+        <v>127.99429049597123</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>140.67327486903795</v>
+        <v>141.22476012293151</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>155.86064150663395</v>
+        <v>156.47166620576974</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.607515865099359</v>
+        <v>77.911762713910974</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>119.62351846302806</v>
+        <v>120.09248178610873</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>132.69386941005573</v>
+        <v>133.21407278436297</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.10574999119584</v>
+        <v>148.68637297884598</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>166.34603185368204</v>
+        <v>166.99816271291184</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>77.74963480276665</v>
+        <v>78.054438804303217</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>121.64709175943567</v>
+        <v>122.12398815178042</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>135.90026120312467</v>
+        <v>136.43303468212116</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.07197279319269</v>
+        <v>153.67206499875508</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>173.88726423849693</v>
+        <v>174.56895919552912</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.16851653083671</v>
+        <v>116.62393511615855</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>111.8551628073442</v>
+        <v>112.29367163510514</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>107.69464685603256</v>
+        <v>108.11684510029517</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>103.68268504207478</v>
+        <v>104.08915508365182</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>85.706969367689155</v>
+        <v>86.042968723687608</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>111.8551628073442</v>
+        <v>112.29367163510514</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>107.69464685603256</v>
+        <v>108.11684510029517</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>103.68268504207478</v>
+        <v>104.08915508365182</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>107.52375959280545</v>
+        <v>107.94528790309631</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.16851653083671</v>
+        <v>116.62393511615855</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>85.706969367689155</v>
+        <v>86.042968723687608</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.900000000000006</v>
+        <v>80.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18286439476770147</v>
+        <v>0.17735100790092828</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5697599346763585E-2</v>
+        <v>6.546356441003956E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>107.72963362225431</v>
+        <v>108.15196902608523</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>107.72976150997809</v>
+        <v>108.1520974151707</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.623497421473666E-2</v>
+        <v>9.6234974214736729E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20067,23 +20067,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>11.673721114952121</v>
+        <v>11.673721114952119</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.644992452651771</v>
+        <v>49.839617062712101</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.318713567603893</v>
+        <v>61.513338177664224</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43080922578263603</v>
+        <v>0.43123237855403451</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20092,23 +20092,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>13.422703581997817</v>
+        <v>13.42270358199781</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.226503175309375</v>
+        <v>62.470451423009543</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.649206757307198</v>
+        <v>75.893155005007358</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.2977864658617021</v>
+        <v>0.29827301630816683</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.216334534427688</v>
+        <v>77.519047824461609</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.607777436665899</v>
+        <v>92.91049072669982</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.1403685845494661</v>
+        <v>0.14092649848759853</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.325942229482138</v>
+        <v>87.668288488689925</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>103.99185122875511</v>
+        <v>104.3341974879629</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.469595382274715E-2</v>
+        <v>3.5300065015011595E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.900000000000006</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19316.714592</v>
+        <v>19634.987455999999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18286439476770147</v>
+        <v>0.17735100790092828</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.78</v>
+        <v>7.8105001449584961</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>107.72963362225431</v>
+        <v>108.15196902608523</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,14 +20445,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.318713567603893</v>
+        <v>61.513338177664224</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20461,14 +20461,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.649206757307198</v>
+        <v>75.893155005007358</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.607777436665899</v>
+        <v>92.91049072669982</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>103.99185122875511</v>
+        <v>104.3341974879629</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11426548736455498</v>
+        <v>0.11285400057661392</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.0856780735107728E-2</v>
+        <v>7.9546134663341636E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-33.923398760128038</v>
+        <v>-34.05638958013688</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.612025216520266</v>
+        <v>21.696751424997203</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.67873205740845</v>
+        <v>22.767640105637994</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.367358513800676</v>
+        <v>10.408001950498313</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.13591175715187</v>
+        <v>-19.210930790893016</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>105.88342353003982</v>
+        <v>106.29852118638532</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.17 HKD</v>
+        <v>116.62 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>111.86 HKD</v>
+        <v>112.29 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>107.69 HKD</v>
+        <v>108.12 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>103.68 HKD</v>
+        <v>104.09 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>85.71 HKD</v>
+        <v>86.04 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>107.72963362225431</v>
+        <v>108.15196902608523</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21480,19 +21480,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>11.673721114952121</v>
+        <v>11.673721114952119</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.644992452651771</v>
+        <v>49.839617062712101</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.318713567603893</v>
+        <v>61.513338177664224</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21501,19 +21501,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>13.422703581997817</v>
+        <v>13.42270358199781</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.226503175309375</v>
+        <v>62.470451423009543</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.649206757307198</v>
+        <v>75.893155005007358</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.216334534427688</v>
+        <v>77.519047824461609</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.607777436665899</v>
+        <v>92.91049072669982</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.325942229482138</v>
+        <v>87.668288488689925</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>103.99185122875511</v>
+        <v>104.3341974879629</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,15 +21684,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21707,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329BE5FB-58B2-4FA1-B3C0-834C373EB05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1306374-6FEE-4530-94C9-744B4602B446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>80.2</v>
+        <v>79.25</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19634.987455999999</v>
+        <v>19402.403439999998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17735100790092828</v>
+        <v>0.1824311310893896</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8105001449584961</v>
+        <v>7.8120999336242676</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.15196902608523</v>
+        <v>108.17412129431614</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.513338177664224</v>
+        <v>61.523546596203801</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.893155005007358</v>
+        <v>75.905950539003555</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.91049072669982</v>
+        <v>92.926368595183177</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.3341974879629</v>
+        <v>104.35215417852928</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11285400057661392</v>
+        <v>0.11423021701460993</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>7.9546134663341636E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.05638958013688</v>
+        <v>-34.063365193098434</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.696751424997203</v>
+        <v>21.701195470368116</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.767640105637994</v>
+        <v>22.772303496190631</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.408001950498313</v>
+        <v>10.410133773460315</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.210930790893016</v>
+        <v>-19.214865677106165</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.62 HKD</v>
+        <v>116.65 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1228517914408276E-2</v>
+        <v>3.1217049374226164E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.29 HKD</v>
+        <v>112.32 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5055141365783064E-2</v>
+        <v>4.5043370956158992E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.12 HKD</v>
+        <v>108.14 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9108665329586307E-2</v>
+        <v>5.9096582979132707E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.09 HKD</v>
+        <v>104.11 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3390636051479871E-2</v>
+        <v>7.3378231365190422E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.04 HKD</v>
+        <v>86.06 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1482631713897552</v>
+        <v>0.14824898752874835</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.15196902608523</v>
+        <v>108.17412129431614</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.839617062712101</v>
+        <v>49.849825481251685</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.513338177664224</v>
+        <v>61.523546596203801</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.470451423009543</v>
+        <v>62.48324695700574</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.893155005007358</v>
+        <v>75.905950539003555</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.519047824461609</v>
+        <v>77.534925692944967</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.91049072669982</v>
+        <v>92.926368595183177</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.668288488689925</v>
+        <v>87.686245179256304</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.3341974879629</v>
+        <v>104.35215417852928</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.58021203601052</v>
+        <v>115.603885796944</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.210930790893016</v>
+        <v>-19.214865677106165</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8337865.1147460938</v>
+        <v>-8339572.9211425781</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.05638958013688</v>
+        <v>-34.063365193098434</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5311913.2427153382</v>
+        <v>5313001.2573676063</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.696751424997203</v>
+        <v>21.701195470368116</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5574093.8638020512</v>
+        <v>5575235.5796998497</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.767640105637994</v>
+        <v>22.772303496190631</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2548141.9917712957</v>
+        <v>2548663.9159248779</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.408001950498317</v>
+        <v>10.410133773460313</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>7.9546134663341636E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.9546134663341636E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.9546134663341636E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.2456359102244386E-2</v>
+        <v>8.3444794952681395E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0508908462444371</v>
+        <v>9.0527446984078352</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.175768418761004</v>
+        <v>10.177852674401453</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.6968146826950923</v>
+        <v>7.698391185692774</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.79194500080489</v>
+        <v>10.794155465048343</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11285400057661392</v>
+        <v>0.11423021701460993</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.12687990547083547</v>
+        <v>0.12842716308393001</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.5970257888966237E-2</v>
+        <v>9.7140582784766866E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13456290524694375</v>
+        <v>0.13620385444855954</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5793491118591931E-2</v>
+        <v>1.5982813725060857E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8207039897586375E-2</v>
+        <v>1.8425294634529053E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9813629990434153E-3</v>
+        <v>5.0410764987164911E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.408001950498313</v>
+        <v>10.410133773460315</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8105001449584961</v>
+        <v>7.8120999336242676</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26024565.213042717</v>
+        <v>26029895.704520442</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.1520974151707</v>
+        <v>108.17424970969897</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>96.955501017504702</v>
+        <v>96.975359964913096</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.51063254734713</v>
+        <v>101.53142450130532</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.42165885331559</v>
+        <v>102.44263740858376</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.33268515928408</v>
+        <v>103.35385031586222</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.2437114652526</v>
+        <v>104.2650632231407</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.131902844697379</v>
+        <v>93.150978622154327</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.62467296285777</v>
+        <v>101.6454882751875</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.37289355365884</v>
+        <v>103.39406694593666</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.13766966684956</v>
+        <v>105.15920453006663</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.91900130242989</v>
+        <v>106.9409010275774</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.745032668317947</v>
+        <v>89.763414728801592</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.73100435261134</v>
+        <v>101.75184144430845</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.2686949964063</v>
+        <v>104.29005187155568</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.85429828942925</v>
+        <v>106.8761847617575</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.48827732321554</v>
+        <v>109.51070330130219</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.745007803459671</v>
+        <v>86.762775382708199</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.83014783956101</v>
+        <v>101.85100523836059</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.11229355787476</v>
+        <v>105.13382322342066</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.48689614027425</v>
+        <v>108.50911701007885</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>111.95574054131272</v>
+        <v>111.97867191849241</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.042968723687608</v>
+        <v>86.060592507514343</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.08915508365182</v>
+        <v>104.11047518447022</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.11684510029517</v>
+        <v>108.13899017425462</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.29367163510514</v>
+        <v>112.31667222914977</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.62393511615855</v>
+        <v>116.64782265806929</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.689125881682131</v>
+        <v>83.706267538752613</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.17534760549179</v>
+        <v>104.19668536072628</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.8649869969847</v>
+        <v>108.88728530939296</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.77034677077094</v>
+        <v>113.79364982536244</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.89971647190366</v>
+        <v>118.92407015159701</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.336126928173698</v>
+        <v>83.353196282099134</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.27582153207214</v>
+        <v>106.29758951767832</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.65085011055253</v>
+        <v>111.67371903843365</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.31849181515793</v>
+        <v>117.34252161990895</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.29274183737877</v>
+        <v>123.3179953201651</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.489283527053317</v>
+        <v>81.505974600575996</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.35075485396449</v>
+        <v>106.37253818781686</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.31433665871342</v>
+        <v>112.33734148547937</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.65413577375122</v>
+        <v>118.67843915228457</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.39173190181876</v>
+        <v>125.41741531104415</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.387548618712287</v>
+        <v>81.40421885434364</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.30417327889982</v>
+        <v>108.32635672242478</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.89918871973293</v>
+        <v>114.92272298980637</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>121.96321422358668</v>
+        <v>121.98819538537334</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.52749791459325</v>
+        <v>129.55402843366676</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.93850092215672</v>
+        <v>79.954874356041955</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.36931817325912</v>
+        <v>108.39151496011186</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.48759902202767</v>
+        <v>115.5112538134653</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.17129631357361</v>
+        <v>123.19652492123429</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.46343050297469</v>
+        <v>131.49035755017763</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.457626683456439</v>
+        <v>78.473696796711934</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.55518735046724</v>
+        <v>113.57844633494854</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.17456655508525</v>
+        <v>123.19979583257438</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>133.91740198651559</v>
+        <v>133.94483166936192</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>145.92038311226725</v>
+        <v>145.95027131029241</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.452321121728744</v>
+        <v>77.468185322889823</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.49313482542183</v>
+        <v>116.51699557611322</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>127.99429049597123</v>
+        <v>128.02050697525152</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.22476012293151</v>
+        <v>141.25368653819018</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.47166620576974</v>
+        <v>156.50371557437157</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.911762713910974</v>
+        <v>77.927721020371081</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.09248178610873</v>
+        <v>120.11707977441168</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.21407278436297</v>
+        <v>133.24135840753772</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.68637297884598</v>
+        <v>148.71682772179861</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>166.99816271291184</v>
+        <v>167.03236817516833</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.054438804303217</v>
+        <v>78.070426334447859</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.12398815178042</v>
+        <v>122.14900224414814</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.43303468212116</v>
+        <v>136.46097963039213</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.67206499875508</v>
+        <v>153.7035409379738</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.56895919552912</v>
+        <v>174.6047153490575</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.62393511615855</v>
+        <v>116.64782265806929</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.29367163510514</v>
+        <v>112.31667222914977</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.11684510029517</v>
+        <v>108.13899017425462</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.08915508365182</v>
+        <v>104.11047518447022</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.042968723687608</v>
+        <v>86.060592507514343</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.29367163510514</v>
+        <v>112.31667222914977</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.11684510029517</v>
+        <v>108.13899017425462</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.08915508365182</v>
+        <v>104.11047518447022</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>107.94528790309631</v>
+        <v>107.96739783778756</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.62393511615855</v>
+        <v>116.64782265806929</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.042968723687608</v>
+        <v>86.060592507514343</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>80.2</v>
+        <v>79.25</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17735100790092828</v>
+        <v>0.1824311310893896</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.546356441003956E-2</v>
+        <v>6.545133929824852E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.15196902608523</v>
+        <v>108.17412129431614</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.1520974151707</v>
+        <v>108.17424970969897</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736729E-2</v>
+        <v>9.6234974214736688E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.839617062712101</v>
+        <v>49.849825481251685</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.513338177664224</v>
+        <v>61.523546596203801</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43123237855403451</v>
+        <v>0.43125448249482135</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.470451423009543</v>
+        <v>62.48324695700574</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.893155005007358</v>
+        <v>75.905950539003555</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29827301630816683</v>
+        <v>0.29829843190977756</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.519047824461609</v>
+        <v>77.534925692944967</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.91049072669982</v>
+        <v>92.926368595183177</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14092649848759853</v>
+        <v>0.14095564185492604</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.668288488689925</v>
+        <v>87.686245179256304</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.3341974879629</v>
+        <v>104.35215417852928</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5300065015011595E-2</v>
+        <v>3.5331621556584647E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>80.2</v>
+        <v>79.25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19634.987455999999</v>
+        <v>19402.403439999998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17735100790092828</v>
+        <v>0.1824311310893896</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8105001449584961</v>
+        <v>7.8120999336242676</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.15196902608523</v>
+        <v>108.17412129431614</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.513338177664224</v>
+        <v>61.523546596203801</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.893155005007358</v>
+        <v>75.905950539003555</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.91049072669982</v>
+        <v>92.926368595183177</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.3341974879629</v>
+        <v>104.35215417852928</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11285400057661392</v>
+        <v>0.11423021701460993</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>7.9546134663341636E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.05638958013688</v>
+        <v>-34.063365193098434</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.696751424997203</v>
+        <v>21.701195470368116</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.767640105637994</v>
+        <v>22.772303496190631</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.408001950498313</v>
+        <v>10.410133773460315</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.210930790893016</v>
+        <v>-19.214865677106165</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.29852118638532</v>
+        <v>106.32029382145684</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.62 HKD</v>
+        <v>116.65 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.29 HKD</v>
+        <v>112.32 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.12 HKD</v>
+        <v>108.14 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.09 HKD</v>
+        <v>104.11 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.04 HKD</v>
+        <v>86.06 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.15196902608523</v>
+        <v>108.17412129431614</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.839617062712101</v>
+        <v>49.849825481251685</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.513338177664224</v>
+        <v>61.523546596203801</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.470451423009543</v>
+        <v>62.48324695700574</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.893155005007358</v>
+        <v>75.905950539003555</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.519047824461609</v>
+        <v>77.534925692944967</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.91049072669982</v>
+        <v>92.926368595183177</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.668288488689925</v>
+        <v>87.686245179256304</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.3341974879629</v>
+        <v>104.35215417852928</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,12 +21684,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21707,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1306374-6FEE-4530-94C9-744B4602B446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812BA53C-70FB-41B3-90FD-34EB628EADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>79.25</v>
+        <v>81</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19402.403439999998</v>
+        <v>19830.847679999999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1824311310893896</v>
+        <v>0.17340891157166777</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8120999336242676</v>
+        <v>7.8152999877929688</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.17412129431614</v>
+        <v>108.2184324335405</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.523546596203801</v>
+        <v>61.543966476030704</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.905950539003555</v>
+        <v>75.931545420866001</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.926368595183177</v>
+        <v>92.958129064748562</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.35215417852928</v>
+        <v>104.38807291187982</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11423021701460993</v>
+        <v>0.11180806117652611</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.0499684542586755E-2</v>
+        <v>7.8760493827160494E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.063365193098434</v>
+        <v>-34.077318498190834</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.701195470368116</v>
+        <v>21.710084885713648</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.772303496190631</v>
+        <v>22.781631667278184</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.410133773460315</v>
+        <v>10.414398054800996</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.214865677106165</v>
+        <v>-19.22273662237485</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.65 HKD</v>
+        <v>116.7 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1217049374226164E-2</v>
+        <v>3.1194122952215651E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.32 HKD</v>
+        <v>112.36 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5043370956158992E-2</v>
+        <v>4.5019841082134616E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.14 HKD</v>
+        <v>108.18 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9096582979132707E-2</v>
+        <v>5.9072429520185502E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.11 HKD</v>
+        <v>104.15 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3378231365190422E-2</v>
+        <v>7.3353433541508681E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.06 HKD</v>
+        <v>86.1 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14824898752874835</v>
+        <v>0.14822063305538999</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.17412129431614</v>
+        <v>108.2184324335405</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.849825481251685</v>
+        <v>49.870245361078581</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.523546596203801</v>
+        <v>61.543966476030704</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.48324695700574</v>
+        <v>62.508841838868186</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.905950539003555</v>
+        <v>75.931545420866001</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.534925692944967</v>
+        <v>77.566686162510351</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.926368595183177</v>
+        <v>92.958129064748562</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.686245179256304</v>
+        <v>87.722163912606845</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.35215417852928</v>
+        <v>104.38807291187982</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.603885796944</v>
+        <v>115.65124037507354</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.214865677106165</v>
+        <v>-19.22273662237485</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8339572.9211425781</v>
+        <v>-8342989.04296875</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.063365193098434</v>
+        <v>-34.077318498190834</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5313001.2573676063</v>
+        <v>5315177.6109686112</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.701195470368116</v>
+        <v>21.710084885713645</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5575235.5796998497</v>
+        <v>5577519.3517982475</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.772303496190631</v>
+        <v>22.78163166727818</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2548663.9159248779</v>
+        <v>2549707.9197981087</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.410133773460313</v>
+        <v>10.414398054800991</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.0499684542586755E-2</v>
+        <v>7.8760493827160494E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.0499684542586755E-2</v>
+        <v>7.8760493827160494E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.0499684542586755E-2</v>
+        <v>7.8760493827160494E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.3444794952681395E-2</v>
+        <v>8.1641975308641979E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0527446984078352</v>
+        <v>9.0564529552986155</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.177852674401453</v>
+        <v>10.182021806920989</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.698391185692774</v>
+        <v>7.7015446615847081</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.794155465048343</v>
+        <v>10.798577052391954</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11423021701460993</v>
+        <v>0.11180806117652611</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.12842716308393001</v>
+        <v>0.12570397292495047</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.7140582784766866E-2</v>
+        <v>9.5080798291169236E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13620385444855954</v>
+        <v>0.13331576607891302</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5982813725060857E-2</v>
+        <v>1.5637506021124358E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8425294634529053E-2</v>
+        <v>1.8027217281313918E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0410764987164911E-3</v>
+        <v>4.9321643521392832E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.410133773460315</v>
+        <v>10.414398054800996</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8120999336242676</v>
+        <v>7.8152999877929688</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26029895.704520442</v>
+        <v>26040558.276296001</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.17424970969897</v>
+        <v>108.21856090152585</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>96.975359964913096</v>
+        <v>97.015083778939243</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.53142450130532</v>
+        <v>101.57301460652546</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.44263740858376</v>
+        <v>102.48460077204268</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.35385031586222</v>
+        <v>103.39618693755993</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.2650632231407</v>
+        <v>104.30777310307721</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.150978622154327</v>
+        <v>93.189135862843912</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.6454882751875</v>
+        <v>101.68712510411294</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.39406694593666</v>
+        <v>103.4364200414885</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.15920453006663</v>
+        <v>105.20228067523797</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.9409010275774</v>
+        <v>106.9847070053613</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.763414728801592</v>
+        <v>89.800184328773469</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.75184144430845</v>
+        <v>101.79352183846028</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.29005187155568</v>
+        <v>104.33277198754</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.8761847617575</v>
+        <v>106.91996422995268</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.51070330130219</v>
+        <v>109.55556194182064</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.762775382708199</v>
+        <v>86.798315837056009</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.85100523836059</v>
+        <v>101.89272625277012</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.13382322342066</v>
+        <v>105.17688897170039</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.50911701007885</v>
+        <v>108.55356537289813</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>111.97867191849241</v>
+        <v>112.02454150783753</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.060592507514343</v>
+        <v>86.095845328158532</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.11047518447022</v>
+        <v>104.15312174083152</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.13899017425462</v>
+        <v>108.18328692279169</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.31667222914977</v>
+        <v>112.36268027285574</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.64782265806929</v>
+        <v>116.69560486187345</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.706267538752613</v>
+        <v>83.740555962180338</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.19668536072628</v>
+        <v>104.23936723118192</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.88728530939296</v>
+        <v>108.93188858050233</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.79364982536244</v>
+        <v>113.84026288031428</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.92407015159701</v>
+        <v>118.97278476990464</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.353196282099134</v>
+        <v>83.387340077685906</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.29758951767832</v>
+        <v>106.34113197711292</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.67371903843365</v>
+        <v>111.71946371056785</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.34252161990895</v>
+        <v>117.39058839179695</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.3179953201651</v>
+        <v>123.36850981285632</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.505974600575996</v>
+        <v>81.539361722606017</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.37253818781686</v>
+        <v>106.41611134831858</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.33734148547937</v>
+        <v>112.38335799588961</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.67843915228457</v>
+        <v>118.72705315327931</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.41741531104415</v>
+        <v>125.4687897847585</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.40421885434364</v>
+        <v>81.437564294379996</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.32635672242478</v>
+        <v>108.37073022152939</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.92272298980637</v>
+        <v>114.96979854463885</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>121.98819538537334</v>
+        <v>122.03816515489653</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.55402843366676</v>
+        <v>129.6070973795691</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.954874356041955</v>
+        <v>79.987626104120565</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.39151496011186</v>
+        <v>108.43591514984919</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.5112538134653</v>
+        <v>115.55857044694905</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.19652492123429</v>
+        <v>123.24698965625986</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.49035755017763</v>
+        <v>131.54421967052909</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.473696796711934</v>
+        <v>78.505841813122544</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.57844633494854</v>
+        <v>113.62497123654438</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.19979583257438</v>
+        <v>123.25026190745655</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>133.94483166936192</v>
+        <v>133.99969921081703</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>145.95027131029241</v>
+        <v>146.01005661489651</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.468185322889823</v>
+        <v>77.49991845373691</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.51699557611322</v>
+        <v>116.56472418949322</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.02050697525152</v>
+        <v>128.07294774796387</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.25368653819018</v>
+        <v>141.31154799058987</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.50371557437157</v>
+        <v>156.56782386429313</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.927721020371081</v>
+        <v>77.959642389865508</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.11707977441168</v>
+        <v>120.16628308275773</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.24135840753772</v>
+        <v>133.29593778671082</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.71682772179861</v>
+        <v>148.77774628512356</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.03236817516833</v>
+        <v>167.10078929505013</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.070426334447859</v>
+        <v>78.102406160021843</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.14900224414814</v>
+        <v>122.1990378846488</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.46097963039213</v>
+        <v>136.51687785627783</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.7035409379738</v>
+        <v>153.76650219821136</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.6047153490575</v>
+        <v>174.67623831368607</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.64782265806929</v>
+        <v>116.69560486187345</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.31667222914977</v>
+        <v>112.36268027285574</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.13899017425462</v>
+        <v>108.18328692279169</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.11047518447022</v>
+        <v>104.15312174083152</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.060592507514343</v>
+        <v>86.095845328158532</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.31667222914977</v>
+        <v>112.36268027285574</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.13899017425462</v>
+        <v>108.18328692279169</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.11047518447022</v>
+        <v>104.15312174083152</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>107.96739783778756</v>
+        <v>108.01162429731446</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.64782265806929</v>
+        <v>116.69560486187345</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.060592507514343</v>
+        <v>86.095845328158532</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>79.25</v>
+        <v>81</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1824311310893896</v>
+        <v>0.17340891157166777</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.545133929824852E-2</v>
+        <v>6.542690045252865E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.17412129431614</v>
+        <v>108.2184324335405</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.17424970969897</v>
+        <v>108.21856090152585</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736688E-2</v>
+        <v>9.623497421473666E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.849825481251685</v>
+        <v>49.870245361078581</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.523546596203801</v>
+        <v>61.543966476030704</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43125448249482135</v>
+        <v>0.43129866981000387</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.48324695700574</v>
+        <v>62.508841838868186</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.905950539003555</v>
+        <v>75.931545420866001</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29829843190977756</v>
+        <v>0.29834923946530678</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.534925692944967</v>
+        <v>77.566686162510351</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.926368595183177</v>
+        <v>92.958129064748562</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14095564185492604</v>
+        <v>0.14101390147342641</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.686245179256304</v>
+        <v>87.722163912606845</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.35215417852928</v>
+        <v>104.38807291187982</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5331621556584647E-2</v>
+        <v>3.5394705278262051E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>79.25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19402.403439999998</v>
+        <v>19830.847679999999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1824311310893896</v>
+        <v>0.17340891157166777</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8120999336242676</v>
+        <v>7.8152999877929688</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.17412129431614</v>
+        <v>108.2184324335405</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.523546596203801</v>
+        <v>61.543966476030704</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.905950539003555</v>
+        <v>75.931545420866001</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.926368595183177</v>
+        <v>92.958129064748562</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.35215417852928</v>
+        <v>104.38807291187982</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11423021701460993</v>
+        <v>0.11180806117652611</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.0499684542586755E-2</v>
+        <v>7.8760493827160494E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.063365193098434</v>
+        <v>-34.077318498190834</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.701195470368116</v>
+        <v>21.710084885713648</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.772303496190631</v>
+        <v>22.781631667278184</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.410133773460315</v>
+        <v>10.414398054800996</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.214865677106165</v>
+        <v>-19.22273662237485</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.32029382145684</v>
+        <v>106.36384558120795</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.65 HKD</v>
+        <v>116.7 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.32 HKD</v>
+        <v>112.36 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.14 HKD</v>
+        <v>108.18 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.11 HKD</v>
+        <v>104.15 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.06 HKD</v>
+        <v>86.1 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.17412129431614</v>
+        <v>108.2184324335405</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.849825481251685</v>
+        <v>49.870245361078581</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.523546596203801</v>
+        <v>61.543966476030704</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.48324695700574</v>
+        <v>62.508841838868186</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.905950539003555</v>
+        <v>75.931545420866001</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.534925692944967</v>
+        <v>77.566686162510351</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.926368595183177</v>
+        <v>92.958129064748562</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.686245179256304</v>
+        <v>87.722163912606845</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.35215417852928</v>
+        <v>104.38807291187982</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,15 +21684,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21707,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812BA53C-70FB-41B3-90FD-34EB628EADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3E05E2-F688-4EF9-BBFE-87EF64E458C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>81</v>
+        <v>79.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19830.847679999999</v>
+        <v>19512.574816</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17340891157166777</v>
+        <v>0.1802044512971728</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8152999877929688</v>
+        <v>7.815619945526123</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.2184324335405</v>
+        <v>108.22286288718669</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.543966476030704</v>
+        <v>61.546008159738619</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.931545420866001</v>
+        <v>75.934104527665241</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.958129064748562</v>
+        <v>92.961304638445242</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.38807291187982</v>
+        <v>104.3916642499931</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11180806117652611</v>
+        <v>0.11363643319612667</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>7.8760493827160494E-2</v>
+        <v>8.0045169385194473E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.077318498190834</v>
+        <v>-34.078713620783141</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.710084885713648</v>
+        <v>21.710973694787828</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.781631667278184</v>
+        <v>22.78256434538871</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.414398054800996</v>
+        <v>10.414824419393396</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.22273662237485</v>
+        <v>-19.223523599617479</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1194122952215651E-2</v>
+        <v>3.1191831683138153E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.36 HKD</v>
+        <v>112.37 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5019841082134616E-2</v>
+        <v>4.5017489504461626E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.18 HKD</v>
+        <v>108.19 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9072429520185502E-2</v>
+        <v>5.9070015621868956E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.15 HKD</v>
+        <v>104.16 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3353433541508681E-2</v>
+        <v>7.3350955245851529E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14822063305538999</v>
+        <v>0.14821779931117282</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.2184324335405</v>
+        <v>108.22286288718669</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.870245361078581</v>
+        <v>49.872287044786503</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.543966476030704</v>
+        <v>61.546008159738619</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.508841838868186</v>
+        <v>62.511400945667432</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.931545420866001</v>
+        <v>75.934104527665241</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.566686162510351</v>
+        <v>77.569861736207031</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.958129064748562</v>
+        <v>92.961304638445242</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.722163912606845</v>
+        <v>87.725755250720127</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.38807291187982</v>
+        <v>104.3916642499931</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.65124037507354</v>
+        <v>115.65597512726023</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.22273662237485</v>
+        <v>-19.223523599617479</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8342989.04296875</v>
+        <v>-8343330.6042480469</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.077318498190834</v>
+        <v>-34.078713620783141</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5315177.6109686112</v>
+        <v>5315395.2138990648</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.710084885713645</v>
+        <v>21.710973694787828</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5577519.3517982475</v>
+        <v>5577747.6949778078</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.78163166727818</v>
+        <v>22.78256434538871</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2549707.9197981087</v>
+        <v>2549812.3046288257</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.414398054800991</v>
+        <v>10.414824419393398</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>7.8760493827160494E-2</v>
+        <v>8.0045169385194473E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>7.8760493827160494E-2</v>
+        <v>8.0045169385194473E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>7.8760493827160494E-2</v>
+        <v>8.0045169385194473E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.1641975308641979E-2</v>
+        <v>8.2973651191969894E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0564529552986155</v>
+        <v>9.0568237257312951</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.182021806920989</v>
+        <v>10.18243865804908</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7015446615847081</v>
+        <v>7.701859962184245</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.798577052391954</v>
+        <v>10.799019145240644</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11180806117652611</v>
+        <v>0.11363643319612667</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.12570397292495047</v>
+        <v>0.12775958165682658</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.5080798291169236E-2</v>
+        <v>9.6635633151621644E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13331576607891302</v>
+        <v>0.13549584874831422</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5637506021124358E-2</v>
+        <v>1.5892571991355998E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8027217281313918E-2</v>
+        <v>1.832126223069545E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9321643521392832E-3</v>
+        <v>5.0126137079458209E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.414398054800996</v>
+        <v>10.414824419393396</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8152999877929688</v>
+        <v>7.815619945526123</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26040558.276296001</v>
+        <v>26041624.374591544</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.21856090152585</v>
+        <v>108.22299136043151</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.015083778939243</v>
+        <v>97.019055568420924</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.57301460652546</v>
+        <v>101.57717299731709</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.48460077204268</v>
+        <v>102.48879648309632</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.39618693755993</v>
+        <v>103.40041996887555</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.30777310307721</v>
+        <v>104.31204345465483</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.189135862843912</v>
+        <v>93.192951018335307</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.68712510411294</v>
+        <v>101.69128816657889</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.4364200414885</v>
+        <v>103.44065471994406</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.20228067523797</v>
+        <v>105.20658764788138</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.9847070053613</v>
+        <v>106.9890869503908</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.800184328773469</v>
+        <v>89.803860740870192</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.79352183846028</v>
+        <v>101.7976892567997</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.33277198754</v>
+        <v>104.33704336256987</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.91996422995268</v>
+        <v>106.92434152441834</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.55556194182064</v>
+        <v>109.56004713743798</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.798315837056009</v>
+        <v>86.801869352905726</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.89272625277012</v>
+        <v>101.89689773253004</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.17688897170039</v>
+        <v>105.18119490480957</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.55356537289813</v>
+        <v>108.55800954685905</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.02454150783753</v>
+        <v>112.02912778327347</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.095845328158532</v>
+        <v>86.099370084923891</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.15312174083152</v>
+        <v>104.1573857609952</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.18328692279169</v>
+        <v>108.18771593758359</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.36268027285574</v>
+        <v>112.36728039166466</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.69560486187345</v>
+        <v>116.7003823702556</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.740555962180338</v>
+        <v>83.743984293594423</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.23936723118192</v>
+        <v>104.24363478222881</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.93188858050233</v>
+        <v>108.93634824298398</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.84026288031428</v>
+        <v>113.84492349123258</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.97278476990464</v>
+        <v>118.9776555058433</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.387340077685906</v>
+        <v>83.390753948471001</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.34113197711292</v>
+        <v>106.34548557423416</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.71946371056785</v>
+        <v>111.72403749614408</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.39058839179695</v>
+        <v>117.39539435274716</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.36850981285632</v>
+        <v>123.37356050941358</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.539361722606017</v>
+        <v>81.542699937310559</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.41611134831858</v>
+        <v>106.42046801508906</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.38335799588961</v>
+        <v>112.3879589612428</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.72705315327931</v>
+        <v>118.73191382898598</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.4687897847585</v>
+        <v>125.47392646660359</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.437564294379996</v>
+        <v>81.440898341506269</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.37073022152939</v>
+        <v>108.37516691023438</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.96979854463885</v>
+        <v>114.97450539865353</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.03816515489653</v>
+        <v>122.04316138725386</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.6070973795691</v>
+        <v>129.61240348338382</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.987626104120565</v>
+        <v>79.990900790897612</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.43591514984919</v>
+        <v>108.44035450721975</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.55857044694905</v>
+        <v>115.56330140523657</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.24698965625986</v>
+        <v>123.252035377792</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.54421967052909</v>
+        <v>131.54960507996969</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.505841813122544</v>
+        <v>78.509055835773651</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.62497123654438</v>
+        <v>113.62962303344065</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.25026190745655</v>
+        <v>123.25530776295437</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>133.99969921081703</v>
+        <v>134.0051851473863</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.01005661489651</v>
+        <v>146.01603425450156</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.49991845373691</v>
+        <v>77.503091293969121</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.56472418949322</v>
+        <v>116.5694963396315</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.07294774796387</v>
+        <v>128.07819104381991</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.31154799058987</v>
+        <v>141.31733327364159</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.56782386429313</v>
+        <v>156.5742337380135</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.959642389865508</v>
+        <v>77.962834051157529</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.16628308275773</v>
+        <v>120.17120268041832</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.29593778671082</v>
+        <v>133.30139491134577</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.77774628512356</v>
+        <v>148.78383723371408</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.10078929505013</v>
+        <v>167.10763038750142</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.102406160021843</v>
+        <v>78.105603666050783</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.1990378846488</v>
+        <v>122.20404070312235</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.51687785627783</v>
+        <v>136.52246684593203</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.76650219821136</v>
+        <v>153.77279738605512</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.67623831368607</v>
+        <v>174.68338954439176</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.69560486187345</v>
+        <v>116.7003823702556</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.36268027285574</v>
+        <v>112.36728039166466</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.18328692279169</v>
+        <v>108.18771593758359</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.15312174083152</v>
+        <v>104.1573857609952</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.095845328158532</v>
+        <v>86.099370084923891</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.36268027285574</v>
+        <v>112.36728039166466</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.18328692279169</v>
+        <v>108.18771593758359</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.15312174083152</v>
+        <v>104.1573857609952</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.01162429731446</v>
+        <v>108.01604628425271</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.69560486187345</v>
+        <v>116.7003823702556</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.095845328158532</v>
+        <v>86.099370084923891</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>81</v>
+        <v>79.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17340891157166777</v>
+        <v>0.1802044512971728</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.542690045252865E-2</v>
+        <v>6.5424458032863828E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.2184324335405</v>
+        <v>108.22286288718669</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.21856090152585</v>
+        <v>108.22299136043151</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.623497421473666E-2</v>
+        <v>9.6234974214736702E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.870245361078581</v>
+        <v>49.872287044786503</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.543966476030704</v>
+        <v>61.546008159738619</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43129866981000387</v>
+        <v>0.43130308589327193</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.508841838868186</v>
+        <v>62.511400945667432</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.931545420866001</v>
+        <v>75.934104527665241</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29834923946530678</v>
+        <v>0.29835431717584282</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.566686162510351</v>
+        <v>77.569861736207031</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.958129064748562</v>
+        <v>92.961304638445242</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14101390147342641</v>
+        <v>0.14101972394363982</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.722163912606845</v>
+        <v>87.725755250720127</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.38807291187982</v>
+        <v>104.3916642499931</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5394705278262051E-2</v>
+        <v>3.5401009869673317E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>81</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19830.847679999999</v>
+        <v>19512.574816</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17340891157166777</v>
+        <v>0.1802044512971728</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8152999877929688</v>
+        <v>7.815619945526123</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.2184324335405</v>
+        <v>108.22286288718669</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.543966476030704</v>
+        <v>61.546008159738619</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.931545420866001</v>
+        <v>75.934104527665241</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.958129064748562</v>
+        <v>92.961304638445242</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.38807291187982</v>
+        <v>104.3916642499931</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11180806117652611</v>
+        <v>0.11363643319612667</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>7.8760493827160494E-2</v>
+        <v>8.0045169385194473E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.077318498190834</v>
+        <v>-34.078713620783141</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.710084885713648</v>
+        <v>21.710973694787828</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.781631667278184</v>
+        <v>22.78256434538871</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.414398054800996</v>
+        <v>10.414824419393396</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.22273662237485</v>
+        <v>-19.223523599617479</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.36384558120795</v>
+        <v>106.36820010822225</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.36 HKD</v>
+        <v>112.37 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.18 HKD</v>
+        <v>108.19 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.15 HKD</v>
+        <v>104.16 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.2184324335405</v>
+        <v>108.22286288718669</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.870245361078581</v>
+        <v>49.872287044786503</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.543966476030704</v>
+        <v>61.546008159738619</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.508841838868186</v>
+        <v>62.511400945667432</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.931545420866001</v>
+        <v>75.934104527665241</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.566686162510351</v>
+        <v>77.569861736207031</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.958129064748562</v>
+        <v>92.961304638445242</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.722163912606845</v>
+        <v>87.725755250720127</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.38807291187982</v>
+        <v>104.3916642499931</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,12 +21684,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21707,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3E05E2-F688-4EF9-BBFE-87EF64E458C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB2FBBF-E9D3-45DF-A56A-90ADA8DD26A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>79.7</v>
+        <v>78.25</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19512.574816</v>
+        <v>19157.578160000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1802044512971728</v>
+        <v>0.18798290292432629</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.815619945526123</v>
+        <v>7.8162999153137207</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.22286288718669</v>
+        <v>108.23227842653016</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.546008159738619</v>
+        <v>61.550347117961422</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.934104527665241</v>
+        <v>75.939543106347386</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.961304638445242</v>
+        <v>92.968053324125506</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.3916642499931</v>
+        <v>104.39929651251104</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11363643319612667</v>
+        <v>0.11575222596768356</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.0045169385194473E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.078713620783141</v>
+        <v>-34.081678516187964</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.710973694787828</v>
+        <v>21.712862579645932</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.78256434538871</v>
+        <v>22.784546460121366</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.414824419393396</v>
+        <v>10.415730523579333</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.223523599617479</v>
+        <v>-19.225196072863366</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.7 HKD</v>
+        <v>116.71 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1191831683138153E-2</v>
+        <v>3.1186962931891854E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.37 HKD</v>
+        <v>112.38 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5017489504461626E-2</v>
+        <v>4.5012492602876368E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.19 HKD</v>
+        <v>108.2 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9070015621868956E-2</v>
+        <v>5.9064886294536878E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.16 HKD</v>
+        <v>104.17 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3350955245851529E-2</v>
+        <v>7.3345689079992588E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.1 HKD</v>
+        <v>86.11 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14821779931117282</v>
+        <v>0.14821177784950459</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.22286288718669</v>
+        <v>108.23227842653016</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.872287044786503</v>
+        <v>49.876626003009299</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.546008159738619</v>
+        <v>61.550347117961422</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.511400945667432</v>
+        <v>62.516839524349578</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.934104527665241</v>
+        <v>75.939543106347386</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.569861736207031</v>
+        <v>77.576610421887295</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.961304638445242</v>
+        <v>92.968053324125506</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.725755250720127</v>
+        <v>87.733387513238071</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.3916642499931</v>
+        <v>104.39929651251104</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.65597512726023</v>
+        <v>115.66603735768979</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.223523599617479</v>
+        <v>-19.225196072863366</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8343330.6042480469</v>
+        <v>-8344056.4855957031</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.078713620783141</v>
+        <v>-34.081678516187964</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5315395.2138990648</v>
+        <v>5315857.6606633374</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.710973694787828</v>
+        <v>21.712862579645932</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5577747.6949778078</v>
+        <v>5578232.966772222</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.78256434538871</v>
+        <v>22.784546460121362</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2549812.3046288257</v>
+        <v>2550034.1418398563</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.414824419393398</v>
+        <v>10.415730523579331</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.0045169385194473E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.0045169385194473E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.0045169385194473E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.2973651191969894E-2</v>
+        <v>8.4511182108626209E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0568237257312951</v>
+        <v>9.0576116819712382</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.18243865804908</v>
+        <v>10.1833245443511</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.701859962184245</v>
+        <v>7.7025300346953305</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.799019145240644</v>
+        <v>10.7999586749012</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11363643319612667</v>
+        <v>0.11575222596768356</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.12775958165682658</v>
+        <v>0.13013833283515783</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.6635633151621644E-2</v>
+        <v>9.8434888622304539E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13549584874831422</v>
+        <v>0.13801864121279489</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5892571991355998E-2</v>
+        <v>1.6187066935604767E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.832126223069545E-2</v>
+        <v>1.8660761658612489E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0126137079458209E-3</v>
+        <v>5.1054992015754875E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.414824419393396</v>
+        <v>10.415730523579333</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.815619945526123</v>
+        <v>7.8162999153137207</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26041624.374591544</v>
+        <v>26043890.032072093</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.22299136043151</v>
+        <v>108.23240691095232</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.019055568420924</v>
+        <v>97.027496360970659</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.57717299731709</v>
+        <v>101.5860103524123</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.48879648309632</v>
+        <v>102.4977131507006</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.40041996887555</v>
+        <v>103.40941594898894</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.31204345465483</v>
+        <v>104.32111874727731</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.192951018335307</v>
+        <v>93.201058934476464</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.69128816657889</v>
+        <v>101.70013544985227</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.44065471994406</v>
+        <v>103.44965420053666</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.20658764788138</v>
+        <v>105.21574076709079</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.9890869503908</v>
+        <v>106.99839514951461</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.803860740870192</v>
+        <v>89.81167380145132</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.7976892567997</v>
+        <v>101.80654579711567</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.33704336256987</v>
+        <v>104.34612083021906</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.92434152441834</v>
+        <v>106.93364409060017</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.56004713743798</v>
+        <v>109.56957901366795</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.801869352905726</v>
+        <v>86.809421236067692</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.89689773253004</v>
+        <v>101.90576290412115</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.18119490480957</v>
+        <v>105.19034581481507</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.55800954685905</v>
+        <v>108.56745424442727</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.02912778327347</v>
+        <v>112.03887447294805</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.099370084923891</v>
+        <v>86.106860849674092</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.1573857609952</v>
+        <v>104.16644759818358</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.18771593758359</v>
+        <v>108.19712841909363</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.36728039166466</v>
+        <v>112.37705650108572</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.7003823702556</v>
+        <v>116.71053546556548</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.743984293594423</v>
+        <v>83.751270136510229</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.24363478222881</v>
+        <v>104.25270412320181</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.93634824298398</v>
+        <v>108.9458258565441</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.84492349123258</v>
+        <v>113.85482815765506</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.9776555058433</v>
+        <v>118.9880067270781</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.390753948471001</v>
+        <v>83.398009059856292</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.34548557423416</v>
+        <v>106.35473777914457</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.72403749614408</v>
+        <v>111.73375764254006</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.39539435274716</v>
+        <v>117.40560791506458</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.37356050941358</v>
+        <v>123.38429418048759</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.542699937310559</v>
+        <v>81.549794265430776</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.42046801508906</v>
+        <v>106.42972674357593</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.3879589612428</v>
+        <v>112.39773686972812</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.73191382898598</v>
+        <v>118.74224367035366</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.47392646660359</v>
+        <v>125.48484287243232</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.440898341506269</v>
+        <v>81.447983812746301</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.37516691023438</v>
+        <v>108.38459570023933</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.97450539865353</v>
+        <v>114.98450834027045</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.04316138725386</v>
+        <v>122.05377931175693</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.61240348338382</v>
+        <v>129.62367994245946</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.990900790897612</v>
+        <v>79.997860110337356</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.44035450721975</v>
+        <v>108.44978896863614</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.56330140523657</v>
+        <v>115.57335557292363</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.252035377792</v>
+        <v>123.26275847601082</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.54960507996969</v>
+        <v>131.56105007827415</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.509055835773651</v>
+        <v>78.515886232644689</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.62962303344065</v>
+        <v>113.63950896842435</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.25530776295437</v>
+        <v>123.26603114587525</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.0051851473863</v>
+        <v>134.0168437845663</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.01603425450156</v>
+        <v>146.02873785223147</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.503091293969121</v>
+        <v>77.509834170528208</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.5694963396315</v>
+        <v>116.57963804767499</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.07819104381991</v>
+        <v>128.089334024283</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.31733327364159</v>
+        <v>141.32962807786183</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.5742337380135</v>
+        <v>156.587855913759</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.962834051157529</v>
+        <v>77.969616925974861</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.17120268041832</v>
+        <v>120.18165774191459</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.30139491134577</v>
+        <v>133.31299231779798</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.78383723371408</v>
+        <v>148.79678163414641</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.10763038750142</v>
+        <v>167.12216898338153</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.105603666050783</v>
+        <v>78.112398962022837</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.20404070312235</v>
+        <v>122.21467262434928</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.52246684593203</v>
+        <v>136.53434449011516</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.77279738605512</v>
+        <v>153.78617583294809</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.68338954439176</v>
+        <v>174.6985872418378</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.7003823702556</v>
+        <v>116.71053546556548</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.36728039166466</v>
+        <v>112.37705650108572</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.18771593758359</v>
+        <v>108.19712841909363</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.1573857609952</v>
+        <v>104.16644759818358</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.099370084923891</v>
+        <v>86.106860849674092</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.36728039166466</v>
+        <v>112.37705650108572</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.18771593758359</v>
+        <v>108.19712841909363</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.1573857609952</v>
+        <v>104.16644759818358</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.01604628425271</v>
+        <v>108.02544383026455</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.7003823702556</v>
+        <v>116.71053546556548</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.099370084923891</v>
+        <v>86.106860849674092</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>79.7</v>
+        <v>78.25</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1802044512971728</v>
+        <v>0.18798290292432629</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5424458032863828E-2</v>
+        <v>6.5419268100243275E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.22286288718669</v>
+        <v>108.23227842653016</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.22299136043151</v>
+        <v>108.23240691095232</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736702E-2</v>
+        <v>9.6234974214736688E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.872287044786503</v>
+        <v>49.876626003009299</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.546008159738619</v>
+        <v>61.550347117961422</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43130308589327193</v>
+        <v>0.43131246969227577</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.511400945667432</v>
+        <v>62.516839524349578</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.934104527665241</v>
+        <v>75.939543106347386</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29835431717584282</v>
+        <v>0.29836510687616735</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.569861736207031</v>
+        <v>77.576610421887295</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.961304638445242</v>
+        <v>92.968053324125506</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14101972394363982</v>
+        <v>0.14103209619454016</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.725755250720127</v>
+        <v>87.733387513238071</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.3916642499931</v>
+        <v>104.39929651251104</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5401009869673317E-2</v>
+        <v>3.5414406586857572E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>79.7</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19512.574816</v>
+        <v>19157.578160000001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1802044512971728</v>
+        <v>0.18798290292432629</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.815619945526123</v>
+        <v>7.8162999153137207</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.22286288718669</v>
+        <v>108.23227842653016</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.546008159738619</v>
+        <v>61.550347117961422</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.934104527665241</v>
+        <v>75.939543106347386</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.961304638445242</v>
+        <v>92.968053324125506</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.3916642499931</v>
+        <v>104.39929651251104</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11363643319612667</v>
+        <v>0.11575222596768356</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.0045169385194473E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.078713620783141</v>
+        <v>-34.081678516187964</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.710973694787828</v>
+        <v>21.712862579645932</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.78256434538871</v>
+        <v>22.784546460121366</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.414824419393396</v>
+        <v>10.415730523579333</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.223523599617479</v>
+        <v>-19.225196072863366</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.36820010822225</v>
+        <v>106.37745428932868</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.7 HKD</v>
+        <v>116.71 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.37 HKD</v>
+        <v>112.38 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.19 HKD</v>
+        <v>108.2 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.16 HKD</v>
+        <v>104.17 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.1 HKD</v>
+        <v>86.11 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.22286288718669</v>
+        <v>108.23227842653016</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.872287044786503</v>
+        <v>49.876626003009299</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.546008159738619</v>
+        <v>61.550347117961422</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.511400945667432</v>
+        <v>62.516839524349578</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.934104527665241</v>
+        <v>75.939543106347386</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.569861736207031</v>
+        <v>77.576610421887295</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.961304638445242</v>
+        <v>92.968053324125506</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.725755250720127</v>
+        <v>87.733387513238071</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.3916642499931</v>
+        <v>104.39929651251104</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,15 +21684,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21707,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB2FBBF-E9D3-45DF-A56A-90ADA8DD26A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A5524B-5B17-8148-9E27-9F0C24BD14EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3275,27 +3286,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4047,7 +4058,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4089,17 +4100,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4108,7 +4119,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4182,10 +4193,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4196,7 +4207,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4234,7 +4245,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4244,7 +4255,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4255,19 +4266,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4275,8 +4286,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4299,29 +4310,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4338,15 +4349,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4357,11 +4368,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4422,14 +4433,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4442,7 +4453,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4479,7 +4490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4496,7 +4507,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4542,7 +4553,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4557,13 +4568,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4579,53 +4590,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4642,7 +4653,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4655,21 +4666,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4679,14 +4690,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4695,8 +4706,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4708,7 +4719,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4716,7 +4727,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4755,7 +4766,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4769,39 +4780,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4812,7 +4823,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4823,10 +4834,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4835,7 +4846,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4848,7 +4859,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4857,8 +4868,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4866,10 +4877,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4878,10 +4889,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4898,16 +4909,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4928,7 +4939,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4946,7 +4957,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4956,10 +4967,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4974,7 +4985,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4988,34 +4999,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5036,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,21 +5054,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5330,7 +5341,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5339,7 +5350,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5352,7 +5363,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5360,7 +5371,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5374,7 +5385,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5388,7 +5399,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5398,7 +5409,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5408,16 +5419,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.25</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5425,43 +5436,43 @@
         <v>244825280</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19157.578160000001</v>
+        <v>18949.476672000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18798290292432629</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.19255135221428826</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5476,7 +5487,7 @@
         <v>USD/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5487,10 +5498,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8162999153137207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>7.8147997856140137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5504,14 +5515,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.23227842653016</v>
+        <v>108.21150613566442</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5520,7 +5531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5536,11 +5547,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5555,13 +5566,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.550347117961422</v>
+        <v>61.540774633691498</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5570,13 +5581,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.939543106347386</v>
+        <v>75.92754467119029</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5585,13 +5596,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.968053324125506</v>
+        <v>92.953164568760769</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5600,13 +5611,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.39929651251104</v>
+        <v>104.38245843545533</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5615,11 +5626,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5629,25 +5640,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5656,16 +5667,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5678,20 +5689,20 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5704,7 +5715,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5717,16 +5728,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5739,16 +5750,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5763,7 +5774,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5778,7 +5789,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5791,12 +5802,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5809,16 +5820,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5831,8 +5842,8 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5840,7 +5851,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5853,25 +5864,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5884,7 +5895,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5897,23 +5908,23 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11575222596768356</v>
+        <v>0.11700094723101183</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.2423772609819118E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5923,7 +5934,7 @@
         <v>5.5052997070948786</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5934,7 +5945,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5947,7 +5958,7 @@
         <v>0.11962870133363827</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5961,7 +5972,7 @@
         <v>0.25059892762124586</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5975,7 +5986,7 @@
         <v>0.26833431587768736</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5989,7 +6000,7 @@
         <v>1.7790164507082717</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -5999,45 +6010,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6051,21 +6062,21 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.081678516187964</v>
+        <v>-34.075137449607624</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6075,7 +6086,7 @@
         <v>0.29042568125650897</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6085,16 +6096,16 @@
         <v>2.3236948196964886</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6108,7 +6119,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6122,30 +6133,30 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.712862579645932</v>
+        <v>21.708695376445657</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6159,38 +6170,38 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.784546460121366</v>
+        <v>22.780173575865451</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.415730523579333</v>
+        <v>10.413731502703488</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6200,42 +6211,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6244,7 +6255,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6253,7 +6264,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6262,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6271,76 +6282,76 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.225196072863366</v>
+        <v>-19.221506310709398</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6357,7 +6368,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (5yrs)</v>
@@ -6368,7 +6379,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.71 HKD</v>
+        <v>116.69 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,10 +6387,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1186962931891854E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6">
+        <v>3.1197705356523227E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (5yrs)</v>
@@ -6390,7 +6401,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.38 HKD</v>
+        <v>112.36 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,10 +6409,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5012492602876368E-2</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6">
+        <v>4.5023517779234419E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (5yrs)</v>
@@ -6412,7 +6423,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.2 HKD</v>
+        <v>108.18 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,10 +6431,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9064886294536878E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6">
+        <v>5.9076203655932524E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (5yrs)</v>
@@ -6434,7 +6445,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.17 HKD</v>
+        <v>104.15 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,10 +6453,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3345689079992588E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6">
+        <v>7.3357308362837867E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (5yrs)</v>
@@ -6456,7 +6467,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.11 HKD</v>
+        <v>86.09 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,32 +6475,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14821177784950459</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+        <v>0.1482250636225694</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.23227842653016</v>
+        <v>108.21150613566442</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6498,7 +6509,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6508,30 +6519,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6540,7 +6551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6553,14 +6564,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6579,7 +6590,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6589,18 +6600,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.876626003009299</v>
+        <v>49.867053518739375</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.550347117961422</v>
+        <v>61.540774633691498</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6610,25 +6621,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.516839524349578</v>
+        <v>62.504841089192475</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.939543106347386</v>
+        <v>75.92754467119029</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6647,7 +6658,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6657,18 +6668,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.576610421887295</v>
+        <v>77.561721666522558</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.968053324125506</v>
+        <v>92.953164568760769</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6678,18 +6689,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.733387513238071</v>
+        <v>87.716549436182362</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.39929651251104</v>
+        <v>104.38245843545533</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6699,21 +6710,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6722,80 +6733,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6835,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6851,15 +6862,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>USD</v>
@@ -6908,7 +6919,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6924,7 +6935,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6932,7 +6943,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6954,7 +6965,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6976,7 +6987,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7001,7 +7012,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7023,7 +7034,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7045,7 +7056,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7061,7 +7072,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7077,7 +7088,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7093,7 +7104,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7115,7 +7126,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7137,7 +7148,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7159,7 +7170,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7181,7 +7192,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7205,13 +7216,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7227,7 +7238,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7243,7 +7254,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7259,7 +7270,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7281,7 +7292,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7303,7 +7314,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7325,7 +7336,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7351,7 +7362,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7359,7 +7370,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7381,7 +7392,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7402,7 +7413,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7423,7 +7434,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7444,7 +7455,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7465,7 +7476,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7481,12 +7492,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7535,7 +7546,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7584,7 +7595,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7633,7 +7644,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7682,7 +7693,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7731,7 +7742,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7780,7 +7791,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7829,7 +7840,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7878,7 +7889,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7927,7 +7938,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7976,7 +7987,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8025,7 +8036,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8074,7 +8085,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8123,12 +8134,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8177,7 +8188,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8226,12 +8237,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8280,7 +8291,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8329,7 +8340,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8378,7 +8389,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8427,13 +8438,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8482,7 +8493,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8531,7 +8542,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8580,7 +8591,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8629,7 +8640,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8678,12 +8689,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8733,7 +8744,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8782,7 +8793,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8832,7 +8843,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8881,7 +8892,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8931,7 +8942,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8947,13 +8958,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9002,7 +9013,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9036,7 +9047,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9070,7 +9081,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9119,7 +9130,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9200,7 +9211,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9211,7 +9222,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9227,7 +9238,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9238,7 +9249,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9258,7 +9269,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9280,7 +9291,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9301,7 +9312,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9322,7 +9333,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9343,7 +9354,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9364,7 +9375,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9385,7 +9396,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9405,7 +9416,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9417,7 +9428,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9441,12 +9452,12 @@
         <v>1612388.4</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9466,7 +9477,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9486,7 +9497,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9506,7 +9517,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9526,7 +9537,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9546,7 +9557,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9566,7 +9577,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9586,7 +9597,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9606,7 +9617,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9618,7 +9629,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9631,7 +9642,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9655,7 +9666,7 @@
         <v>141941.1</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9672,7 +9683,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9691,7 +9702,7 @@
         <v>-549409.29999999981</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9706,7 +9717,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9725,7 +9736,7 @@
         <v>-602179.29999999981</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9741,7 +9752,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9758,7 +9769,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9778,7 +9789,7 @@
         <v>2314027.7000000002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9789,7 +9800,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9802,7 +9813,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9821,7 +9832,7 @@
         <v>559698.19999999995</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9838,7 +9849,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9854,7 +9865,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9870,7 +9881,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9889,7 +9900,7 @@
         <v>28062.2</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9909,7 +9920,7 @@
         <v>1754329.5</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9929,7 +9940,7 @@
         <v>1040662.8</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9949,7 +9960,7 @@
         <v>713666.7</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9960,7 +9971,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9974,7 +9985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9988,25 +9999,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.66603735768979</v>
+        <v>115.64383835563413</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.225196072863366</v>
+        <v>-19.221506310709398</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10019,7 +10030,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10033,7 +10044,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10044,10 +10055,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10059,7 +10070,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10073,7 +10084,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10087,10 +10098,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10102,7 +10113,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10113,7 +10124,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10124,10 +10135,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10139,7 +10150,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10155,7 +10166,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10166,7 +10177,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10180,7 +10191,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10196,7 +10207,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10206,7 +10217,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10216,7 +10227,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10226,7 +10237,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10236,10 +10247,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10251,7 +10262,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10267,7 +10278,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10283,7 +10294,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10296,7 +10307,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10309,10 +10320,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10324,7 +10335,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10338,7 +10349,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10352,7 +10363,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10366,7 +10377,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10380,7 +10391,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10391,7 +10402,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10399,68 +10410,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8344056.4855957031</v>
+        <v>-8342455.0671386719</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.081678516187964</v>
+        <v>-34.075137449607624</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5315857.6606633374</v>
+        <v>5314837.4239730136</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.712862579645932</v>
+        <v>21.708695376445657</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5578232.966772222</v>
+        <v>5577162.3741598604</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.784546460121362</v>
+        <v>22.780173575865451</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2550034.1418398563</v>
+        <v>2549544.7309942022</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.415730523579331</v>
+        <v>10.413731502703484</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10486,19 +10497,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10555,7 +10566,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10578,7 +10589,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10598,7 +10609,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10655,7 +10666,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10710,7 +10721,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10765,7 +10776,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10820,7 +10831,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10877,7 +10888,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -10934,7 +10945,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10989,7 +11000,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11044,7 +11055,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11099,7 +11110,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11156,7 +11167,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11213,7 +11224,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11268,7 +11279,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11323,7 +11334,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11349,7 +11360,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11374,7 +11385,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11431,7 +11442,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11450,7 +11461,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11473,7 +11484,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11494,7 +11505,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11551,7 +11562,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11608,7 +11619,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11665,7 +11676,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11722,18 +11733,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11790,7 +11801,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11848,7 +11859,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11906,7 +11917,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11961,18 +11972,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12029,18 +12040,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12095,18 +12106,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12164,10 +12175,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12190,14 +12201,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12252,7 +12263,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12307,7 +12318,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12364,7 +12375,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12419,11 +12430,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12433,7 +12444,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12457,7 +12468,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12481,7 +12492,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12536,11 +12547,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12550,7 +12561,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12605,7 +12616,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12660,7 +12671,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12715,7 +12726,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12770,7 +12781,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12826,7 +12837,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12881,11 +12892,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12895,7 +12906,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12920,7 +12931,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12945,7 +12956,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12970,7 +12981,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12997,10 +13008,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13023,7 +13034,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13044,7 +13055,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13101,7 +13112,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13158,7 +13169,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13215,7 +13226,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13272,7 +13283,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13329,7 +13340,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13386,7 +13397,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13443,7 +13454,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13500,7 +13511,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13558,7 +13569,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13615,7 +13626,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13672,7 +13683,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13731,7 +13742,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13757,7 +13768,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13781,7 +13792,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13838,18 +13849,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13905,7 +13916,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13961,7 +13972,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14016,7 +14027,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14037,27 +14048,27 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.2423772609819118E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.2423772609819118E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.152843450479233E-2</v>
+        <v>8.2423772609819118E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.4511182108626209E-2</v>
+        <v>8.5439276485788113E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14092,11 +14103,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14117,7 +14128,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14174,7 +14185,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14231,10 +14242,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14257,7 +14268,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14267,7 +14278,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14324,7 +14335,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14381,7 +14392,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14438,7 +14449,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14495,7 +14506,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14552,11 +14563,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14579,7 +14590,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14636,7 +14647,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14693,7 +14704,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14720,18 +14731,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14785,7 +14796,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14840,11 +14851,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14903,7 +14914,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14961,7 +14972,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15018,7 +15029,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15077,7 +15088,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15136,7 +15147,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15155,7 +15166,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15178,7 +15189,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15199,7 +15210,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15207,22 +15218,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0576116819712382</v>
+        <v>9.055873315680314</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.1833245443511</v>
+        <v>10.181370127586614</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7025300346953305</v>
+        <v>7.7010517400811116</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.7999586749012</v>
+        <v>10.797885911708979</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15257,29 +15268,29 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11575222596768356</v>
+        <v>0.11700094723101183</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13013833283515783</v>
+        <v>0.13154224971042136</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.8434888622304539E-2</v>
+        <v>9.9496792507507897E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13801864121279489</v>
+        <v>0.13950756991872065</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15314,22 +15325,22 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6187066935604767E-2</v>
+        <v>1.6364831882572001E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8660761658612489E-2</v>
+        <v>1.8865692503700612E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1054992015754875E-3</v>
+        <v>5.16156734526204E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15364,688 +15375,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16067,16 +16078,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16091,7 +16102,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16106,7 +16117,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16138,7 +16149,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16166,7 +16177,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16199,7 +16210,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16229,7 +16240,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16246,7 +16257,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.415730523579333</v>
+        <v>10.413731502703488</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16264,14 +16275,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*USD/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8162999153137207</v>
+        <v>7.8147997856140137</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16290,13 +16301,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26043890.032072093</v>
+        <v>26038891.603997897</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16312,13 +16323,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16328,7 +16339,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16343,7 +16354,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16361,7 +16372,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16386,7 +16397,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16402,7 +16413,7 @@
         <v>1.0085935369058155E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>550</v>
       </c>
@@ -16421,7 +16432,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16441,17 +16452,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.23240691095232</v>
+        <v>108.21163459542744</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16490,7 +16501,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16539,7 +16550,7 @@
         <v>267195.88505103323</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16588,7 +16599,7 @@
         <v>251646.43867462582</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16645,7 +16656,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16702,7 +16713,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16759,7 +16770,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16808,7 +16819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16857,7 +16868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16906,7 +16917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16955,7 +16966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17004,7 +17015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17053,7 +17064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17102,7 +17113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17159,7 +17170,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17216,7 +17227,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17273,7 +17284,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17322,7 +17333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17371,7 +17382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17420,7 +17431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17469,7 +17480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17518,7 +17529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17567,7 +17578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17616,7 +17627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17665,7 +17676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17714,7 +17725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17763,7 +17774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17812,7 +17823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17869,7 +17880,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17926,7 +17937,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17983,7 +17994,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18040,7 +18051,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18086,7 +18097,7 @@
         <v>2059178.5077419525</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18099,10 +18110,10 @@
         <v>3063853.1587418988</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18117,7 +18128,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>3063853.1587418988</v>
@@ -18149,7 +18160,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18176,7 +18187,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18202,7 +18213,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18228,7 +18239,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18254,7 +18265,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18280,7 +18291,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18306,7 +18317,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18332,7 +18343,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18358,7 +18369,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18384,7 +18395,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18410,7 +18421,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18445,7 +18456,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18480,7 +18491,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18515,7 +18526,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18550,7 +18561,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18571,7 +18582,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18595,7 +18606,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>-0.05</v>
@@ -18623,29 +18634,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18654,29 +18665,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.027496360970659</v>
+        <v>97.008874528318856</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.5860103524123</v>
+        <v>101.56651363493017</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.4977131507006</v>
+        <v>102.47804145625243</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.40941594898894</v>
+        <v>103.38956927757469</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.32111874727731</v>
+        <v>104.301097098897</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18685,29 +18696,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.201058934476464</v>
+        <v>93.183171484139791</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.70013544985227</v>
+        <v>101.68061682911029</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.44965420053666</v>
+        <v>103.42979980646631</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.21574076709079</v>
+        <v>105.19554741994297</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.99839514951461</v>
+        <v>106.97785966954021</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18716,29 +18727,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.81167380145132</v>
+        <v>89.794436852932236</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.80654579711567</v>
+        <v>101.78700675375379</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.34612083021906</v>
+        <v>104.32609438335768</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.93364409060017</v>
+        <v>106.9131210378596</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.56957901366795</v>
+        <v>109.54855006372441</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18747,29 +18758,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.809421236067692</v>
+        <v>86.792760489624811</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.90576290412115</v>
+        <v>101.88620481868941</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.19034581481507</v>
+        <v>105.17015734154909</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.56745424442727</v>
+        <v>108.54661762552853</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.03887447294805</v>
+        <v>112.0173716077894</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18778,29 +18789,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.106860849674092</v>
+        <v>86.090334940905407</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.16644759818358</v>
+        <v>104.14645563479323</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.19712841909363</v>
+        <v>108.17636287433164</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.37705650108572</v>
+        <v>112.35548873093239</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.71053546556548</v>
+        <v>116.68813600003608</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18809,29 +18820,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.751270136510229</v>
+        <v>83.735196320372012</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.25270412320181</v>
+        <v>104.23269560517865</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.9458258565441</v>
+        <v>108.92491661933504</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.85482815765506</v>
+        <v>113.83297676875945</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.9880067270781</v>
+        <v>118.96517016185744</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18840,30 +18851,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.398009059856292</v>
+        <v>83.382003042732762</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.35473777914457</v>
+        <v>106.33432583198599</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.73375764254006</v>
+        <v>111.71231333639578</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.40560791506458</v>
+        <v>117.38307504897017</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.38429418048759</v>
+        <v>123.3606138654814</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18872,29 +18883,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.549794265430776</v>
+        <v>81.534142963701314</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.42972674357593</v>
+        <v>106.40930040429141</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.39773686972812</v>
+        <v>112.37616513053119</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.74224367035366</v>
+        <v>118.71945427277812</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.48484287243232</v>
+        <v>125.46075941328982</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18903,30 +18914,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.447983812746301</v>
+        <v>81.43235205081001</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.38459570023933</v>
+        <v>108.36379417614707</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.98450834027045</v>
+        <v>114.96244013948026</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.05377931175693</v>
+        <v>122.03035435349139</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.62367994245946</v>
+        <v>129.59880214424626</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18935,30 +18946,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.997860110337356</v>
+        <v>79.982506660858093</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.44978896863614</v>
+        <v>108.4289749324398</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.57335557292363</v>
+        <v>115.55117435865752</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.26275847601082</v>
+        <v>123.23910148653228</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.56105007827415</v>
+        <v>131.53580045368381</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18967,30 +18978,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.515886232644689</v>
+        <v>78.500817208411661</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.63950896842435</v>
+        <v>113.61769890428779</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.26603114587525</v>
+        <v>123.24237352829526</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.0168437845663</v>
+        <v>133.99112283606121</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.02873785223147</v>
+        <v>146.00071154195214</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18999,30 +19010,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.509834170528208</v>
+        <v>77.494958231078797</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.57963804767499</v>
+        <v>116.55726370440372</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.089334024283</v>
+        <v>128.06475070272839</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.32962807786183</v>
+        <v>141.30250363601272</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.587855913759</v>
+        <v>156.55780306320122</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19031,30 +19042,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.969616925974861</v>
+        <v>77.954652743523738</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.18165774191459</v>
+        <v>120.15859208730922</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.31299231779798</v>
+        <v>133.28740645475543</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.79678163414641</v>
+        <v>148.7682240719023</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.12216898338153</v>
+        <v>167.09009435320002</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19063,30 +19074,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.112398962022837</v>
+        <v>78.09740737637901</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.21467262434928</v>
+        <v>122.19121678691594</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.53434449011516</v>
+        <v>136.50814037468729</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.78617583294809</v>
+        <v>153.75666068994298</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.6985872418378</v>
+        <v>174.66505852082432</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19095,7 +19106,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19118,7 +19129,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19133,7 +19144,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.71053546556548</v>
+        <v>116.68813600003608</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19146,7 +19157,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19161,7 +19172,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.37705650108572</v>
+        <v>112.35548873093239</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19174,7 +19185,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19189,7 +19200,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.19712841909363</v>
+        <v>108.17636287433164</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19202,7 +19213,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19217,7 +19228,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.16644759818358</v>
+        <v>104.14645563479323</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19230,7 +19241,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19245,7 +19256,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.106860849674092</v>
+        <v>86.090334940905407</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19258,7 +19269,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19271,16 +19282,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19292,7 +19303,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19304,7 +19315,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19316,7 +19327,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19328,7 +19339,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19368,14 +19379,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19385,7 +19396,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19394,7 +19405,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19415,14 +19426,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19435,7 +19446,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19448,7 +19459,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19461,7 +19472,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19474,14 +19485,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19491,7 +19502,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19504,7 +19515,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19517,7 +19528,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19530,7 +19541,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19540,7 +19551,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19548,7 +19559,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19560,18 +19571,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19592,7 +19603,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19605,7 +19616,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.37705650108572</v>
+        <v>112.35548873093239</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19616,7 +19627,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19629,7 +19640,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.19712841909363</v>
+        <v>108.17636287433164</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19639,7 +19650,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19652,7 +19663,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.16644759818358</v>
+        <v>104.14645563479323</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19662,13 +19673,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.02544383026455</v>
+        <v>108.00471123576719</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19676,12 +19687,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19702,7 +19713,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19715,7 +19726,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.71053546556548</v>
+        <v>116.68813600003608</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19725,7 +19736,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19738,7 +19749,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.106860849674092</v>
+        <v>86.090334940905407</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19748,16 +19759,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19777,13 +19788,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.25</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,16 +19805,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18798290292432629</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+        <v>0.19255135221428826</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,16 +19825,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5419268100243275E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
+        <v>6.5430719181553396E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.23227842653016</v>
+        <v>108.21150613566442</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19836,7 +19847,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19846,7 +19857,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -19855,7 +19866,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>551</v>
       </c>
@@ -19867,7 +19878,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19877,7 +19888,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19887,7 +19898,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19895,7 +19906,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19908,7 +19919,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19920,13 +19931,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.23240691095232</v>
+        <v>108.21163459542744</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19936,7 +19947,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19948,7 +19959,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19958,7 +19969,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19970,7 +19981,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19980,7 +19991,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19993,10 +20004,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736688E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="13.9">
+        <v>9.6234974214736674E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20006,12 +20017,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20021,7 +20032,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20034,13 +20045,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20061,7 +20072,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20071,11 +20082,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.876626003009299</v>
+        <v>49.867053518739375</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.550347117961422</v>
+        <v>61.540774633691498</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,10 +20094,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43131246969227577</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="13.15">
+        <v>0.43129176525333612</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20096,11 +20107,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.516839524349578</v>
+        <v>62.504841089192475</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.939543106347386</v>
+        <v>75.92754467119029</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,10 +20119,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29836510687616735</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="13.15">
+        <v>0.29834130045283569</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20132,7 +20143,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20142,11 +20153,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.576610421887295</v>
+        <v>77.561721666522558</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.968053324125506</v>
+        <v>92.953164568760769</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,10 +20165,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14103209619454016</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" ht="13.15">
+        <v>0.14100479802743271</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20167,11 +20178,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.733387513238071</v>
+        <v>87.716549436182362</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.39929651251104</v>
+        <v>104.38245843545533</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20190,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5414406586857572E-2</v>
+        <v>3.53848480346316E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20198,7 +20209,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20207,7 +20218,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20221,7 +20232,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20230,7 +20241,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20247,7 +20258,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20263,7 +20274,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20273,7 +20284,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20284,16 +20295,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20302,43 +20313,43 @@
         <v>244825280</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19157.578160000001</v>
+        <v>18949.476672000001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18798290292432629</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.19255135221428826</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20354,7 +20365,7 @@
         <v>USD/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20367,10 +20378,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8162999153137207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>7.8147997856140137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20386,14 +20397,14 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.23227842653016</v>
+        <v>108.21150613566442</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20403,7 +20414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20419,11 +20430,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20439,13 +20450,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.550347117961422</v>
+        <v>61.540774633691498</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20455,13 +20466,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.939543106347386</v>
+        <v>75.92754467119029</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20471,13 +20482,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.968053324125506</v>
+        <v>92.953164568760769</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20487,13 +20498,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.39929651251104</v>
+        <v>104.38245843545533</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20503,7 +20514,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20513,25 +20524,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20540,7 +20551,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20549,7 +20560,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20562,11 +20573,11 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20575,7 +20586,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20588,7 +20599,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20601,7 +20612,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20610,7 +20621,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20623,7 +20634,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20632,7 +20643,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20647,7 +20658,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20662,7 +20673,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20675,12 +20686,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20693,7 +20704,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20702,7 +20713,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20715,16 +20726,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20737,25 +20748,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20768,7 +20779,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20781,23 +20792,23 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11575222596768356</v>
+        <v>0.11700094723101183</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.2423772609819118E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20807,7 +20818,7 @@
         <v>5.5052997070948786</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20818,7 +20829,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20831,7 +20842,7 @@
         <v>0.11962870133363827</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20845,7 +20856,7 @@
         <v>0.25059892762124586</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20859,7 +20870,7 @@
         <v>0.26833431587768736</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20873,7 +20884,7 @@
         <v>1.7790164507082717</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20883,43 +20894,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20932,20 +20943,20 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.081678516187964</v>
+        <v>-34.075137449607624</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -20954,7 +20965,7 @@
         <v>0.29042568125650897</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -20963,12 +20974,12 @@
         <v>2.3236948196964886</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20981,7 +20992,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -20994,25 +21005,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.712862579645932</v>
+        <v>21.708695376445657</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21025,33 +21036,33 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.784546460121366</v>
+        <v>22.780173575865451</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.415730523579333</v>
+        <v>10.413731502703488</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21061,49 +21072,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21113,7 +21124,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21123,7 +21134,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21133,7 +21144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21142,97 +21153,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.225196072863366</v>
+        <v>-19.221506310709398</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.37745428932868</v>
+        <v>106.35703798234357</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21250,7 +21261,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21266,14 +21277,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.71 HKD</v>
+        <v>116.69 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21289,14 +21300,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.38 HKD</v>
+        <v>112.36 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21311,14 +21322,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.2 HKD</v>
+        <v>108.18 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21333,14 +21344,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.17 HKD</v>
+        <v>104.15 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21355,14 +21366,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.11 HKD</v>
+        <v>86.09 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21371,29 +21382,29 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.23227842653016</v>
+        <v>108.21150613566442</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21403,30 +21414,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21435,7 +21446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21448,14 +21459,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21474,7 +21485,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21484,18 +21495,18 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.876626003009299</v>
+        <v>49.867053518739375</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.550347117961422</v>
+        <v>61.540774633691498</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21505,18 +21516,18 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.516839524349578</v>
+        <v>62.504841089192475</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.939543106347386</v>
+        <v>75.92754467119029</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21535,7 +21546,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21545,18 +21556,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.576610421887295</v>
+        <v>77.561721666522558</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.968053324125506</v>
+        <v>92.953164568760769</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21566,18 +21577,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.733387513238071</v>
+        <v>87.716549436182362</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.39929651251104</v>
+        <v>104.38245843545533</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21587,50 +21598,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21639,57 +21650,60 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21718,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A5524B-5B17-8148-9E27-9F0C24BD14EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C93BC6-8D9A-4D47-832F-90C7A7AE322C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3286,27 +3275,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4058,7 +4047,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4100,17 +4089,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4119,7 +4108,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4193,10 +4182,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4207,7 +4196,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4245,7 +4234,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4255,7 +4244,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4266,19 +4255,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4286,8 +4275,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4310,29 +4299,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4349,15 +4338,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4368,11 +4357,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4433,14 +4422,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4453,7 +4442,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4490,7 +4479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4507,7 +4496,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4553,7 +4542,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4568,13 +4557,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4590,53 +4579,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4653,7 +4642,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4666,21 +4655,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4690,14 +4679,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4706,8 +4695,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4719,7 +4708,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4727,7 +4716,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4766,7 +4755,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4780,39 +4769,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4823,7 +4812,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4834,10 +4823,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4846,7 +4835,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4859,7 +4848,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4868,8 +4857,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4877,10 +4866,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4889,10 +4878,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4909,16 +4898,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4939,7 +4928,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4957,7 +4946,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4967,10 +4956,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4985,7 +4974,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4999,34 +4988,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5036,30 +5025,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5341,7 +5330,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5350,7 +5339,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5363,7 +5352,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5371,7 +5360,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5385,7 +5374,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5399,7 +5388,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5409,7 +5398,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5419,16 +5408,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>77.400000000000006</v>
+        <v>79.25</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5436,43 +5425,43 @@
         <v>244825280</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>18949.476672000001</v>
+        <v>19402.403439999998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19255135221428826</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.18288518227546327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="460" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5487,7 +5476,7 @@
         <v>USD/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5498,10 +5487,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8147997856140137</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.8223000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5515,14 +5504,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.21150613566442</v>
+        <v>108.31536157883805</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5531,7 +5520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5547,11 +5536,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5566,13 +5555,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.540774633691498</v>
+        <v>61.588634284923586</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5581,13 +5570,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.92754467119029</v>
+        <v>75.987533374828487</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5596,13 +5585,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.953164568760769</v>
+        <v>93.02760403702662</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5611,13 +5600,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.38245843545533</v>
+        <v>104.4666439480748</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5626,11 +5615,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5640,25 +5629,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="460" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="462" t="s">
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5667,16 +5656,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="461" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5689,20 +5678,20 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5715,7 +5704,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5728,16 +5717,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="461" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5750,16 +5739,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="461" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5774,7 +5763,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5789,7 +5778,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5802,12 +5791,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5820,16 +5809,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="461" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5842,8 +5831,8 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="461" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,7 +5840,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5864,25 +5853,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="460" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="460" t="s">
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5895,7 +5884,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5908,23 +5897,23 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11700094723101183</v>
+        <v>0.11437936459407808</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.2423772609819118E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5934,7 +5923,7 @@
         <v>5.5052997070948786</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5945,7 +5934,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5958,7 +5947,7 @@
         <v>0.11962870133363827</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5972,7 +5961,7 @@
         <v>0.25059892762124586</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5986,7 +5975,7 @@
         <v>0.26833431587768736</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -6000,7 +5989,7 @@
         <v>1.7790164507082717</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6010,45 +5999,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6062,21 +6051,21 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.075137449607624</v>
+        <v>-34.107840889633621</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6086,7 +6075,7 @@
         <v>0.29042568125650897</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6096,16 +6085,16 @@
         <v>2.3236948196964886</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6119,7 +6108,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6133,30 +6122,30 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.708695376445657</v>
+        <v>21.729530186527825</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6170,38 +6159,38 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.780173575865451</v>
+        <v>22.802036731705158</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.413731502703488</v>
+        <v>10.423726028599361</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6211,42 +6200,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="460" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="462" t="s">
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="462" t="s">
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6255,7 +6244,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6264,7 +6253,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6273,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6282,76 +6271,76 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="460" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="460" t="s">
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.221506310709398</v>
+        <v>-19.23995405372353</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="460" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6368,7 +6357,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (5yrs)</v>
@@ -6379,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.69 HKD</v>
+        <v>116.8 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6387,10 +6376,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1197705356523227E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+        <v>3.1144037503142475E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (5yrs)</v>
@@ -6401,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.36 HKD</v>
+        <v>112.46 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6409,10 +6398,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5023517779234419E-2</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+        <v>4.4968437350928286E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (5yrs)</v>
@@ -6423,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.18 HKD</v>
+        <v>108.28 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6431,10 +6420,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9076203655932524E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+        <v>5.9019663520227028E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (5yrs)</v>
@@ -6445,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.15 HKD</v>
+        <v>104.25 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6453,10 +6442,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3357308362837867E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.3299259891921695E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (5yrs)</v>
@@ -6467,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.09 HKD</v>
+        <v>86.17 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6475,32 +6464,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1482250636225694</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="461" t="s">
+        <v>0.14815868970338986</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.21150613566442</v>
+        <v>108.31536157883805</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6509,7 +6498,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6519,30 +6508,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="463" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="460" t="s">
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6551,7 +6540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6564,14 +6553,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6590,7 +6579,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6600,18 +6589,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.867053518739375</v>
+        <v>49.914913169971463</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.540774633691498</v>
+        <v>61.588634284923586</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6621,25 +6610,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.504841089192475</v>
+        <v>62.564829792830672</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.92754467119029</v>
+        <v>75.987533374828487</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6658,7 +6647,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6668,18 +6657,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.561721666522558</v>
+        <v>77.636161134788409</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.953164568760769</v>
+        <v>93.02760403702662</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6689,18 +6678,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.716549436182362</v>
+        <v>87.800734948801832</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.38245843545533</v>
+        <v>104.4666439480748</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6710,21 +6699,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="467" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6733,92 +6722,80 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="461" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="466" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="466" t="s">
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6835,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6862,15 +6851,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>USD</v>
@@ -6919,7 +6908,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6935,7 +6924,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6943,7 +6932,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6965,7 +6954,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6987,7 +6976,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7012,7 +7001,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7034,7 +7023,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7056,7 +7045,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7072,7 +7061,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7088,7 +7077,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7104,7 +7093,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7126,7 +7115,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7148,7 +7137,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7170,7 +7159,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7192,7 +7181,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7216,13 +7205,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7238,7 +7227,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7254,7 +7243,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7270,7 +7259,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7292,7 +7281,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7314,7 +7303,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7336,7 +7325,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7362,7 +7351,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7370,7 +7359,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7392,7 +7381,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7413,7 +7402,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7434,7 +7423,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7455,7 +7444,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7476,7 +7465,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7492,12 +7481,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7546,7 +7535,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7595,7 +7584,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7644,7 +7633,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7693,7 +7682,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7742,7 +7731,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7791,7 +7780,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7840,7 +7829,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7889,7 +7878,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7938,7 +7927,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7987,7 +7976,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8036,7 +8025,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8085,7 +8074,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8134,12 +8123,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8188,7 +8177,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8237,12 +8226,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8291,7 +8280,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8340,7 +8329,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8389,7 +8378,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8438,13 +8427,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8493,7 +8482,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8542,7 +8531,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8591,7 +8580,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8640,7 +8629,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8689,12 +8678,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8744,7 +8733,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8793,7 +8782,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8843,7 +8832,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8892,7 +8881,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8942,7 +8931,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8958,13 +8947,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9013,7 +9002,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9047,7 +9036,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9081,7 +9070,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9130,7 +9119,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9211,7 +9200,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9222,7 +9211,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9238,7 +9227,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9249,7 +9238,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9269,7 +9258,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9291,7 +9280,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9312,7 +9301,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9333,7 +9322,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9354,7 +9343,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9375,7 +9364,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9396,7 +9385,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9416,7 +9405,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9428,7 +9417,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9452,12 +9441,12 @@
         <v>1612388.4</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9477,7 +9466,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9497,7 +9486,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9517,7 +9506,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9537,7 +9526,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9557,7 +9546,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9577,7 +9566,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9597,7 +9586,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9617,7 +9606,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9629,7 +9618,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9642,7 +9631,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9666,7 +9655,7 @@
         <v>141941.1</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9683,7 +9672,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9702,7 +9691,7 @@
         <v>-549409.29999999981</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9717,7 +9706,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9736,7 +9725,7 @@
         <v>-602179.29999999981</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9752,7 +9741,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9769,7 +9758,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9789,7 +9778,7 @@
         <v>2314027.7000000002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9800,7 +9789,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9813,7 +9802,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9832,7 +9821,7 @@
         <v>559698.19999999995</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9849,7 +9838,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9865,7 +9854,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9881,7 +9870,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9900,7 +9889,7 @@
         <v>28062.2</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9920,7 +9909,7 @@
         <v>1754329.5</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9940,7 +9929,7 @@
         <v>1040662.8</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9960,7 +9949,7 @@
         <v>713666.7</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9971,7 +9960,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9985,7 +9974,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9999,25 +9988,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.64383835563413</v>
+        <v>115.75482694189098</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.221506310709398</v>
+        <v>-19.23995405372353</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10030,7 +10019,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10044,7 +10033,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10055,10 +10044,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10070,7 +10059,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10084,7 +10073,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10098,10 +10087,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10113,7 +10102,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10124,7 +10113,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10135,10 +10124,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10150,7 +10139,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10166,7 +10155,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10177,7 +10166,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10191,7 +10180,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10207,7 +10196,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10217,7 +10206,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10227,7 +10216,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10237,7 +10226,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10247,10 +10236,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10262,7 +10251,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10278,7 +10267,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10294,7 +10283,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10307,7 +10296,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10320,10 +10309,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10335,7 +10324,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10349,7 +10338,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10363,7 +10352,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10377,7 +10366,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10391,7 +10380,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10402,7 +10391,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10410,68 +10399,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8342455.0671386719</v>
+        <v>-8350461.6960000005</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.075137449607624</v>
+        <v>-34.107840889633621</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5314837.4239730136</v>
+        <v>5319938.3121851273</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.708695376445657</v>
+        <v>21.729530186527825</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5577162.3741598604</v>
+        <v>5582515.0274099996</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.780173575865451</v>
+        <v>22.802036731705158</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2549544.7309942022</v>
+        <v>2551991.6435951265</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.413731502703484</v>
+        <v>10.423726028599361</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10497,19 +10486,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10566,7 +10555,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10589,7 +10578,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10609,7 +10598,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10666,7 +10655,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10721,7 +10710,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10776,7 +10765,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10831,7 +10820,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10888,7 +10877,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -10945,7 +10934,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -11000,7 +10989,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11055,7 +11044,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11110,7 +11099,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11167,7 +11156,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11224,7 +11213,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11279,7 +11268,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11334,7 +11323,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11360,7 +11349,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11385,7 +11374,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11442,7 +11431,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11461,7 +11450,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11484,7 +11473,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11505,7 +11494,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11562,7 +11551,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11619,7 +11608,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11676,7 +11665,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11733,18 +11722,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11801,7 +11790,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11859,7 +11848,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11917,7 +11906,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11972,18 +11961,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12040,18 +12029,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12106,18 +12095,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12175,10 +12164,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12201,14 +12190,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12263,7 +12252,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12318,7 +12307,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12375,7 +12364,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12430,11 +12419,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12444,7 +12433,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12468,7 +12457,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12492,7 +12481,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12547,11 +12536,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12561,7 +12550,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12616,7 +12605,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12671,7 +12660,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12726,7 +12715,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12781,7 +12770,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12837,7 +12826,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12892,11 +12881,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12906,7 +12895,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12931,7 +12920,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12956,7 +12945,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12981,7 +12970,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -13008,10 +12997,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13034,7 +13023,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13055,7 +13044,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13112,7 +13101,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13169,7 +13158,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13226,7 +13215,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13283,7 +13272,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13340,7 +13329,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13397,7 +13386,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13454,7 +13443,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13511,7 +13500,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13569,7 +13558,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13626,7 +13615,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13683,7 +13672,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13742,7 +13731,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13768,7 +13757,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13792,7 +13781,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13849,18 +13838,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13916,7 +13905,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13972,7 +13961,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14027,7 +14016,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14048,27 +14037,27 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.2423772609819118E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2423772609819118E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.2423772609819118E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.5439276485788113E-2</v>
+        <v>8.3444794952681395E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14103,11 +14092,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14128,7 +14117,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14185,7 +14174,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14242,10 +14231,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14268,7 +14257,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14278,7 +14267,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14335,7 +14324,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14392,7 +14381,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14449,7 +14438,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14506,7 +14495,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14563,11 +14552,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14590,7 +14579,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14647,7 +14636,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14704,7 +14693,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14731,18 +14720,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14796,7 +14785,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14851,11 +14840,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14914,7 +14903,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14972,7 +14961,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15029,7 +15018,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15088,7 +15077,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15147,7 +15136,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15166,7 +15155,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15189,7 +15178,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15210,7 +15199,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15218,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.055873315680314</v>
+        <v>9.0645646440806864</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.181370127586614</v>
+        <v>10.191141645833383</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7010517400811116</v>
+        <v>7.7084427853583701</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.797885911708979</v>
+        <v>10.808249127846944</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15268,29 +15257,29 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11700094723101183</v>
+        <v>0.11437936459407808</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13154224971042136</v>
+        <v>0.12859484726603637</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.9496792507507897E-2</v>
+        <v>9.7267416849947885E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13950756991872065</v>
+        <v>0.13638169246494566</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15325,22 +15314,22 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6364831882572001E-2</v>
+        <v>1.5982813725060857E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8865692503700612E-2</v>
+        <v>1.8425294634529053E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.16156734526204E-3</v>
+        <v>5.0410764987164911E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15375,688 +15364,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16078,16 +16067,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16102,7 +16091,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16117,7 +16106,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16149,7 +16138,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16177,7 +16166,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16210,7 +16199,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16240,7 +16229,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16257,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.413731502703488</v>
+        <v>10.423726028599361</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16275,14 +16264,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*USD/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8147997856140137</v>
+        <v>7.8223000000000003</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16301,13 +16290,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26038891.603997897</v>
+        <v>26063882.297907032</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16323,13 +16312,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16339,7 +16328,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16354,7 +16343,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16372,7 +16361,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16397,7 +16386,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16413,7 +16402,7 @@
         <v>1.0085935369058155E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>550</v>
       </c>
@@ -16432,7 +16421,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16452,17 +16441,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.21163459542744</v>
+        <v>108.31549016188967</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16501,7 +16490,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16550,7 +16539,7 @@
         <v>267195.88505103323</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16599,7 +16588,7 @@
         <v>251646.43867462582</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16656,7 +16645,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16713,7 +16702,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16770,7 +16759,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16819,7 +16808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16868,7 +16857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16917,7 +16906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16966,7 +16955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17015,7 +17004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17064,7 +17053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17113,7 +17102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17170,7 +17159,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17227,7 +17216,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17284,7 +17273,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17333,7 +17322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17382,7 +17371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17431,7 +17420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17480,7 +17469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17529,7 +17518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17578,7 +17567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17627,7 +17616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17676,7 +17665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17725,7 +17714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17774,7 +17763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17823,7 +17812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17880,7 +17869,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17937,7 +17926,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17994,7 +17983,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18051,7 +18040,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18097,7 +18086,7 @@
         <v>2059178.5077419525</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18110,10 +18099,10 @@
         <v>3063853.1587418988</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18128,7 +18117,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>3063853.1587418988</v>
@@ -18160,7 +18149,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18187,7 +18176,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18213,7 +18202,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18239,7 +18228,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18265,7 +18254,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18291,7 +18280,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18317,7 +18306,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18343,7 +18332,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18369,7 +18358,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18395,7 +18384,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18421,7 +18410,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18456,7 +18445,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18491,7 +18480,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18526,7 +18515,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18561,7 +18550,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18582,7 +18571,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18606,7 +18595,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>-0.05</v>
@@ -18634,29 +18623,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18665,29 +18654,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.008874528318856</v>
+        <v>97.101978302729691</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.56651363493017</v>
+        <v>101.66399158031548</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.47804145625243</v>
+        <v>102.57639423583264</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.38956927757469</v>
+        <v>103.48879689134979</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.301097098897</v>
+        <v>104.40119954686699</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18696,29 +18685,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.183171484139791</v>
+        <v>93.272603559492993</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.68061682911029</v>
+        <v>101.77820428445644</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.42979980646631</v>
+        <v>103.5290660312871</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.19554741994297</v>
+        <v>105.29650831206374</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.97785966954021</v>
+        <v>107.08053112678633</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18727,29 +18716,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.794436852932236</v>
+        <v>89.880616607441837</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.78700675375379</v>
+        <v>101.88469631628952</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.32609438335768</v>
+        <v>104.42622082234442</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.9131210378596</v>
+        <v>107.01573036253289</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.54855006372441</v>
+        <v>109.65368872801423</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18758,29 +18747,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.792760489624811</v>
+        <v>86.876059400496729</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.88620481868941</v>
+        <v>101.98398958606393</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.17015734154909</v>
+        <v>105.27109386567113</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.54661762552853</v>
+        <v>108.65079469025179</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.0173716077894</v>
+        <v>112.12487971101166</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18789,29 +18778,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.090334940905407</v>
+        <v>86.172959702426084</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.14645563479323</v>
+        <v>104.24640966640381</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.17636287433164</v>
+        <v>108.28018458893877</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.35548873093239</v>
+        <v>112.46332134034557</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.68813600003608</v>
+        <v>116.80012684565089</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18820,29 +18809,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.735196320372012</v>
+        <v>83.815560749568462</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.23269560517865</v>
+        <v>104.3327324051626</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.92491661933504</v>
+        <v>109.0294567545954</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.83297676875945</v>
+        <v>113.94222738980957</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.96517016185744</v>
+        <v>119.0793463794391</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18851,30 +18840,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.382003042732762</v>
+        <v>83.462028496475639</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.33432583198599</v>
+        <v>106.43637966090139</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.71231333639578</v>
+        <v>111.81952866149213</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.38307504897017</v>
+        <v>117.49573285880611</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.3606138654814</v>
+        <v>123.47900858782364</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18883,29 +18872,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.534142963701314</v>
+        <v>81.612394943122609</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.40930040429141</v>
+        <v>106.51142618967164</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.37616513053119</v>
+        <v>112.48401758401381</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.71945427277812</v>
+        <v>118.83339466578376</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.46075941328982</v>
+        <v>125.58116973965039</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18914,30 +18903,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.43235205081001</v>
+        <v>81.510506336919889</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.36379417614707</v>
+        <v>108.46779577699374</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.96244013948026</v>
+        <v>115.07277475726146</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.03035435349139</v>
+        <v>122.14747236602628</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.59880214424626</v>
+        <v>129.72318393609183</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18946,30 +18935,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.982506660858093</v>
+        <v>80.059269465221846</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.4289749324398</v>
+        <v>108.53303909018612</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.55117435865752</v>
+        <v>115.66207401111411</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.23910148653228</v>
+        <v>123.35737958798624</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.53580045368381</v>
+        <v>131.66204126981467</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18978,30 +18967,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.500817208411661</v>
+        <v>78.576157968852144</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.61769890428779</v>
+        <v>113.72674291350135</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.24237352829526</v>
+        <v>123.36065477007469</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>133.99112283606121</v>
+        <v>134.11972013537263</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.00071154195214</v>
+        <v>146.14083498300138</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19010,30 +18999,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.494958231078797</v>
+        <v>77.569333623476709</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.55726370440372</v>
+        <v>116.6691289459978</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.06475070272839</v>
+        <v>128.18766019649772</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.30250363601272</v>
+        <v>141.43811799589659</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.55780306320122</v>
+        <v>156.70805861919573</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19042,30 +19031,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.954652743523738</v>
+        <v>78.029469325394189</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.15859208730922</v>
+        <v>120.27391368551984</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.28740645475543</v>
+        <v>133.4153283658456</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.7682240719023</v>
+        <v>148.91100361904</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.09009435320002</v>
+        <v>167.25045822224382</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19074,30 +19063,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.09740737637901</v>
+        <v>78.17236096628298</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.19121678691594</v>
+        <v>122.30848918635394</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.50814037468729</v>
+        <v>136.63915336879205</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.75666068994298</v>
+        <v>153.90422786377778</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.66505852082432</v>
+        <v>174.83269242323837</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19106,7 +19095,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19129,7 +19118,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19144,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.68813600003608</v>
+        <v>116.80012684565089</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19157,7 +19146,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19172,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.35548873093239</v>
+        <v>112.46332134034557</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19185,7 +19174,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19200,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.17636287433164</v>
+        <v>108.28018458893877</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19213,7 +19202,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19228,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.14645563479323</v>
+        <v>104.24640966640381</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19241,7 +19230,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19256,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.090334940905407</v>
+        <v>86.172959702426084</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19269,7 +19258,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19282,16 +19271,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19303,7 +19292,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19315,7 +19304,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19327,7 +19316,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19339,7 +19328,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19379,14 +19368,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19396,7 +19385,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19405,7 +19394,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19426,14 +19415,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19446,7 +19435,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19459,7 +19448,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19472,7 +19461,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19485,14 +19474,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19502,7 +19491,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19515,7 +19504,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19528,7 +19517,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19541,7 +19530,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19551,7 +19540,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19559,7 +19548,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19571,18 +19560,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19603,7 +19592,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19616,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.35548873093239</v>
+        <v>112.46332134034557</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19627,7 +19616,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19640,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.17636287433164</v>
+        <v>108.28018458893877</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19650,7 +19639,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19663,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.14645563479323</v>
+        <v>104.24640966640381</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19673,13 +19662,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.00471123576719</v>
+        <v>108.10836820858638</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19687,12 +19676,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19713,7 +19702,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19726,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.68813600003608</v>
+        <v>116.80012684565089</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19736,7 +19725,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19749,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.090334940905407</v>
+        <v>86.172959702426084</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19759,16 +19748,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19788,13 +19777,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>77.400000000000006</v>
+        <v>79.25</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19805,16 +19794,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19255135221428826</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.18288518227546327</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19825,16 +19814,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5430719181553396E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+        <v>6.5373511013037927E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.21150613566442</v>
+        <v>108.31536157883805</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19847,7 +19836,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19857,7 +19846,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -19866,7 +19855,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>551</v>
       </c>
@@ -19878,7 +19867,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19888,7 +19877,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19898,7 +19887,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19906,7 +19895,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19919,7 +19908,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19931,13 +19920,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.21163459542744</v>
+        <v>108.31549016188967</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19947,7 +19936,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19959,7 +19948,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19969,7 +19958,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19981,7 +19970,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19991,7 +19980,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -20004,10 +19993,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736674E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+        <v>9.6234974214736688E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20017,12 +20006,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20032,7 +20021,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20045,13 +20034,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20072,7 +20061,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20082,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.867053518739375</v>
+        <v>49.914913169971463</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.540774633691498</v>
+        <v>61.588634284923586</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20094,10 +20083,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43129176525333612</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.43139520205454984</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20107,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.504841089192475</v>
+        <v>62.564829792830672</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.92754467119029</v>
+        <v>75.987533374828487</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20119,10 +20108,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29834130045283569</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+        <v>0.29846023438217062</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20143,7 +20132,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20153,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.561721666522558</v>
+        <v>77.636161134788409</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.953164568760769</v>
+        <v>93.02760403702662</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20165,10 +20154,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14100479802743271</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.14114117627428258</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20178,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.716549436182362</v>
+        <v>87.800734948801832</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.38245843545533</v>
+        <v>104.4666439480748</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20190,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.53848480346316E-2</v>
+        <v>3.5532518884331399E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20209,7 +20198,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20218,7 +20207,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20232,7 +20221,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20241,7 +20230,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20258,7 +20247,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20274,7 +20263,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20284,7 +20273,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20295,16 +20284,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>77.400000000000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>79.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20313,43 +20302,43 @@
         <v>244825280</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>18949.476672000001</v>
+        <v>19402.403439999998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19255135221428826</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.18288518227546327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="471" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20365,7 +20354,7 @@
         <v>USD/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20378,10 +20367,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8147997856140137</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>7.8223000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20397,14 +20386,14 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.21150613566442</v>
+        <v>108.31536157883805</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20414,7 +20403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20430,11 +20419,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20450,13 +20439,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.540774633691498</v>
+        <v>61.588634284923586</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20466,13 +20455,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.92754467119029</v>
+        <v>75.987533374828487</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20482,13 +20471,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.953164568760769</v>
+        <v>93.02760403702662</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20498,13 +20487,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.38245843545533</v>
+        <v>104.4666439480748</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,7 +20503,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20524,25 +20513,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="471" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="472" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20551,7 +20540,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20560,7 +20549,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20573,11 +20562,11 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20586,7 +20575,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20599,7 +20588,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20612,7 +20601,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20621,7 +20610,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20634,7 +20623,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20643,7 +20632,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20658,7 +20647,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20673,7 +20662,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20686,12 +20675,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20704,7 +20693,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20713,7 +20702,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20726,16 +20715,16 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20748,25 +20737,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="471" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="471" t="s">
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20779,7 +20768,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20792,23 +20781,23 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11700094723101183</v>
+        <v>0.11437936459407808</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.2423772609819118E-2</v>
+        <v>8.0499684542586755E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20818,7 +20807,7 @@
         <v>5.5052997070948786</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20829,7 +20818,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20842,7 +20831,7 @@
         <v>0.11962870133363827</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20856,7 +20845,7 @@
         <v>0.25059892762124586</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20870,7 +20859,7 @@
         <v>0.26833431587768736</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20884,7 +20873,7 @@
         <v>1.7790164507082717</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20894,43 +20883,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="472" t="s">
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="471" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20943,20 +20932,20 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.075137449607624</v>
+        <v>-34.107840889633621</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -20965,7 +20954,7 @@
         <v>0.29042568125650897</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -20974,12 +20963,12 @@
         <v>2.3236948196964886</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20992,7 +20981,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -21005,25 +20994,25 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.708695376445657</v>
+        <v>21.729530186527825</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21036,33 +21025,33 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.780173575865451</v>
+        <v>22.802036731705158</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.413731502703488</v>
+        <v>10.423726028599361</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21072,49 +21061,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21124,7 +21113,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21134,7 +21123,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21144,7 +21133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21153,97 +21142,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.221506310709398</v>
+        <v>-19.23995405372353</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.35703798234357</v>
+        <v>106.45911360912987</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21261,7 +21250,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21277,14 +21266,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.69 HKD</v>
+        <v>116.8 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21300,14 +21289,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.36 HKD</v>
+        <v>112.46 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21322,14 +21311,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.18 HKD</v>
+        <v>108.28 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21344,14 +21333,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.15 HKD</v>
+        <v>104.25 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21366,14 +21355,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.09 HKD</v>
+        <v>86.17 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21382,29 +21371,29 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.21150613566442</v>
+        <v>108.31536157883805</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="475" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21414,30 +21403,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="476" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="471" t="s">
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21446,7 +21435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21459,14 +21448,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21485,7 +21474,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21495,18 +21484,18 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.867053518739375</v>
+        <v>49.914913169971463</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.540774633691498</v>
+        <v>61.588634284923586</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21516,18 +21505,18 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.504841089192475</v>
+        <v>62.564829792830672</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.92754467119029</v>
+        <v>75.987533374828487</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21546,7 +21535,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21556,18 +21545,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.561721666522558</v>
+        <v>77.636161134788409</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.953164568760769</v>
+        <v>93.02760403702662</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21577,18 +21566,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.716549436182362</v>
+        <v>87.800734948801832</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.38245843545533</v>
+        <v>104.4666439480748</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21598,50 +21587,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="477" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="473" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21650,60 +21639,57 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="474" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="474" t="s">
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21718,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C93BC6-8D9A-4D47-832F-90C7A7AE322C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D793F6BD-25B9-4086-9B13-D7A444D01A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>79.25</v>
+        <v>77.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19402.403439999998</v>
+        <v>18900.511616</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18288518227546327</v>
+        <v>0.19403843148385216</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8223000000000003</v>
+        <v>7.8234000205993652</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.31536157883805</v>
+        <v>108.33059356034788</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.588634284923586</v>
+        <v>61.595653631241476</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.987533374828487</v>
+        <v>75.996331631296258</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.02760403702662</v>
+        <v>93.038521718080005</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.4666439480748</v>
+        <v>104.47899103487575</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11437936459407808</v>
+        <v>0.11743315232746157</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.0499684542586755E-2</v>
+        <v>8.2637305699481856E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.107840889633621</v>
+        <v>-34.112637346887681</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.729530186527825</v>
+        <v>21.732585928549955</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.802036731705158</v>
+        <v>22.805243296284932</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.423726028599361</v>
+        <v>10.425191877947199</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.23995405372353</v>
+        <v>-19.242659696026937</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.8 HKD</v>
+        <v>116.82 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1144037503142475E-2</v>
+        <v>3.1136174940733858E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.46 HKD</v>
+        <v>112.48 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4968437350928286E-2</v>
+        <v>4.4960367844334118E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.28 HKD</v>
+        <v>108.3 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9019663520227028E-2</v>
+        <v>5.9011380165565099E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.25 HKD</v>
+        <v>104.26 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3299259891921695E-2</v>
+        <v>7.3290755563529056E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.17 HKD</v>
+        <v>86.19 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14815868970338986</v>
+        <v>0.14814896569079619</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.31536157883805</v>
+        <v>108.33059356034788</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.914913169971463</v>
+        <v>49.92193251628936</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.588634284923586</v>
+        <v>61.595653631241476</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.564829792830672</v>
+        <v>62.573628049298442</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.987533374828487</v>
+        <v>75.996331631296258</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.636161134788409</v>
+        <v>77.647078815841795</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.02760403702662</v>
+        <v>93.038521718080005</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.800734948801832</v>
+        <v>87.813082035602775</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.4666439480748</v>
+        <v>104.47899103487575</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.75482694189098</v>
+        <v>115.7711051074065</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.23995405372353</v>
+        <v>-19.242659696026937</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8350461.6960000005</v>
+        <v>-8351635.9899902344</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.107840889633621</v>
+        <v>-34.112637346887681</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5319938.3121851273</v>
+        <v>5320686.4350813022</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.729530186527825</v>
+        <v>21.732585928549955</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5582515.0274099996</v>
+        <v>5583300.0754810805</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.802036731705158</v>
+        <v>22.805243296284928</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2551991.6435951265</v>
+        <v>2552350.5205721483</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.423726028599361</v>
+        <v>10.425191877947203</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.0499684542586755E-2</v>
+        <v>8.2637305699481856E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.0499684542586755E-2</v>
+        <v>8.2637305699481856E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.0499684542586755E-2</v>
+        <v>8.2637305699481856E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.3444794952681395E-2</v>
+        <v>8.5660621761658035E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0645646440806864</v>
+        <v>9.0658393596800337</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.191141645833383</v>
+        <v>10.192574787715115</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7084427853583701</v>
+        <v>7.7095267946462931</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.808249127846944</v>
+        <v>10.809769051230566</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11437936459407808</v>
+        <v>0.11743315232746157</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.12859484726603637</v>
+        <v>0.13202817082532531</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.7267416849947885E-2</v>
+        <v>9.9864336718216234E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13638169246494566</v>
+        <v>0.14002291517138038</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5982813725060857E-2</v>
+        <v>1.640722782009162E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8425294634529053E-2</v>
+        <v>1.8914567354746468E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0410764987164911E-3</v>
+        <v>5.1749392813896624E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.423726028599361</v>
+        <v>10.425191877947199</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8223000000000003</v>
+        <v>7.8234000205993652</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26063882.297907032</v>
+        <v>26067547.563548483</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.31549016188967</v>
+        <v>108.33072216148165</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.101978302729691</v>
+        <v>97.115633388365893</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.66399158031548</v>
+        <v>101.6782882047037</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.57639423583264</v>
+        <v>102.59081916797126</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.48879689134979</v>
+        <v>103.50335013123882</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.40119954686699</v>
+        <v>104.41588109450643</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.272603559492993</v>
+        <v>93.285720134575996</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.77820428445644</v>
+        <v>101.79251697014725</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.5290660312871</v>
+        <v>103.54362493407368</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.29650831206374</v>
+        <v>105.31131576360414</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.08053112678633</v>
+        <v>107.09558945873862</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.880616607441837</v>
+        <v>89.893256180170042</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.88469631628952</v>
+        <v>101.89902397755385</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.42622082234442</v>
+        <v>104.44090588863162</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.01573036253289</v>
+        <v>107.03077958179766</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.65368872801423</v>
+        <v>109.66910891343248</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.876059400496729</v>
+        <v>86.888276453656559</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.98398958606393</v>
+        <v>101.99833121056696</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.27109386567113</v>
+        <v>105.28589774327362</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.65079469025179</v>
+        <v>108.66607384245722</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.12487971101166</v>
+        <v>112.14064741071424</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.172959702426084</v>
+        <v>86.185077881322428</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.24640966640381</v>
+        <v>104.26106944652511</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.28018458893877</v>
+        <v>108.29541162364094</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.46332134034557</v>
+        <v>112.4791366338203</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.80012684565089</v>
+        <v>116.8165520077565</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.815560749568462</v>
+        <v>83.827347416325281</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.3327324051626</v>
+        <v>104.34740432452567</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.0294567545954</v>
+        <v>109.04478915662135</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.94222738980957</v>
+        <v>113.9582506562742</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.0793463794391</v>
+        <v>119.09609205960686</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.462028496475639</v>
+        <v>83.473765447322691</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.43637966090139</v>
+        <v>106.45134740825816</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.81952866149213</v>
+        <v>111.83525342082621</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.49573285880611</v>
+        <v>117.5122558413665</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.47900858782364</v>
+        <v>123.49637297592379</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.612394943122609</v>
+        <v>81.623871786966617</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.51142618967164</v>
+        <v>106.52640449053921</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.48401758401381</v>
+        <v>112.49983578792337</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.83339466578376</v>
+        <v>118.85010575868799</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.58116973965039</v>
+        <v>125.59882974675904</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.510506336919889</v>
+        <v>81.521968852552789</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.46779577699374</v>
+        <v>108.48304919475098</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.07277475726146</v>
+        <v>115.08895700834606</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.14747236602628</v>
+        <v>122.16464950520056</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.72318393609183</v>
+        <v>129.74142641906295</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.059269465221846</v>
+        <v>80.070527898877145</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.53303909018612</v>
+        <v>108.54830168286486</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.66207401111411</v>
+        <v>115.67833913313417</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.35737958798624</v>
+        <v>123.37472687185806</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.66204126981467</v>
+        <v>131.68055640699313</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.576157968852144</v>
+        <v>78.587207838121373</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.72674291350135</v>
+        <v>113.74273587719534</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.36065477007469</v>
+        <v>123.37800251452303</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.11972013537263</v>
+        <v>134.13858088667723</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.14083498300138</v>
+        <v>146.16138621842956</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.569333623476709</v>
+        <v>77.580241906828775</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.6691289459978</v>
+        <v>116.68553568636196</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.18766019649772</v>
+        <v>128.20568674454631</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.43811799589659</v>
+        <v>141.45800790593981</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.70805861919573</v>
+        <v>156.73009588350004</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.029469325394189</v>
+        <v>78.040442315897678</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.27391368551984</v>
+        <v>120.29082735319052</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.4153283658456</v>
+        <v>133.43409006118756</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.91100361904</v>
+        <v>148.93194441285422</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.25045822224382</v>
+        <v>167.27397802451398</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.17236096628298</v>
+        <v>78.183354051099968</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.30848918635394</v>
+        <v>122.32568896871746</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.63915336879205</v>
+        <v>136.65836841850702</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.90422786377778</v>
+        <v>153.92587083591891</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.83269242323837</v>
+        <v>174.85727848655836</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.80012684565089</v>
+        <v>116.8165520077565</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.46332134034557</v>
+        <v>112.4791366338203</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.28018458893877</v>
+        <v>108.29541162364094</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.24640966640381</v>
+        <v>104.26106944652511</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.172959702426084</v>
+        <v>86.185077881322428</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.46332134034557</v>
+        <v>112.4791366338203</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.28018458893877</v>
+        <v>108.29541162364094</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.24640966640381</v>
+        <v>104.26106944652511</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.10836820858638</v>
+        <v>108.12357108139786</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.80012684565089</v>
+        <v>116.8165520077565</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.172959702426084</v>
+        <v>86.185077881322428</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>79.25</v>
+        <v>77.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18288518227546327</v>
+        <v>0.19403843148385216</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5373511013037927E-2</v>
+        <v>6.5365129789877394E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.31536157883805</v>
+        <v>108.33059356034788</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.31549016188967</v>
+        <v>108.33072216148165</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736688E-2</v>
+        <v>9.6234974214736729E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.914913169971463</v>
+        <v>49.92193251628936</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.588634284923586</v>
+        <v>61.595653631241476</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43139520205454984</v>
+        <v>0.43141035595887978</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.564829792830672</v>
+        <v>62.573628049298442</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.987533374828487</v>
+        <v>75.996331631296258</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29846023438217062</v>
+        <v>0.29847765867763965</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.636161134788409</v>
+        <v>77.647078815841795</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.02760403702662</v>
+        <v>93.038521718080005</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14114117627428258</v>
+        <v>0.14116115623191061</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.800734948801832</v>
+        <v>87.813082035602775</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.4666439480748</v>
+        <v>104.47899103487575</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5532518884331399E-2</v>
+        <v>3.5554153253360643E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>79.25</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19402.403439999998</v>
+        <v>18900.511616</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18288518227546327</v>
+        <v>0.19403843148385216</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8223000000000003</v>
+        <v>7.8234000205993652</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.31536157883805</v>
+        <v>108.33059356034788</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.588634284923586</v>
+        <v>61.595653631241476</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.987533374828487</v>
+        <v>75.996331631296258</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.02760403702662</v>
+        <v>93.038521718080005</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.4666439480748</v>
+        <v>104.47899103487575</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11437936459407808</v>
+        <v>0.11743315232746157</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.0499684542586755E-2</v>
+        <v>8.2637305699481856E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.107840889633621</v>
+        <v>-34.112637346887681</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.729530186527825</v>
+        <v>21.732585928549955</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.802036731705158</v>
+        <v>22.805243296284932</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.423726028599361</v>
+        <v>10.425191877947199</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.23995405372353</v>
+        <v>-19.242659696026937</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.45911360912987</v>
+        <v>106.4740845534762</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.8 HKD</v>
+        <v>116.82 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.46 HKD</v>
+        <v>112.48 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.28 HKD</v>
+        <v>108.3 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.25 HKD</v>
+        <v>104.26 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.17 HKD</v>
+        <v>86.19 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.31536157883805</v>
+        <v>108.33059356034788</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.914913169971463</v>
+        <v>49.92193251628936</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.588634284923586</v>
+        <v>61.595653631241476</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.564829792830672</v>
+        <v>62.573628049298442</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.987533374828487</v>
+        <v>75.996331631296258</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.636161134788409</v>
+        <v>77.647078815841795</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.02760403702662</v>
+        <v>93.038521718080005</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.800734948801832</v>
+        <v>87.813082035602775</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.4666439480748</v>
+        <v>104.47899103487575</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,12 +21684,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21707,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D793F6BD-25B9-4086-9B13-D7A444D01A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445E309E-9220-4136-81F1-216194BEDA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>77.2</v>
+        <v>74.45</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>18900.511616</v>
+        <v>18227.242096000002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19403843148385216</v>
+        <v>0.20915224820505735</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8234000205993652</v>
+        <v>7.8136000633239746</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.33059356034788</v>
+        <v>108.19489358518186</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.595653631241476</v>
+        <v>61.533119080473725</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.996331631296258</v>
+        <v>75.917948974160637</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.038521718080005</v>
+        <v>92.9412573505479</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.47899103487575</v>
+        <v>104.36899225558497</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11743315232746157</v>
+        <v>0.12161830845800888</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.2637305699481856E-2</v>
+        <v>8.5689724647414367E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.112637346887681</v>
+        <v>-34.069906259678774</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.732585928549955</v>
+        <v>21.705362673568391</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.805243296284932</v>
+        <v>22.776676380446546</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.425191877947199</v>
+        <v>10.412132794336157</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.242659696026937</v>
+        <v>-19.218555439260133</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.82 HKD</v>
+        <v>116.67 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1136174940733858E-2</v>
+        <v>3.1206299530444678E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.48 HKD</v>
+        <v>112.34 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4960367844334118E-2</v>
+        <v>4.5032338162035425E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.3 HKD</v>
+        <v>108.16 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9011380165565099E-2</v>
+        <v>5.9085257794573916E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.26 HKD</v>
+        <v>104.13 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3290755563529056E-2</v>
+        <v>7.336660404677553E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.19 HKD</v>
+        <v>86.08 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14814896569079619</v>
+        <v>0.1482356925447687</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.33059356034788</v>
+        <v>108.19489358518186</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.92193251628936</v>
+        <v>49.859397965521609</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.595653631241476</v>
+        <v>61.533119080473725</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.573628049298442</v>
+        <v>62.495245392162829</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.996331631296258</v>
+        <v>75.917948974160637</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.647078815841795</v>
+        <v>77.549814448309689</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.038521718080005</v>
+        <v>92.9412573505479</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.813082035602775</v>
+        <v>87.703083256311999</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.47899103487575</v>
+        <v>104.36899225558497</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.7711051074065</v>
+        <v>115.62608479899966</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.242659696026937</v>
+        <v>-19.218555439260133</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8351635.9899902344</v>
+        <v>-8341174.3395996094</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.112637346887681</v>
+        <v>-34.069906259678774</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5320686.4350813022</v>
+        <v>5314021.4940579301</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.732585928549955</v>
+        <v>21.705362673568391</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5583300.0754810805</v>
+        <v>5576306.1723122112</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.805243296284928</v>
+        <v>22.776676380446542</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2552350.5205721483</v>
+        <v>2549153.3267705319</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.425191877947203</v>
+        <v>10.412132794336159</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.2637305699481856E-2</v>
+        <v>8.5689724647414367E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2637305699481856E-2</v>
+        <v>8.5689724647414367E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.2637305699481856E-2</v>
+        <v>8.5689724647414367E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.5660621761658035E-2</v>
+        <v>8.8824714573539285E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0658393596800337</v>
+        <v>9.0544830646987613</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.192574787715115</v>
+        <v>10.179807091165939</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7095267946462931</v>
+        <v>7.6998694803069929</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.809769051230566</v>
+        <v>10.796228228240565</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11743315232746157</v>
+        <v>0.12161830845800888</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13202817082532531</v>
+        <v>0.1367334733534713</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.9864336718216234E-2</v>
+        <v>0.10342336440976485</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.14002291517138038</v>
+        <v>0.14501313939879873</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.640722782009162E-2</v>
+        <v>1.7013270486381103E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8914567354746468E-2</v>
+        <v>1.9613224980341536E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1749392813896624E-3</v>
+        <v>5.3660888183113759E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.425191877947199</v>
+        <v>10.412132794336157</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8234000205993652</v>
+        <v>7.8136000633239746</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26067547.563548483</v>
+        <v>26034894.132594634</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.33072216148165</v>
+        <v>108.19502202522382</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.115633388365893</v>
+        <v>96.993981797564899</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.6782882047037</v>
+        <v>101.55092121878745</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.59081916797126</v>
+        <v>102.46230910303194</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.50335013123882</v>
+        <v>103.37369698727646</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.41588109450643</v>
+        <v>104.28508487152101</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.285720134575996</v>
+        <v>93.168866072490999</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.79251697014725</v>
+        <v>101.66500689592948</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.54362493407368</v>
+        <v>103.41392134000701</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.31131576360414</v>
+        <v>105.17939787721446</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.09558945873862</v>
+        <v>106.9614365075518</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.893256180170042</v>
+        <v>89.780651677320662</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.89902397755385</v>
+        <v>101.77138048767034</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.44090588863162</v>
+        <v>104.31007831841704</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.03077958179766</v>
+        <v>106.89670781449809</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.66910891343248</v>
+        <v>109.53173225124573</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.888276453656559</v>
+        <v>86.779436129151094</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.99833121056696</v>
+        <v>101.87056332379233</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.28589774327362</v>
+        <v>105.15401169668665</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.66607384245722</v>
+        <v>108.52995362897759</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.14064741071424</v>
+        <v>112.00017478365106</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.185077881322428</v>
+        <v>86.077118416283028</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.26106944652511</v>
+        <v>104.13046714786057</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.29541162364094</v>
+        <v>108.1597557190166</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.4791366338203</v>
+        <v>112.3382399993031</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.8165520077565</v>
+        <v>116.67022212359869</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.827347416325281</v>
+        <v>83.72234135489083</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.34740432452567</v>
+        <v>104.21669387874944</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.04478915662135</v>
+        <v>108.90819454660203</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.9582506562742</v>
+        <v>113.81550121425805</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.09609205960686</v>
+        <v>118.94690671681767</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.473765447322691</v>
+        <v>83.369202299222664</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.45134740825816</v>
+        <v>106.31800146483691</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.83525342082621</v>
+        <v>111.69516334457792</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.5122558413665</v>
+        <v>117.36505448600337</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.49637297592379</v>
+        <v>123.34167563517128</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.623871786966617</v>
+        <v>81.521625902305473</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.52640449053921</v>
+        <v>106.39296452710138</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.49983578792337</v>
+        <v>112.3589132246763</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.85010575868799</v>
+        <v>118.70122854986012</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.59882974675904</v>
+        <v>125.44149877018666</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.521968852552789</v>
+        <v>81.419850616279916</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.48304919475098</v>
+        <v>108.34715824651703</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.08895700834606</v>
+        <v>114.94479119059656</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.16464950520056</v>
+        <v>122.01162034363887</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.74142641906295</v>
+        <v>129.57890623187996</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.070527898877145</v>
+        <v>79.970227805521219</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.54830168286486</v>
+        <v>108.4123289963082</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.67833913313417</v>
+        <v>115.53343502773141</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.37472687185806</v>
+        <v>123.22018191071282</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.68055640699313</v>
+        <v>131.51560717476798</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.587207838121373</v>
+        <v>78.488765820944948</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.74273587719534</v>
+        <v>113.60025639908511</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.37800251452303</v>
+        <v>123.22345345015437</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.13858088667723</v>
+        <v>133.97055261786704</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.16138621842956</v>
+        <v>145.97829762057174</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.580241906828775</v>
+        <v>77.48306126233922</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.68553568636196</v>
+        <v>116.53936991938448</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.20568674454631</v>
+        <v>128.04509029680614</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.45800790593981</v>
+        <v>141.28081098003929</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.73009588350004</v>
+        <v>156.53376842492935</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.040442315897678</v>
+        <v>77.942685202822204</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.29082735319052</v>
+        <v>120.14014542901705</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.43409006118756</v>
+        <v>133.26694427058027</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.93194441285422</v>
+        <v>148.74538528404273</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.27397802451398</v>
+        <v>167.06444280534984</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.183354051099968</v>
+        <v>78.0854179200917</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.32568896871746</v>
+        <v>122.17245808158147</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.65836841850702</v>
+        <v>136.48718374582</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.92587083591891</v>
+        <v>153.73305608097894</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.85727848655836</v>
+        <v>174.63824407007098</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.8165520077565</v>
+        <v>116.67022212359869</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.4791366338203</v>
+        <v>112.3382399993031</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.29541162364094</v>
+        <v>108.1597557190166</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.26106944652511</v>
+        <v>104.13046714786057</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.185077881322428</v>
+        <v>86.077118416283028</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.4791366338203</v>
+        <v>112.3382399993031</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.29541162364094</v>
+        <v>108.1597557190166</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.26106944652511</v>
+        <v>104.13046714786057</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.12357108139786</v>
+        <v>107.98813043228489</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.8165520077565</v>
+        <v>116.67022212359869</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.185077881322428</v>
+        <v>86.077118416283028</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>77.2</v>
+        <v>74.45</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19403843148385216</v>
+        <v>0.20915224820505735</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5365129789877394E-2</v>
+        <v>6.5439880299721739E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.33059356034788</v>
+        <v>108.19489358518186</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.33072216148165</v>
+        <v>108.19502202522382</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736729E-2</v>
+        <v>9.6234974214736715E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.92193251628936</v>
+        <v>49.859397965521609</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.595653631241476</v>
+        <v>61.533119080473725</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43141035595887978</v>
+        <v>0.43127520124571606</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.573628049298442</v>
+        <v>62.495245392162829</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.996331631296258</v>
+        <v>75.917948974160637</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29847765867763965</v>
+        <v>0.29832225478931296</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.647078815841795</v>
+        <v>77.549814448309689</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.038521718080005</v>
+        <v>92.9412573505479</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14116115623191061</v>
+        <v>0.14098295889190715</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.813082035602775</v>
+        <v>87.703083256311999</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.47899103487575</v>
+        <v>104.36899225558497</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5554153253360643E-2</v>
+        <v>3.5361200541176752E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>77.2</v>
+        <v>74.45</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>18900.511616</v>
+        <v>18227.242096000002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19403843148385216</v>
+        <v>0.20915224820505735</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8234000205993652</v>
+        <v>7.8136000633239746</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.33059356034788</v>
+        <v>108.19489358518186</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.595653631241476</v>
+        <v>61.533119080473725</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.996331631296258</v>
+        <v>75.917948974160637</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.038521718080005</v>
+        <v>92.9412573505479</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.47899103487575</v>
+        <v>104.36899225558497</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11743315232746157</v>
+        <v>0.12161830845800888</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.2637305699481856E-2</v>
+        <v>8.5689724647414367E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.112637346887681</v>
+        <v>-34.069906259678774</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.732585928549955</v>
+        <v>21.705362673568391</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.805243296284932</v>
+        <v>22.776676380446546</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.425191877947199</v>
+        <v>10.412132794336157</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.242659696026937</v>
+        <v>-19.218555439260133</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.4740845534762</v>
+        <v>106.34071012844194</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.82 HKD</v>
+        <v>116.67 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.48 HKD</v>
+        <v>112.34 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.3 HKD</v>
+        <v>108.16 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.26 HKD</v>
+        <v>104.13 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.19 HKD</v>
+        <v>86.08 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.33059356034788</v>
+        <v>108.19489358518186</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.92193251628936</v>
+        <v>49.859397965521609</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.595653631241476</v>
+        <v>61.533119080473725</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.573628049298442</v>
+        <v>62.495245392162829</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.996331631296258</v>
+        <v>75.917948974160637</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.647078815841795</v>
+        <v>77.549814448309689</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.038521718080005</v>
+        <v>92.9412573505479</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.813082035602775</v>
+        <v>87.703083256311999</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.47899103487575</v>
+        <v>104.36899225558497</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,15 +21684,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21707,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445E309E-9220-4136-81F1-216194BEDA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A09F24-0E90-422F-9674-D6F83C0C18F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>74.45</v>
+        <v>78.25</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>18227.242096000002</v>
+        <v>19157.578160000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20915224820505735</v>
+        <v>0.18846101742319771</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8136000633239746</v>
+        <v>7.8270001411437988</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.19489358518186</v>
+        <v>108.38044441732059</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.533119080473725</v>
+        <v>61.618626376390196</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>75.917948974160637</v>
+        <v>76.025126350125248</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>92.9412573505479</v>
+        <v>93.074252837915878</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.36899225558497</v>
+        <v>104.51940027892232</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.12161830845800888</v>
+        <v>0.11591068648885185</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.5689724647414367E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.069906259678774</v>
+        <v>-34.128335075012792</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.705362673568391</v>
+        <v>21.742586686389135</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.776676380446546</v>
+        <v>22.815737662506212</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.412132794336157</v>
+        <v>10.429989273882551</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.218555439260133</v>
+        <v>-19.251514656059506</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.67 HKD</v>
+        <v>116.87 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1206299530444678E-2</v>
+        <v>3.1110457977341362E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.34 HKD</v>
+        <v>112.53 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.5032338162035425E-2</v>
+        <v>4.4933974012347139E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.16 HKD</v>
+        <v>108.35 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9085257794573916E-2</v>
+        <v>5.8984286884237284E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.13 HKD</v>
+        <v>104.31 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.336660404677553E-2</v>
+        <v>7.3262939526748519E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.08 HKD</v>
+        <v>86.22 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1482356925447687</v>
+        <v>0.14811716034698766</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.19489358518186</v>
+        <v>108.38044441732059</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.859397965521609</v>
+        <v>49.944905261438073</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.533119080473725</v>
+        <v>61.618626376390196</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.495245392162829</v>
+        <v>62.60242276812744</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>75.917948974160637</v>
+        <v>76.025126350125248</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.549814448309689</v>
+        <v>77.682809935677668</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>92.9412573505479</v>
+        <v>93.074252837915878</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.703083256311999</v>
+        <v>87.853491279649347</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.36899225558497</v>
+        <v>104.51940027892232</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.62608479899966</v>
+        <v>115.82437988983504</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.218555439260133</v>
+        <v>-19.251514656059506</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8341174.3395996094</v>
+        <v>-8355479.1906738281</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.069906259678774</v>
+        <v>-34.128335075012792</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5314021.4940579301</v>
+        <v>5323134.8734194916</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.705362673568391</v>
+        <v>21.742586686389135</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5576306.1723122112</v>
+        <v>5585869.3616296286</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.776676380446542</v>
+        <v>22.815737662506208</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2549153.3267705319</v>
+        <v>2553525.044375292</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.412132794336159</v>
+        <v>10.429989273882551</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.5689724647414367E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.5689724647414367E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.5689724647414367E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.8824714573539285E-2</v>
+        <v>8.4511182108626209E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0544830646987613</v>
+        <v>9.0700112177526595</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.179807091165939</v>
+        <v>10.197265139454423</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.6998694803069929</v>
+        <v>7.7130745137617911</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.796228228240565</v>
+        <v>10.814743419349215</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.12161830845800888</v>
+        <v>0.11591068648885185</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.1367334733534713</v>
+        <v>0.13031648740516835</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10342336440976485</v>
+        <v>9.8569642348393494E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.14501313939879873</v>
+        <v>0.13820758363385577</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7013270486381103E-2</v>
+        <v>1.6187066935604767E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9613224980341536E-2</v>
+        <v>1.8660761658612489E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3660888183113759E-3</v>
+        <v>5.1054992015754875E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.412132794336157</v>
+        <v>10.429989273882551</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8136000633239746</v>
+        <v>7.8270001411437988</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26034894.132594634</v>
+        <v>26079543.155398503</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.19502202522382</v>
+        <v>108.3805730776332</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>96.993981797564899</v>
+        <v>97.160323419046492</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.55092121878745</v>
+        <v>101.72507784773931</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.46230910303194</v>
+        <v>102.63802873347787</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.37369698727646</v>
+        <v>103.55097961921643</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.28508487152101</v>
+        <v>104.46393050495504</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.168866072490999</v>
+        <v>93.328647741073752</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.66500689592948</v>
+        <v>101.83935917822161</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.41392134000701</v>
+        <v>103.59127295544401</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.17939787721446</v>
+        <v>105.35977722926403</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>106.9614365075518</v>
+        <v>107.14487199968161</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.780651677320662</v>
+        <v>89.93462266501399</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.77138048767034</v>
+        <v>101.94591519731935</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.31007831841704</v>
+        <v>104.48896681482469</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>106.89670781449809</v>
+        <v>107.08003229895959</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.53173225124573</v>
+        <v>109.7195757195589</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.779436129151094</v>
+        <v>86.928260126779193</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>101.87056332379233</v>
+        <v>102.04526812887899</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.15401169668665</v>
+        <v>105.33434751223682</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.52995362897759</v>
+        <v>108.71607907853017</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.00017478365106</v>
+        <v>112.19225155310072</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.077118416283028</v>
+        <v>86.224737961170987</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.13046714786057</v>
+        <v>104.30904761677215</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.1597557190166</v>
+        <v>108.34524629082243</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.3382399993031</v>
+        <v>112.53089653994159</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.67022212359869</v>
+        <v>116.87030787703401</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.72234135489083</v>
+        <v>83.865922531342306</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.21669387874944</v>
+        <v>104.39542222378658</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>108.90819454660203</v>
+        <v>109.09496866740599</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>113.81550121425805</v>
+        <v>114.01069121131616</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>118.94690671681767</v>
+        <v>119.15089691256806</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.369202299222664</v>
+        <v>83.5121778533248</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.31800146483691</v>
+        <v>106.50033348614987</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.69516334457792</v>
+        <v>111.88671702902369</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.36505448600337</v>
+        <v>117.56633185503873</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.34167563517128</v>
+        <v>123.55320272109124</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.521625902305473</v>
+        <v>81.661432921123478</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.39296452710138</v>
+        <v>106.57542510770325</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.3589132246763</v>
+        <v>112.55160521924468</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.70122854986012</v>
+        <v>118.90479741529808</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.44149877018666</v>
+        <v>125.65662698659563</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.419850616279916</v>
+        <v>81.559483093690403</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.34715824651703</v>
+        <v>108.53297020775049</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>114.94479119059656</v>
+        <v>115.14191788436827</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.01162034363887</v>
+        <v>122.22086642665788</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.57890623187996</v>
+        <v>129.80112997167248</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>79.970227805521219</v>
+        <v>80.107374225504117</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.4123289963082</v>
+        <v>108.59825272332334</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.53343502773141</v>
+        <v>115.73157122712944</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.22018191071282</v>
+        <v>123.43150063872486</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.51560717476798</v>
+        <v>131.74115229563171</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.488765820944948</v>
+        <v>78.623371580320764</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.60025639908511</v>
+        <v>113.79507725806982</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.22345345015437</v>
+        <v>123.43477778875344</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>133.97055261786704</v>
+        <v>134.20030789278451</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>145.97829762057174</v>
+        <v>146.22864579967842</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.48306126233922</v>
+        <v>77.615942270097364</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.53936991938448</v>
+        <v>116.73923126541411</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.04509029680614</v>
+        <v>128.26468359061667</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.28081098003929</v>
+        <v>141.52310311762474</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.53376842492935</v>
+        <v>156.80221890375154</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>77.942685202822204</v>
+        <v>78.076354451150678</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.14014542901705</v>
+        <v>120.34618199154735</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.26694427058027</v>
+        <v>133.49549287936026</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.74538528404273</v>
+        <v>149.00047893127223</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.06444280534984</v>
+        <v>167.35095305880208</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.0854179200917</v>
+        <v>78.219331950531284</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.17245808158147</v>
+        <v>122.38197999625136</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.48718374582</v>
+        <v>136.72125496379638</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.73305608097894</v>
+        <v>153.99670342641116</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.63824407007098</v>
+        <v>174.937743153962</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.67022212359869</v>
+        <v>116.87030787703401</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.3382399993031</v>
+        <v>112.53089653994159</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.1597557190166</v>
+        <v>108.34524629082243</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.13046714786057</v>
+        <v>104.30904761677215</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.077118416283028</v>
+        <v>86.224737961170987</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.3382399993031</v>
+        <v>112.53089653994159</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.1597557190166</v>
+        <v>108.34524629082243</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.13046714786057</v>
+        <v>104.30904761677215</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>107.98813043228489</v>
+        <v>108.1733266721337</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.67022212359869</v>
+        <v>116.87030787703401</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.077118416283028</v>
+        <v>86.224737961170987</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>74.45</v>
+        <v>78.25</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20915224820505735</v>
+        <v>0.18846101742319771</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5439880299721739E-2</v>
+        <v>6.5337716402624715E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.19489358518186</v>
+        <v>108.38044441732059</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.19502202522382</v>
+        <v>108.3805730776332</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736715E-2</v>
+        <v>9.6234974214736702E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.859397965521609</v>
+        <v>49.944905261438073</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.533119080473725</v>
+        <v>61.618626376390196</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43127520124571606</v>
+        <v>0.43145992150459622</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.495245392162829</v>
+        <v>62.60242276812744</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>75.917948974160637</v>
+        <v>76.025126350125248</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29832225478931296</v>
+        <v>0.29853465024198167</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.549814448309689</v>
+        <v>77.682809935677668</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>92.9412573505479</v>
+        <v>93.074252837915878</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14098295889190715</v>
+        <v>0.14122650688225624</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.703083256311999</v>
+        <v>87.853491279649347</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.36899225558497</v>
+        <v>104.51940027892232</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5361200541176752E-2</v>
+        <v>3.5624915169486293E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>74.45</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>18227.242096000002</v>
+        <v>19157.578160000001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20915224820505735</v>
+        <v>0.18846101742319771</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8136000633239746</v>
+        <v>7.8270001411437988</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.19489358518186</v>
+        <v>108.38044441732059</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.533119080473725</v>
+        <v>61.618626376390196</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>75.917948974160637</v>
+        <v>76.025126350125248</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>92.9412573505479</v>
+        <v>93.074252837915878</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.36899225558497</v>
+        <v>104.51940027892232</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.12161830845800888</v>
+        <v>0.11591068648885185</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.5689724647414367E-2</v>
+        <v>8.152843450479233E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.069906259678774</v>
+        <v>-34.128335075012792</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.705362673568391</v>
+        <v>21.742586686389135</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.776676380446546</v>
+        <v>22.815737662506212</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.412132794336157</v>
+        <v>10.429989273882551</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.218555439260133</v>
+        <v>-19.251514656059506</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.34071012844194</v>
+        <v>106.5230810943972</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.67 HKD</v>
+        <v>116.87 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.34 HKD</v>
+        <v>112.53 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.16 HKD</v>
+        <v>108.35 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.13 HKD</v>
+        <v>104.31 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.08 HKD</v>
+        <v>86.22 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.19489358518186</v>
+        <v>108.38044441732059</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.859397965521609</v>
+        <v>49.944905261438073</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.533119080473725</v>
+        <v>61.618626376390196</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.495245392162829</v>
+        <v>62.60242276812744</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>75.917948974160637</v>
+        <v>76.025126350125248</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.549814448309689</v>
+        <v>77.682809935677668</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>92.9412573505479</v>
+        <v>93.074252837915878</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.703083256311999</v>
+        <v>87.853491279649347</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.36899225558497</v>
+        <v>104.51940027892232</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,12 +21684,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21707,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A09F24-0E90-422F-9674-D6F83C0C18F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909274B8-2B45-4AEF-974C-50D033600F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.25</v>
+        <v>76.849999999999994</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19157.578160000001</v>
+        <v>18814.822768000002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18846101742319771</v>
+        <v>0.19611470151787844</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8270001411437988</v>
+        <v>7.8264999389648438</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.38044441732059</v>
+        <v>108.3735181194445</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.618626376390196</v>
+        <v>61.615434534050976</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.025126350125248</v>
+        <v>76.021125600449537</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.074252837915878</v>
+        <v>93.069288341928086</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.51940027892232</v>
+        <v>104.51378580249782</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11591068648885185</v>
+        <v>0.11801472450402546</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.3013662979830843E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.128335075012792</v>
+        <v>-34.126154026429582</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.742586686389135</v>
+        <v>21.741197177121148</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.815737662506212</v>
+        <v>22.814279571093483</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.429989273882551</v>
+        <v>10.429322721785043</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.251514656059506</v>
+        <v>-19.250284344394053</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.87 HKD</v>
+        <v>116.86 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1110457977341362E-2</v>
+        <v>3.1114029688458507E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.53 HKD</v>
+        <v>112.52 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4933974012347139E-2</v>
+        <v>4.4937639730005072E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.35 HKD</v>
+        <v>108.34 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8984286884237284E-2</v>
+        <v>5.8988049744521182E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.31 HKD</v>
+        <v>104.3 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3262939526748519E-2</v>
+        <v>7.326680276648341E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14811716034698766</v>
+        <v>0.14812157763864028</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.38044441732059</v>
+        <v>108.3735181194445</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.944905261438073</v>
+        <v>49.941713419098861</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.618626376390196</v>
+        <v>61.615434534050976</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.60242276812744</v>
+        <v>62.598422018451721</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.025126350125248</v>
+        <v>76.021125600449537</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.682809935677668</v>
+        <v>77.677845439689875</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.074252837915878</v>
+        <v>93.069288341928086</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.853491279649347</v>
+        <v>87.84787680322485</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.51940027892232</v>
+        <v>104.51378580249782</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.82437988983504</v>
+        <v>115.81697787039563</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.251514656059506</v>
+        <v>-19.250284344394053</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8355479.1906738281</v>
+        <v>-8354945.21484375</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.128335075012792</v>
+        <v>-34.126154026429582</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5323134.8734194916</v>
+        <v>5322794.686423894</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.742586686389135</v>
+        <v>21.741197177121144</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5585869.3616296286</v>
+        <v>5585512.3839912415</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.815737662506208</v>
+        <v>22.814279571093483</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2553525.044375292</v>
+        <v>2553361.8555713855</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.429989273882551</v>
+        <v>10.429322721785045</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.3013662979830843E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.3013662979830843E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.152843450479233E-2</v>
+        <v>8.3013662979830843E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.4511182108626209E-2</v>
+        <v>8.6050748210800276E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0700112177526595</v>
+        <v>9.0694315781343562</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.197265139454423</v>
+        <v>10.196613460120048</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7130745137617911</v>
+        <v>7.7125815922581937</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.814743419349215</v>
+        <v>10.814052278666241</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11591068648885185</v>
+        <v>0.11801472450402546</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13031648740516835</v>
+        <v>0.13268202290331879</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.8569642348393494E-2</v>
+        <v>0.10035890165592966</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13820758363385577</v>
+        <v>0.14071636016481773</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6187066935604767E-2</v>
+        <v>1.6481951694353583E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8660761658612489E-2</v>
+        <v>1.9000710472172118E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1054992015754875E-3</v>
+        <v>5.1985076450654774E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.429989273882551</v>
+        <v>10.429322721785043</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8270001411437988</v>
+        <v>7.8264999389648438</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26079543.155398503</v>
+        <v>26077876.483100399</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.3805730776332</v>
+        <v>108.37364677153478</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.160323419046492</v>
+        <v>97.154114168426105</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.72507784773931</v>
+        <v>101.71857687614404</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.63802873347787</v>
+        <v>102.63146941768761</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.55097961921643</v>
+        <v>103.5443619592312</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.46393050495504</v>
+        <v>104.45725450077482</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.328647741073752</v>
+        <v>93.322683362369631</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.83935917822161</v>
+        <v>101.83285090321895</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.59127295544401</v>
+        <v>103.58465272042183</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.35977722926403</v>
+        <v>105.35304397396904</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.14487199968161</v>
+        <v>107.13802466386052</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.93462266501399</v>
+        <v>89.928875189172757</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.94591519731935</v>
+        <v>101.93940011261286</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.48896681482469</v>
+        <v>104.48228921064238</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.08003229895959</v>
+        <v>107.07318910686649</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.7195757195589</v>
+        <v>109.71256384146265</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.928260126779193</v>
+        <v>86.922704779347981</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.04526812887899</v>
+        <v>102.03874669479828</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.33434751223682</v>
+        <v>105.3276158820855</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.71607907853017</v>
+        <v>108.70913133116056</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.19225155310072</v>
+        <v>112.18508165305258</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.224737961170987</v>
+        <v>86.219227573917848</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.30904761677215</v>
+        <v>104.30238151073385</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.34524629082243</v>
+        <v>108.33832224236238</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.53089653994159</v>
+        <v>112.52370499801825</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.87030787703401</v>
+        <v>116.86283901519664</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.865922531342306</v>
+        <v>83.860562889533981</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.39542222378658</v>
+        <v>104.38875059778331</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.09496866740599</v>
+        <v>109.0879967062387</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.01069121131616</v>
+        <v>114.00340509976132</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.15089691256806</v>
+        <v>119.14328230452087</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.5121778533248</v>
+        <v>83.506840818371657</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.50033348614987</v>
+        <v>106.49352734102294</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.88671702902369</v>
+        <v>111.87956665485162</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.56633185503873</v>
+        <v>117.55881851221196</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.55320272109124</v>
+        <v>123.54530677371632</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.661432921123478</v>
+        <v>81.65621416221876</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.57542510770325</v>
+        <v>106.56861416367609</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.55160521924468</v>
+        <v>112.54441235388627</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.90479741529808</v>
+        <v>118.89719853479689</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.65662698659563</v>
+        <v>125.64859661512695</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.559483093690403</v>
+        <v>81.554270850120417</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.53297020775049</v>
+        <v>108.52603416236818</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.14191788436827</v>
+        <v>115.13455947920968</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.22086642665788</v>
+        <v>122.21305562525275</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.80112997167248</v>
+        <v>129.79283473634965</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.107374225504117</v>
+        <v>80.102254782241644</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.59825272332334</v>
+        <v>108.59131250591395</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.73157122712944</v>
+        <v>115.72417513883791</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.43150063872486</v>
+        <v>123.42361246899728</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.74115229563171</v>
+        <v>131.73273307878642</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.623371580320764</v>
+        <v>78.618346975609882</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.79507725806982</v>
+        <v>113.78780492581322</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.43477778875344</v>
+        <v>123.42688940959215</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.20030789278451</v>
+        <v>134.19173151802869</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.22864579967842</v>
+        <v>146.21930072673405</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.615942270097364</v>
+        <v>77.610982047439251</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.73923126541411</v>
+        <v>116.73177078032461</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.26468359061667</v>
+        <v>128.25648654538122</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.52310311762474</v>
+        <v>141.51405876304759</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.80221890375154</v>
+        <v>156.79219810265963</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.076354451150678</v>
+        <v>78.071364804808908</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.34618199154735</v>
+        <v>120.33849099609884</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.49549287936026</v>
+        <v>133.48696154740489</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>149.00047893127223</v>
+        <v>148.99095671805097</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.35095305880208</v>
+        <v>167.34025811695199</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.219331950531284</v>
+        <v>78.214333166888437</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.38197999625136</v>
+        <v>122.3741588985185</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.72125496379638</v>
+        <v>136.71251748220587</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.99670342641116</v>
+        <v>153.98686191814278</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.937743153962</v>
+        <v>174.92656336110022</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.87030787703401</v>
+        <v>116.86283901519664</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.53089653994159</v>
+        <v>112.52370499801825</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.34524629082243</v>
+        <v>108.33832224236238</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.30904761677215</v>
+        <v>104.30238151073385</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.224737961170987</v>
+        <v>86.219227573917848</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.53089653994159</v>
+        <v>112.52370499801825</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.34524629082243</v>
+        <v>108.33832224236238</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.30904761677215</v>
+        <v>104.30238151073385</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.1733266721337</v>
+        <v>108.16641361058642</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.87030787703401</v>
+        <v>116.86283901519664</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.224737961170987</v>
+        <v>86.219227573917848</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.25</v>
+        <v>76.849999999999994</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18846101742319771</v>
+        <v>0.19611470151787844</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5337716402624715E-2</v>
+        <v>6.5341523720629013E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.38044441732059</v>
+        <v>108.3735181194445</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.3805730776332</v>
+        <v>108.37364677153478</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736702E-2</v>
+        <v>9.6234974214736729E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.944905261438073</v>
+        <v>49.941713419098861</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.618626376390196</v>
+        <v>61.615434534050976</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43145992150459622</v>
+        <v>0.4314530375756449</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.60242276812744</v>
+        <v>62.598422018451721</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.025126350125248</v>
+        <v>76.021125600449537</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29853465024198167</v>
+        <v>0.29852673494771653</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.682809935677668</v>
+        <v>77.677845439689875</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.074252837915878</v>
+        <v>93.069288341928086</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14122650688225624</v>
+        <v>0.14121743063327308</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.853491279649347</v>
+        <v>87.84787680322485</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.51940027892232</v>
+        <v>104.51378580249782</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5624915169486293E-2</v>
+        <v>3.561508737487562E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.25</v>
+        <v>76.849999999999994</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19157.578160000001</v>
+        <v>18814.822768000002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18846101742319771</v>
+        <v>0.19611470151787844</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8270001411437988</v>
+        <v>7.8264999389648438</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.38044441732059</v>
+        <v>108.3735181194445</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.618626376390196</v>
+        <v>61.615434534050976</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.025126350125248</v>
+        <v>76.021125600449537</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.074252837915878</v>
+        <v>93.069288341928086</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.51940027892232</v>
+        <v>104.51378580249782</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11591068648885185</v>
+        <v>0.11801472450402546</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.152843450479233E-2</v>
+        <v>8.3013662979830843E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.128335075012792</v>
+        <v>-34.126154026429582</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.742586686389135</v>
+        <v>21.741197177121148</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.815737662506212</v>
+        <v>22.814279571093483</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.429989273882551</v>
+        <v>10.429322721785043</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.251514656059506</v>
+        <v>-19.250284344394053</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.5230810943972</v>
+        <v>106.51627349553281</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.87 HKD</v>
+        <v>116.86 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.53 HKD</v>
+        <v>112.52 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.35 HKD</v>
+        <v>108.34 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.31 HKD</v>
+        <v>104.3 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.38044441732059</v>
+        <v>108.3735181194445</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.944905261438073</v>
+        <v>49.941713419098861</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.618626376390196</v>
+        <v>61.615434534050976</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.60242276812744</v>
+        <v>62.598422018451721</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.025126350125248</v>
+        <v>76.021125600449537</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.682809935677668</v>
+        <v>77.677845439689875</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.074252837915878</v>
+        <v>93.069288341928086</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.853491279649347</v>
+        <v>87.84787680322485</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.51940027892232</v>
+        <v>104.51378580249782</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,15 +21684,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21707,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909274B8-2B45-4AEF-974C-50D033600F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656E800F-A6D3-4C8B-9932-FF8E260B46C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>76.849999999999994</v>
+        <v>77.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>18814.822768000002</v>
+        <v>19022.924255999998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19611470151787844</v>
+        <v>0.19168637716804129</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8264999389648438</v>
+        <v>7.8322000503540039</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.3735181194445</v>
+        <v>108.45244754252425</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,13 +5561,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>61.615434534050976</v>
+        <v>60.949955185491234</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5576,13 +5576,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.021125600449537</v>
+        <v>76.200342327849683</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.069288341928086</v>
+        <v>93.125861826235152</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.51378580249782</v>
+        <v>104.5777662135353</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11801472450402546</v>
+        <v>0.11680871207192643</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.3013662979830843E-2</v>
+        <v>8.2105534105534103E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.126154026429582</v>
+        <v>-34.151008416099458</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.741197177121148</v>
+        <v>21.757031489599232</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.814279571093483</v>
+        <v>22.830895419280132</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.429322721785043</v>
+        <v>10.436918492779906</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.250284344394053</v>
+        <v>-19.264304502305222</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.86 HKD</v>
+        <v>116.95 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1114029688458507E-2</v>
+        <v>3.1073354842866559E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.52 HKD</v>
+        <v>112.61 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4937639730005072E-2</v>
+        <v>4.4895894344789591E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.34 HKD</v>
+        <v>108.42 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8988049744521182E-2</v>
+        <v>5.8945198106734702E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.3 HKD</v>
+        <v>104.38 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.326680276648341E-2</v>
+        <v>7.3222808016017257E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.22 HKD</v>
+        <v>86.28 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14812157763864028</v>
+        <v>0.1480712734025792</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.3735181194445</v>
+        <v>108.45244754252425</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6585,19 +6585,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>11.673721114952119</v>
+        <v>11.586073736913978</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.941713419098861</v>
+        <v>49.363881448577253</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>61.615434534050976</v>
+        <v>60.949955185491234</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6606,19 +6606,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>13.42270358199781</v>
+        <v>13.438509259259257</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.598422018451721</v>
+        <v>62.761833068590427</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.021125600449537</v>
+        <v>76.200342327849683</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.677845439689875</v>
+        <v>77.734418923996941</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.069288341928086</v>
+        <v>93.125861826235152</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.84787680322485</v>
+        <v>87.911857214262326</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.51378580249782</v>
+        <v>104.5777662135353</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.81697787039563</v>
+        <v>115.90132843319708</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.250284344394053</v>
+        <v>-19.264304502305222</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8354945.21484375</v>
+        <v>-8361030.1977539063</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.126154026429582</v>
+        <v>-34.151008416099458</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5322794.686423894</v>
+        <v>5326671.326409949</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.741197177121144</v>
+        <v>21.757031489599232</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5585512.3839912415</v>
+        <v>5589580.3636759752</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.814279571093483</v>
+        <v>22.830895419280129</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2553361.8555713855</v>
+        <v>2555221.492332018</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.429322721785045</v>
+        <v>10.436918492779903</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.3013662979830843E-2</v>
+        <v>8.2105534105534103E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.3013662979830843E-2</v>
+        <v>8.2105534105534103E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.3013662979830843E-2</v>
+        <v>8.2105534105534103E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.6050748210800276E-2</v>
+        <v>8.5109395109395108E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0694315781343562</v>
+        <v>9.0760369279886834</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.196613460120048</v>
+        <v>10.20403974683418</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7125815922581937</v>
+        <v>7.71819873587497</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.814052278666241</v>
+        <v>10.821928251711318</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11801472450402546</v>
+        <v>0.11680871207192643</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13268202290331879</v>
+        <v>0.13132612286787876</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10035890165592966</v>
+        <v>9.9333317064027926E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.14071636016481773</v>
+        <v>0.13927835587788054</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6481951694353583E-2</v>
+        <v>1.6301647203488711E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9000710472172118E-2</v>
+        <v>1.8792851992103312E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1985076450654774E-3</v>
+        <v>5.1416385138131522E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.429322721785043</v>
+        <v>10.436918492779906</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8264999389648438</v>
+        <v>7.8322000503540039</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26077876.483100399</v>
+        <v>26096869.238726243</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.37364677153478</v>
+        <v>108.45257628831301</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.154114168426105</v>
+        <v>97.224872397135485</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.71857687614404</v>
+        <v>101.79265944473313</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.63146941768761</v>
+        <v>102.70621685425265</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.5443619592312</v>
+        <v>103.61977426377217</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.45725450077482</v>
+        <v>104.53333167329174</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.322683362369631</v>
+        <v>93.390651125028441</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.83285090321895</v>
+        <v>101.9070166986257</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.58465272042183</v>
+        <v>103.66009436909218</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.35304397396904</v>
+        <v>105.42977355814101</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.13802466386052</v>
+        <v>107.21605426577212</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.928875189172757</v>
+        <v>89.994371210341569</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.93940011261286</v>
+        <v>102.01364350878197</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.48228921064238</v>
+        <v>104.55838461616715</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.07318910686649</v>
+        <v>107.15117148844976</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.71256384146265</v>
+        <v>109.79246850377196</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.922704779347981</v>
+        <v>86.986011379150355</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.03874669479828</v>
+        <v>102.11306244599058</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.3276158820855</v>
+        <v>105.4043269467459</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.70913133116056</v>
+        <v>108.78830518440772</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.18508165305258</v>
+        <v>112.26678707266687</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.219227573917848</v>
+        <v>86.282021824846282</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.30238151073385</v>
+        <v>104.37834588783758</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.33832224236238</v>
+        <v>108.41722603196335</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.52370499801825</v>
+        <v>112.60565704010752</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.86283901519664</v>
+        <v>116.94795128822226</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.860562889533981</v>
+        <v>83.921639303429828</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.38875059778331</v>
+        <v>104.46477787828199</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.0879967062387</v>
+        <v>109.16744649059889</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.00340509976132</v>
+        <v>114.08643482094958</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.14328230452087</v>
+        <v>119.2300554452226</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.506840818371657</v>
+        <v>83.567659613252346</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.49352734102294</v>
+        <v>106.57108754964777</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.87956665485162</v>
+        <v>111.96104956510229</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.55881851221196</v>
+        <v>117.64443767346199</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.54530677371632</v>
+        <v>123.63528594904501</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.65621416221876</v>
+        <v>81.715685128803003</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.56861416367609</v>
+        <v>106.64622905871968</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.54441235388627</v>
+        <v>112.62637947733194</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.89719853479689</v>
+        <v>118.98379245044151</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.64859661512695</v>
+        <v>125.74010763565761</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.554270850120417</v>
+        <v>81.613667570459356</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.52603416236818</v>
+        <v>108.60507466427498</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.13455947920968</v>
+        <v>115.21841303046394</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.21305562525275</v>
+        <v>122.30206450990185</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.79283473634965</v>
+        <v>129.88736404335555</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.102254782241644</v>
+        <v>80.160593986016309</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.59131250591395</v>
+        <v>108.67040055063457</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.72417513883791</v>
+        <v>115.80845811256235</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.42361246899728</v>
+        <v>123.51350301325235</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.73273307878642</v>
+        <v>131.82867523147326</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.618346975609882</v>
+        <v>78.675605435775651</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.78780492581322</v>
+        <v>113.87067762342561</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.42688940959215</v>
+        <v>123.51678234047299</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.19173151802869</v>
+        <v>134.28946458173814</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.21930072673405</v>
+        <v>146.32579357895244</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.610982047439251</v>
+        <v>77.667506834527032</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.73177078032461</v>
+        <v>116.81678759515765</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.25648654538122</v>
+        <v>128.34989691596732</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.51405876304759</v>
+        <v>141.61712474456834</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.79219810265963</v>
+        <v>156.90639129260484</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.071364804808908</v>
+        <v>78.128224892863798</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.33849099609884</v>
+        <v>120.42613461820713</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.48696154740489</v>
+        <v>133.5841813207077</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>148.99095671805097</v>
+        <v>149.09946819264286</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.34025811695199</v>
+        <v>167.46213355534667</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.214333166888437</v>
+        <v>78.271297380107242</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.3741588985185</v>
+        <v>122.46328511615297</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.71251748220587</v>
+        <v>136.81208645735671</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>153.98686191814278</v>
+        <v>154.09901195612215</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.92656336110022</v>
+        <v>175.05396397489403</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.86283901519664</v>
+        <v>116.94795128822226</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.52370499801825</v>
+        <v>112.60565704010752</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.33832224236238</v>
+        <v>108.41722603196335</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.30238151073385</v>
+        <v>104.37834588783758</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.219227573917848</v>
+        <v>86.282021824846282</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.52370499801825</v>
+        <v>112.60565704010752</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.33832224236238</v>
+        <v>108.41722603196335</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.30238151073385</v>
+        <v>104.37834588783758</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.16641361058642</v>
+        <v>108.24519219756074</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.86283901519664</v>
+        <v>116.94795128822226</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.219227573917848</v>
+        <v>86.282021824846282</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>76.849999999999994</v>
+        <v>77.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19611470151787844</v>
+        <v>0.19168637716804129</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5341523720629013E-2</v>
+        <v>6.5298165802016514E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.3735181194445</v>
+        <v>108.45244754252425</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.37364677153478</v>
+        <v>108.45257628831301</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736729E-2</v>
+        <v>9.623497421473666E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20067,23 +20067,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>11.673721114952119</v>
+        <v>11.586073736913978</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.941713419098861</v>
+        <v>49.363881448577253</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>61.615434534050976</v>
+        <v>60.949955185491234</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.4314530375756449</v>
+        <v>0.43800295367614706</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20092,23 +20092,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>13.42270358199781</v>
+        <v>13.438509259259257</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.598422018451721</v>
+        <v>62.761833068590427</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.021125600449537</v>
+        <v>76.200342327849683</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29852673494771653</v>
+        <v>0.29738476120632051</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.677845439689875</v>
+        <v>77.734418923996941</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.069288341928086</v>
+        <v>93.125861826235152</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14121743063327308</v>
+        <v>0.14132079140288223</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.84787680322485</v>
+        <v>87.911857214262326</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.51378580249782</v>
+        <v>104.5777662135353</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.561508737487562E-2</v>
+        <v>3.5727006783039084E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>76.849999999999994</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>18814.822768000002</v>
+        <v>19022.924255999998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19611470151787844</v>
+        <v>0.19168637716804129</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8264999389648438</v>
+        <v>7.8322000503540039</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.3735181194445</v>
+        <v>108.45244754252425</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,14 +20445,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>61.615434534050976</v>
+        <v>60.949955185491234</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20461,14 +20461,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.021125600449537</v>
+        <v>76.200342327849683</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.069288341928086</v>
+        <v>93.125861826235152</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.51378580249782</v>
+        <v>104.5777662135353</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11801472450402546</v>
+        <v>0.11680871207192643</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.3013662979830843E-2</v>
+        <v>8.2105534105534103E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.126154026429582</v>
+        <v>-34.151008416099458</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.741197177121148</v>
+        <v>21.757031489599232</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.814279571093483</v>
+        <v>22.830895419280132</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.429322721785043</v>
+        <v>10.436918492779906</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.250284344394053</v>
+        <v>-19.264304502305222</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.51627349553281</v>
+        <v>106.59385027038974</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.86 HKD</v>
+        <v>116.95 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.52 HKD</v>
+        <v>112.61 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.34 HKD</v>
+        <v>108.42 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.3 HKD</v>
+        <v>104.38 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.22 HKD</v>
+        <v>86.28 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.3735181194445</v>
+        <v>108.45244754252425</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21480,19 +21480,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>11.673721114952119</v>
+        <v>11.586073736913978</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.941713419098861</v>
+        <v>49.363881448577253</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>61.615434534050976</v>
+        <v>60.949955185491234</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21501,19 +21501,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>13.42270358199781</v>
+        <v>13.438509259259257</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.598422018451721</v>
+        <v>62.761833068590427</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.021125600449537</v>
+        <v>76.200342327849683</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.677845439689875</v>
+        <v>77.734418923996941</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.069288341928086</v>
+        <v>93.125861826235152</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.84787680322485</v>
+        <v>87.911857214262326</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.51378580249782</v>
+        <v>104.5777662135353</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,12 +21684,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21707,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656E800F-A6D3-4C8B-9932-FF8E260B46C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AD1FA0-F102-4454-A69B-A214205292A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>77.7</v>
+        <v>76.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>19022.924255999998</v>
+        <v>18729.13392</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19168637716804129</v>
+        <v>0.19854052639458994</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8322000503540039</v>
+        <v>7.837090015411377</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.45244754252425</v>
+        <v>108.52015887209447</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>60.949955185491234</v>
+        <v>60.980775089710718</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.200342327849683</v>
+        <v>76.239527125054664</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.125861826235152</v>
+        <v>93.174394625429457</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.5777662135353</v>
+        <v>104.63265320660783</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11680871207192643</v>
+        <v>0.11871507806059703</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.2105534105534103E-2</v>
+        <v>8.3393464052287578E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.151008416099458</v>
+        <v>-34.172330297148861</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.757031489599232</v>
+        <v>21.77061530041258</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.830895419280132</v>
+        <v>22.845149687571425</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.436918492779906</v>
+        <v>10.443434690835142</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.264304502305222</v>
+        <v>-19.276332000998469</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.95 HKD</v>
+        <v>117.02 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1073354842866559E-2</v>
+        <v>3.1038508147826663E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.61 HKD</v>
+        <v>112.68 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4895894344789591E-2</v>
+        <v>4.4860130524968234E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.42 HKD</v>
+        <v>108.48 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8945198106734702E-2</v>
+        <v>5.8908486568052192E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.38 HKD</v>
+        <v>104.44 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3222808016017257E-2</v>
+        <v>7.318511718171837E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.28 HKD</v>
+        <v>86.34 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1480712734025792</v>
+        <v>0.14802817730036527</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.45244754252425</v>
+        <v>108.52015887209447</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.363881448577253</v>
+        <v>49.394701352796744</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>60.949955185491234</v>
+        <v>60.980775089710718</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.761833068590427</v>
+        <v>62.801017865795409</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.200342327849683</v>
+        <v>76.239527125054664</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.734418923996941</v>
+        <v>77.782951723191246</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.125861826235152</v>
+        <v>93.174394625429457</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.911857214262326</v>
+        <v>87.966744207334855</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.5777662135353</v>
+        <v>104.63265320660783</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.90132843319708</v>
+        <v>115.97369040588646</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.264304502305222</v>
+        <v>-19.276332000998469</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8361030.1977539063</v>
+        <v>-8366250.3332519531</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.151008416099458</v>
+        <v>-34.172330297148861</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5326671.326409949</v>
+        <v>5329996.9866957944</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.757031489599232</v>
+        <v>21.77061530041258</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5589580.3636759752</v>
+        <v>5593070.168901586</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.830895419280129</v>
+        <v>22.845149687571421</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2555221.492332018</v>
+        <v>2556816.8223454272</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.436918492779903</v>
+        <v>10.44343469083514</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.2105534105534103E-2</v>
+        <v>8.3393464052287578E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.2105534105534103E-2</v>
+        <v>8.3393464052287578E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.2105534105534103E-2</v>
+        <v>8.3393464052287578E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.5109395109395108E-2</v>
+        <v>8.6444444444444449E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0760369279886834</v>
+        <v>9.0817034716356737</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.20403974683418</v>
+        <v>10.210410549097308</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.71819873587497</v>
+        <v>7.7230175252166173</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.821928251711318</v>
+        <v>10.828684827215525</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11680871207192643</v>
+        <v>0.11871507806059703</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13132612286787876</v>
+        <v>0.13346941894244846</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>9.9333317064027926E-2</v>
+        <v>0.10095447745381199</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.13927835587788054</v>
+        <v>0.14155143564987616</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6301647203488711E-2</v>
+        <v>1.6557359316484613E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8792851992103312E-2</v>
+        <v>1.9087641827273558E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1416385138131522E-3</v>
+        <v>5.2222916669710058E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.436918492779906</v>
+        <v>10.443434690835142</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8322000503540039</v>
+        <v>7.837090015411377</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26096869.238726243</v>
+        <v>26113162.588980805</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.45257628831301</v>
+        <v>108.52028769826454</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.224872397135485</v>
+        <v>97.285573889139386</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.79265944473313</v>
+        <v>101.85621279431328</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.70621685425265</v>
+        <v>102.77034057534804</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.61977426377217</v>
+        <v>103.68446835638282</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.53333167329174</v>
+        <v>104.59859613741764</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.390651125028441</v>
+        <v>93.448958754781344</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.9070166986257</v>
+        <v>101.9706414461492</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.66009436909218</v>
+        <v>103.72481363520515</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.42977355814101</v>
+        <v>105.4955977078552</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.21605426577212</v>
+        <v>107.28299366409934</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.994371210341569</v>
+        <v>90.050558402669353</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>102.01364350878197</v>
+        <v>102.07733482781444</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.55838461616715</v>
+        <v>104.62366472187708</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.15117148844976</v>
+        <v>107.21807037778692</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.79246850377196</v>
+        <v>109.86101646361651</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.986011379150355</v>
+        <v>87.040320328537462</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.11306244599058</v>
+        <v>102.17681583636008</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.4043269467459</v>
+        <v>105.4701352090926</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.78830518440772</v>
+        <v>108.85622620373594</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.26678707266687</v>
+        <v>112.33687985149778</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.282021824846282</v>
+        <v>86.335891244561111</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.37834588783758</v>
+        <v>104.4435135879546</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.41722603196335</v>
+        <v>108.48491537129397</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.60565704010752</v>
+        <v>112.67596138941532</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.94795128822226</v>
+        <v>117.02096671066475</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.921639303429828</v>
+        <v>83.974035039125155</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.46477787828199</v>
+        <v>104.52999954145031</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.16744649059889</v>
+        <v>109.23560422345935</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.08643482094958</v>
+        <v>114.15766368081118</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.2300554452226</v>
+        <v>119.30449567927784</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.567659613252346</v>
+        <v>83.619834344848584</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.57108754964777</v>
+        <v>106.63762426869143</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.96104956510229</v>
+        <v>112.03095145941555</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.64443767346199</v>
+        <v>117.71788794103931</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.63528594904501</v>
+        <v>123.71247654993138</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.715685128803003</v>
+        <v>81.766703596455798</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.64622905871968</v>
+        <v>106.71281269170211</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.62637947733194</v>
+        <v>112.69669676451075</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.98379245044151</v>
+        <v>119.05807893236687</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.74010763565761</v>
+        <v>125.81861236340916</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.613667570459356</v>
+        <v>81.664622344348928</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.60507466427498</v>
+        <v>108.67288128524321</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.21841303046394</v>
+        <v>115.29034863094179</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.30206450990185</v>
+        <v>122.37842272573559</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.88736404335555</v>
+        <v>129.96845807408548</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.160593986016309</v>
+        <v>80.21064154622286</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.67040055063457</v>
+        <v>108.73824795724407</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.80845811256235</v>
+        <v>115.88076210248572</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.51350301325235</v>
+        <v>123.59061758003632</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.82867523147326</v>
+        <v>131.91098130273002</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.675605435775651</v>
+        <v>78.72472585647165</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.87067762342561</v>
+        <v>113.94177177718292</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.51678234047299</v>
+        <v>123.59389895467601</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.28946458173814</v>
+        <v>134.3733070251329</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.32579357895244</v>
+        <v>146.41715079825138</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.667506834527032</v>
+        <v>77.71599785774815</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.81678759515765</v>
+        <v>116.88972112670464</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.34989691596732</v>
+        <v>128.43003104264969</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.61712474456834</v>
+        <v>141.70554214798941</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.90639129260484</v>
+        <v>157.004354414814</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.128224892863798</v>
+        <v>78.177003561343213</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.42613461820713</v>
+        <v>120.50132161375009</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.5841813207077</v>
+        <v>133.66758342671577</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>149.09946819264286</v>
+        <v>149.19255713123579</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.46213355534667</v>
+        <v>167.56668706218437</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.271297380107242</v>
+        <v>78.320165374632822</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.46328511615297</v>
+        <v>122.539743988651</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.81208645735671</v>
+        <v>136.89750387748154</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>154.09901195612215</v>
+        <v>154.1952223157908</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>175.05396397489403</v>
+        <v>175.16325737412905</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.94795128822226</v>
+        <v>117.02096671066475</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.60565704010752</v>
+        <v>112.67596138941532</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.41722603196335</v>
+        <v>108.48491537129397</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.37834588783758</v>
+        <v>104.4435135879546</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.282021824846282</v>
+        <v>86.335891244561111</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.60565704010752</v>
+        <v>112.67596138941532</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.41722603196335</v>
+        <v>108.48491537129397</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.37834588783758</v>
+        <v>104.4435135879546</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.24519219756074</v>
+        <v>108.31277412908339</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.94795128822226</v>
+        <v>117.02096671066475</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.282021824846282</v>
+        <v>86.335891244561111</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>77.7</v>
+        <v>76.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19168637716804129</v>
+        <v>0.19854052639458994</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5298165802016514E-2</v>
+        <v>6.5261020536413597E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.45244754252425</v>
+        <v>108.52015887209447</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.45257628831301</v>
+        <v>108.52028769826454</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.623497421473666E-2</v>
+        <v>9.6234974214736688E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.363881448577253</v>
+        <v>49.394701352796744</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>60.949955185491234</v>
+        <v>60.980775089710718</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43800295367614706</v>
+        <v>0.43806961099656405</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.761833068590427</v>
+        <v>62.801017865795409</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.200342327849683</v>
+        <v>76.239527125054664</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29738476120632051</v>
+        <v>0.29746207601010655</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.734418923996941</v>
+        <v>77.782951723191246</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.125861826235152</v>
+        <v>93.174394625429457</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14132079140288223</v>
+        <v>0.14140934187860943</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.911857214262326</v>
+        <v>87.966744207334855</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.5777662135353</v>
+        <v>104.63265320660783</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5727006783039084E-2</v>
+        <v>3.5822889552424853E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>77.7</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>19022.924255999998</v>
+        <v>18729.13392</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19168637716804129</v>
+        <v>0.19854052639458994</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8322000503540039</v>
+        <v>7.837090015411377</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.45244754252425</v>
+        <v>108.52015887209447</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>60.949955185491234</v>
+        <v>60.980775089710718</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.200342327849683</v>
+        <v>76.239527125054664</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.125861826235152</v>
+        <v>93.174394625429457</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.5777662135353</v>
+        <v>104.63265320660783</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11680871207192643</v>
+        <v>0.11871507806059703</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.2105534105534103E-2</v>
+        <v>8.3393464052287578E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.151008416099458</v>
+        <v>-34.172330297148861</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.757031489599232</v>
+        <v>21.77061530041258</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.830895419280132</v>
+        <v>22.845149687571425</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.436918492779906</v>
+        <v>10.443434690835142</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.264304502305222</v>
+        <v>-19.276332000998469</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.59385027038974</v>
+        <v>106.66040120113742</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.95 HKD</v>
+        <v>117.02 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.61 HKD</v>
+        <v>112.68 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.42 HKD</v>
+        <v>108.48 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.38 HKD</v>
+        <v>104.44 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.28 HKD</v>
+        <v>86.34 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.45244754252425</v>
+        <v>108.52015887209447</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.363881448577253</v>
+        <v>49.394701352796744</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>60.949955185491234</v>
+        <v>60.980775089710718</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.761833068590427</v>
+        <v>62.801017865795409</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.200342327849683</v>
+        <v>76.239527125054664</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.734418923996941</v>
+        <v>77.782951723191246</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.125861826235152</v>
+        <v>93.174394625429457</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.911857214262326</v>
+        <v>87.966744207334855</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.5777662135353</v>
+        <v>104.63265320660783</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,15 +21684,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21707,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AD1FA0-F102-4454-A69B-A214205292A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96182190-A33D-4B31-898E-807B2D62543E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19854052639458994</v>
+        <v>0.19853737511444283</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.837090015411377</v>
+        <v>7.8370199203491211</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.52015887209447</v>
+        <v>108.51918826600506</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>60.980775089710718</v>
+        <v>60.980333302687782</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.239527125054664</v>
+        <v>76.238965431715897</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.174394625429457</v>
+        <v>93.173698933427346</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.63265320660783</v>
+        <v>104.63186643059791</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11871507806059703</v>
+        <v>0.11871401627098241</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.172330297148861</v>
+        <v>-34.172024659263514</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.77061530041258</v>
+        <v>21.77042058367055</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.845149687571425</v>
+        <v>22.844945360176123</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.443434690835142</v>
+        <v>10.443341284583155</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.276332000998469</v>
+        <v>-19.276159593167371</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1038508147826663E-2</v>
+        <v>3.103900734983174E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.68 HKD</v>
+        <v>112.67 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4860130524968234E-2</v>
+        <v>4.4860642865256095E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8908486568052192E-2</v>
+        <v>5.8909012484892338E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.318511718171837E-2</v>
+        <v>7.3185657127457102E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14802817730036527</v>
+        <v>0.14802879467914332</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.52015887209447</v>
+        <v>108.51918826600506</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.394701352796744</v>
+        <v>49.394259565773801</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>60.980775089710718</v>
+        <v>60.980333302687782</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.801017865795409</v>
+        <v>62.800456172456634</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.239527125054664</v>
+        <v>76.238965431715897</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.782951723191246</v>
+        <v>77.782256031189135</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.174394625429457</v>
+        <v>93.173698933427346</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.966744207334855</v>
+        <v>87.965957431324938</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.63265320660783</v>
+        <v>104.63186643059791</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.97369040588646</v>
+        <v>115.97265313528817</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.276332000998469</v>
+        <v>-19.276159593167371</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8366250.3332519531</v>
+        <v>-8366175.5053710938</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.172330297148861</v>
+        <v>-34.172024659263514</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5329996.9866957944</v>
+        <v>5329949.3151149051</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.77061530041258</v>
+        <v>21.77042058367055</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5593070.168901586</v>
+        <v>5593020.1443898194</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.845149687571421</v>
+        <v>22.844945360176119</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2556816.8223454272</v>
+        <v>2556793.9541336307</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.44343469083514</v>
+        <v>10.443341284583155</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0817034716356737</v>
+        <v>9.0816222447301538</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.210410549097308</v>
+        <v>10.210319227017086</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7230175252166173</v>
+        <v>7.722948450420593</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.828684827215525</v>
+        <v>10.828587975279969</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11871507806059703</v>
+        <v>0.11871401627098241</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13346941894244846</v>
+        <v>0.13346822518976584</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10095447745381199</v>
+        <v>0.10095357451530187</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.14155143564987616</v>
+        <v>0.14155016961150288</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.443434690835142</v>
+        <v>10.443341284583155</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.837090015411377</v>
+        <v>7.8370199203491211</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26113162.588980805</v>
+        <v>26112929.032424252</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.52028769826454</v>
+        <v>108.51931709102291</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.285573889139386</v>
+        <v>97.284703765363219</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.85621279431328</v>
+        <v>101.85530179066743</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.77034057534804</v>
+        <v>102.76942139572824</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.68446835638282</v>
+        <v>103.68354100078909</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.59859613741764</v>
+        <v>104.59766060584997</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.448958754781344</v>
+        <v>93.448122945754179</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.9706414461492</v>
+        <v>101.9697294190516</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.72481363520515</v>
+        <v>103.72388591876258</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.4955977078552</v>
+        <v>105.4946541534907</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.28299366409934</v>
+        <v>107.28203412323595</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>90.050558402669353</v>
+        <v>90.049752988990932</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>102.07733482781444</v>
+        <v>102.07642184644946</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.62366472187708</v>
+        <v>104.62272896609556</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.21807037778692</v>
+        <v>107.21711141759846</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.86101646361651</v>
+        <v>109.86003386487471</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>87.040320328537462</v>
+        <v>87.039541838477987</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.17681583636008</v>
+        <v>102.17590196523533</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.4701352090926</v>
+        <v>105.46919188246511</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.85622620373594</v>
+        <v>108.85525259185478</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.33687985149778</v>
+        <v>112.33587510859304</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.335891244561111</v>
+        <v>86.335119054926977</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.4435135879546</v>
+        <v>104.4425794434478</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.48491537129397</v>
+        <v>108.48394508042301</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.67596138941532</v>
+        <v>112.67495361375971</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>117.02096671066475</v>
+        <v>117.01992007320995</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.974035039125155</v>
+        <v>83.973283973971846</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.52999954145031</v>
+        <v>104.52906462341173</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.23560422345935</v>
+        <v>109.23462721841493</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.15766368081118</v>
+        <v>114.15664265278586</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.30449567927784</v>
+        <v>119.3034286179023</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.619834344848584</v>
+        <v>83.619086447672117</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.63762426869143</v>
+        <v>106.63667050002253</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>112.03095145941555</v>
+        <v>112.02994945273939</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.71788794103931</v>
+        <v>117.71683507030953</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.71247654993138</v>
+        <v>123.7113700635023</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.766703596455798</v>
+        <v>81.765972273711284</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.71281269170211</v>
+        <v>106.71185825054673</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.69669676451075</v>
+        <v>112.6956888033976</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>119.05807893236687</v>
+        <v>119.05701407494678</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.81861236340916</v>
+        <v>125.81748703966664</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.664622344348928</v>
+        <v>81.663891934620807</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.67288128524321</v>
+        <v>108.67190931320202</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.29034863094179</v>
+        <v>115.28931747216362</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.37842272573559</v>
+        <v>122.3773281711059</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.96845807408548</v>
+        <v>129.96729563405452</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.21064154622286</v>
+        <v>80.209924140922965</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.73824795724407</v>
+        <v>108.7372754005623</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.88076210248572</v>
+        <v>115.87972566303972</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.59061758003632</v>
+        <v>123.58951218351588</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.91098130273002</v>
+        <v>131.9098014887393</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.72472585647165</v>
+        <v>78.724021741226181</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.94177177718292</v>
+        <v>113.94075268009834</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.59389895467601</v>
+        <v>123.59279352880689</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.3733070251329</v>
+        <v>134.37210518806035</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.41715079825138</v>
+        <v>146.41584124084164</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.71599785774815</v>
+        <v>77.715302764582518</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.88972112670464</v>
+        <v>116.88867566311251</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.43003104264969</v>
+        <v>128.42888236233546</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.70554214798941</v>
+        <v>141.70427473128507</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>157.004354414814</v>
+        <v>157.00295016528062</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.177003561343213</v>
+        <v>78.176304344934977</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.50132161375009</v>
+        <v>120.50024384794366</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.66758342671577</v>
+        <v>133.66638790164671</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>149.19255713123579</v>
+        <v>149.19122275054605</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.56668706218437</v>
+        <v>167.56518834297373</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.320165374632822</v>
+        <v>78.319464877782977</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.539743988651</v>
+        <v>122.53864799116127</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.89750387748154</v>
+        <v>136.89627946395075</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>154.1952223157908</v>
+        <v>154.1938431911812</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>175.16325737412905</v>
+        <v>175.16169071106833</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>117.02096671066475</v>
+        <v>117.01992007320995</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.67596138941532</v>
+        <v>112.67495361375971</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.48491537129397</v>
+        <v>108.48394508042301</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.4435135879546</v>
+        <v>104.4425794434478</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.335891244561111</v>
+        <v>86.335119054926977</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.67596138941532</v>
+        <v>112.67495361375971</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.48491537129397</v>
+        <v>108.48394508042301</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.4435135879546</v>
+        <v>104.4425794434478</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.31277412908339</v>
+        <v>108.31180537784655</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>117.02096671066475</v>
+        <v>117.01992007320995</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.335891244561111</v>
+        <v>86.335119054926977</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19854052639458994</v>
+        <v>0.19853737511444283</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5261020536413597E-2</v>
+        <v>6.5261552666609268E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.52015887209447</v>
+        <v>108.51918826600506</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.52028769826454</v>
+        <v>108.51931709102291</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736688E-2</v>
+        <v>9.6234974214736715E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.394701352796744</v>
+        <v>49.394259565773801</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>60.980775089710718</v>
+        <v>60.980333302687782</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43806961099656405</v>
+        <v>0.43806865608678158</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.801017865795409</v>
+        <v>62.800456172456634</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.239527125054664</v>
+        <v>76.238965431715897</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29746207601010655</v>
+        <v>0.29746096842489311</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.782951723191246</v>
+        <v>77.782256031189135</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.174394625429457</v>
+        <v>93.173698933427346</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14140934187860943</v>
+        <v>0.14140807333503502</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.966744207334855</v>
+        <v>87.965957431324938</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.63265320660783</v>
+        <v>104.63186643059791</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5822889552424853E-2</v>
+        <v>3.5821515968940343E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19854052639458994</v>
+        <v>0.19853737511444283</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.837090015411377</v>
+        <v>7.8370199203491211</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.52015887209447</v>
+        <v>108.51918826600506</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>60.980775089710718</v>
+        <v>60.980333302687782</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.239527125054664</v>
+        <v>76.238965431715897</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.174394625429457</v>
+        <v>93.173698933427346</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.63265320660783</v>
+        <v>104.63186643059791</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11871507806059703</v>
+        <v>0.11871401627098241</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.172330297148861</v>
+        <v>-34.172024659263514</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.77061530041258</v>
+        <v>21.77042058367055</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.845149687571425</v>
+        <v>22.844945360176123</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.443434690835142</v>
+        <v>10.443341284583155</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.276332000998469</v>
+        <v>-19.276159593167371</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.66040120113742</v>
+        <v>106.65944722875126</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.68 HKD</v>
+        <v>112.67 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.52015887209447</v>
+        <v>108.51918826600506</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.394701352796744</v>
+        <v>49.394259565773801</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>60.980775089710718</v>
+        <v>60.980333302687782</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.801017865795409</v>
+        <v>62.800456172456634</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.239527125054664</v>
+        <v>76.238965431715897</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.782951723191246</v>
+        <v>77.782256031189135</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.174394625429457</v>
+        <v>93.173698933427346</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.966744207334855</v>
+        <v>87.965957431324938</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.63265320660783</v>
+        <v>104.63186643059791</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,12 +21684,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21707,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96182190-A33D-4B31-898E-807B2D62543E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59F6847-1533-4F29-AAEA-0F534667F24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>76.5</v>
+        <v>68.849999999999994</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>18729.13392</v>
+        <v>16856.220527999998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19853737511444283</v>
+        <v>0.24435769793756101</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8370199203491211</v>
+        <v>7.8329950000000004</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.51918826600506</v>
+        <v>108.46345520757713</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>60.980333302687782</v>
+        <v>60.954965501855767</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.238965431715897</v>
+        <v>76.20671250438491</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.173698933427346</v>
+        <v>93.133751684564629</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.63186643059791</v>
+        <v>104.58668905760491</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.11871401627098241</v>
+        <v>0.1318367193044952</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>8.3393464052287578E-2</v>
+        <v>9.2659404502541759E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.172024659263514</v>
+        <v>-34.154474662093719</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.77042058367055</v>
+        <v>21.759239776462362</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.844945360176123</v>
+        <v>22.833212700773796</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.443341284583155</v>
+        <v>10.437977815142434</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.276159593167371</v>
+        <v>-19.266259783317711</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>117.02 HKD</v>
+        <v>116.96 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.103900734983174E-2</v>
+        <v>3.1067686942008826E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.67 HKD</v>
+        <v>112.62 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4860642865256095E-2</v>
+        <v>4.4890077269998212E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.48 HKD</v>
+        <v>108.43 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8909012484892338E-2</v>
+        <v>5.8939226881700876E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.44 HKD</v>
+        <v>104.39 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3185657127457102E-2</v>
+        <v>7.3216677504590558E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.34 HKD</v>
+        <v>86.29 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14802879467914332</v>
+        <v>0.1480642637012933</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.51918826600506</v>
+        <v>108.46345520757713</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.394259565773801</v>
+        <v>49.368891764941786</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>60.980333302687782</v>
+        <v>60.954965501855767</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.800456172456634</v>
+        <v>62.768203245125655</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.238965431715897</v>
+        <v>76.20671250438491</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.782256031189135</v>
+        <v>77.742308782326418</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.173698933427346</v>
+        <v>93.133751684564629</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.965957431324938</v>
+        <v>87.920780058331943</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.63186643059791</v>
+        <v>104.58668905760491</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.97265313528817</v>
+        <v>115.91309214191445</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.276159593167371</v>
+        <v>-19.266259783317711</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10405,11 +10405,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8366175.5053710938</v>
+        <v>-8361878.8223999999</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.172024659263514</v>
+        <v>-34.154474662093719</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10422,11 +10422,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5329949.3151149051</v>
+        <v>5327211.970859535</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.77042058367055</v>
+        <v>21.759239776462362</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10439,11 +10439,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5593020.1443898194</v>
+        <v>5590147.6927664997</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.844945360176119</v>
+        <v>22.833212700773792</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10456,11 +10456,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2556793.9541336307</v>
+        <v>2555480.8412260348</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.443341284583155</v>
+        <v>10.437977815142435</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14044,20 +14044,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>8.3393464052287578E-2</v>
+        <v>9.2659404502541759E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>8.3393464052287578E-2</v>
+        <v>9.2659404502541759E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>8.3393464052287578E-2</v>
+        <v>9.2659404502541759E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>8.6444444444444449E-2</v>
+        <v>9.6049382716049403E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15207,22 +15207,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0816222447301538</v>
+        <v>9.0769581241144941</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.210319227017086</v>
+        <v>10.205075432558795</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.722948450420593</v>
+        <v>7.7189821146591395</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.828587975279969</v>
+        <v>10.823026651647146</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15264,22 +15264,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11871401627098241</v>
+        <v>0.1318367193044952</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.13346822518976584</v>
+        <v>0.14822186539664192</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.10095357451530187</v>
+        <v>0.11211302998778708</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.14155016961150288</v>
+        <v>0.15719719174505659</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15321,15 +15321,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6557359316484613E-2</v>
+        <v>1.8397065907205128E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9087641827273558E-2</v>
+        <v>2.1208490919192847E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2222916669710058E-3</v>
+        <v>5.8025462966344509E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.443341284583155</v>
+        <v>10.437977815142434</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8370199203491211</v>
+        <v>7.8329950000000004</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26112929.032424252</v>
+        <v>26099518.008781854</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.51931709102291</v>
+        <v>108.46358396643326</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18629,23 +18629,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18660,23 +18660,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.284703765363219</v>
+        <v>97.23474049005921</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.85530179066743</v>
+        <v>101.80299115716008</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.76942139572824</v>
+        <v>102.71664129058024</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.68354100078909</v>
+        <v>103.63029142400042</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.59766060584997</v>
+        <v>104.54394155742064</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18691,23 +18691,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.448122945754179</v>
+        <v>93.400130053627549</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.9697294190516</v>
+        <v>101.91736001804148</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.72388591876258</v>
+        <v>103.67061562171506</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.4946541534907</v>
+        <v>105.44047442898555</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.28203412323595</v>
+        <v>107.22693643985293</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18722,23 +18722,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>90.049752988990932</v>
+        <v>90.003505424620499</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>102.07642184644946</v>
+        <v>102.02399765056495</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.62272896609556</v>
+        <v>104.56899704311004</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.21711141759846</v>
+        <v>107.16204707708324</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.86003386487471</v>
+        <v>109.80361217775997</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18753,23 +18753,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>87.039541838477987</v>
+        <v>86.994840252073416</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.17590196523533</v>
+        <v>102.12342667855884</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.46919188246511</v>
+        <v>105.41502523482002</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.85525259185478</v>
+        <v>108.7993469382111</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.33587510859304</v>
+        <v>112.27818188409493</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18784,23 +18784,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.335119054926977</v>
+        <v>86.290779244506723</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.4425794434478</v>
+        <v>104.38894004127849</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.48394508042301</v>
+        <v>108.42823012211682</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.67495361375971</v>
+        <v>112.61708624602996</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>117.01992007320995</v>
+        <v>116.95982122666598</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18815,23 +18815,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.973283973971846</v>
+        <v>83.930157149887634</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.52906462341173</v>
+        <v>104.47538080436401</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.23462721841493</v>
+        <v>109.17852672634162</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.15664265278586</v>
+        <v>114.09801432228903</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.3034286179023</v>
+        <v>119.24215701180147</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.619086447672117</v>
+        <v>83.576141531614908</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.63667050002253</v>
+        <v>106.58190426114345</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>112.02994945273939</v>
+        <v>111.9724133449017</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.71683507030953</v>
+        <v>117.65637830361453</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.7113700635023</v>
+        <v>123.64783463602517</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18878,23 +18878,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.765972273711284</v>
+        <v>81.723979076167467</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.71185825054673</v>
+        <v>106.65705339689951</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.6956888033976</v>
+        <v>112.6378107865324</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>119.05701407494678</v>
+        <v>118.99586902191309</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.81748703966664</v>
+        <v>125.75286995702452</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18910,23 +18910,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.663891934620807</v>
+        <v>81.621951163284677</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.67190931320202</v>
+        <v>108.61609782061709</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.28931747216362</v>
+        <v>115.23010742489487</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.3773281711059</v>
+        <v>122.31447787808214</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.96729563405452</v>
+        <v>129.90054730136757</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18942,23 +18942,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.209924140922965</v>
+        <v>80.168730095334553</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.7372754005623</v>
+        <v>108.68143033739852</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.87972566303972</v>
+        <v>115.82021239516341</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.58951218351588</v>
+        <v>123.52603933955466</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.9098014887393</v>
+        <v>131.84205552794597</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18974,23 +18974,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.724021741226181</v>
+        <v>78.683590822293823</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.94075268009834</v>
+        <v>113.88223522592351</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.59279352880689</v>
+        <v>123.52931899961919</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.37210518806035</v>
+        <v>134.30309464246744</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.41584124084164</v>
+        <v>146.34064529840009</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.715302764582518</v>
+        <v>77.675389901438834</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.88867566311251</v>
+        <v>116.82864422079899</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.42888236233546</v>
+        <v>128.36292412472875</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.70427473128507</v>
+        <v>141.63149854534703</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>157.00295016528062</v>
+        <v>156.92231691751365</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19038,23 +19038,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.176304344934977</v>
+        <v>78.136154721560928</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.50024384794366</v>
+        <v>120.43835758397256</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.66638790164671</v>
+        <v>133.59773979686625</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>149.19122275054605</v>
+        <v>149.1146014334559</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.56518834297373</v>
+        <v>167.47913056294757</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19070,23 +19070,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.319464877782977</v>
+        <v>78.279241730320976</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.53864799116127</v>
+        <v>122.47571484784072</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.89627946395075</v>
+        <v>136.82597255819661</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>154.1938431911812</v>
+        <v>154.11465263871651</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>175.16169071106833</v>
+        <v>175.07173153519605</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>117.01992007320995</v>
+        <v>116.95982122666598</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.67495361375971</v>
+        <v>112.61708624602996</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.48394508042301</v>
+        <v>108.42823012211682</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.4425794434478</v>
+        <v>104.38894004127849</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.335119054926977</v>
+        <v>86.290779244506723</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.67495361375971</v>
+        <v>112.61708624602996</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.48394508042301</v>
+        <v>108.42823012211682</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.4425794434478</v>
+        <v>104.38894004127849</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.31180537784655</v>
+        <v>108.25617882668986</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19715,7 +19715,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>117.01992007320995</v>
+        <v>116.95982122666598</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.335119054926977</v>
+        <v>86.290779244506723</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>76.5</v>
+        <v>68.849999999999994</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19853737511444283</v>
+        <v>0.24435769793756101</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5261552666609268E-2</v>
+        <v>6.5292124029553048E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.51918826600506</v>
+        <v>108.46345520757713</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.51931709102291</v>
+        <v>108.46358396643326</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20071,11 +20071,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.394259565773801</v>
+        <v>49.368891764941786</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>60.980333302687782</v>
+        <v>60.954965501855767</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20083,7 +20083,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43806865608678158</v>
+        <v>0.43801379565863652</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20096,11 +20096,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.800456172456634</v>
+        <v>62.768203245125655</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.238965431715897</v>
+        <v>76.20671250438491</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29746096842489311</v>
+        <v>0.29739733665555212</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20142,11 +20142,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.782256031189135</v>
+        <v>77.742308782326418</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.173698933427346</v>
+        <v>93.133751684564629</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14140807333503502</v>
+        <v>0.14133519436269615</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20167,11 +20167,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.965957431324938</v>
+        <v>87.920780058331943</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.63186643059791</v>
+        <v>104.58668905760491</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5821515968940343E-2</v>
+        <v>3.5742602359042142E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>76.5</v>
+        <v>68.849999999999994</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20308,14 +20308,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>18729.13392</v>
+        <v>16856.220527999998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19853737511444283</v>
+        <v>0.24435769793756101</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20323,13 +20323,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8370199203491211</v>
+        <v>7.8329950000000004</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.51918826600506</v>
+        <v>108.46345520757713</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>60.980333302687782</v>
+        <v>60.954965501855767</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.238965431715897</v>
+        <v>76.20671250438491</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.173698933427346</v>
+        <v>93.133751684564629</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.63186643059791</v>
+        <v>104.58668905760491</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20514,22 +20514,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20719,10 +20719,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20738,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.11871401627098241</v>
+        <v>0.1318367193044952</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>8.3393464052287578E-2</v>
+        <v>9.2659404502541759E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20888,22 +20888,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20911,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.172024659263514</v>
+        <v>-34.154474662093719</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.77042058367055</v>
+        <v>21.759239776462362</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.844945360176123</v>
+        <v>22.833212700773796</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.443341284583155</v>
+        <v>10.437977815142434</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21066,33 +21066,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21155,23 +21155,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.276159593167371</v>
+        <v>-19.266259783317711</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.65944722875126</v>
+        <v>106.60466929224732</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21215,13 +21215,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>117.02 HKD</v>
+        <v>116.96 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.67 HKD</v>
+        <v>112.62 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.48 HKD</v>
+        <v>108.43 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.44 HKD</v>
+        <v>104.39 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.34 HKD</v>
+        <v>86.29 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.51918826600506</v>
+        <v>108.46345520757713</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21385,13 +21385,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21404,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21484,11 +21484,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.394259565773801</v>
+        <v>49.368891764941786</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>60.980333302687782</v>
+        <v>60.954965501855767</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21505,11 +21505,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.800456172456634</v>
+        <v>62.768203245125655</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.238965431715897</v>
+        <v>76.20671250438491</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21545,11 +21545,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.782256031189135</v>
+        <v>77.742308782326418</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.173698933427346</v>
+        <v>93.133751684564629</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21566,11 +21566,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.965957431324938</v>
+        <v>87.920780058331943</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.63186643059791</v>
+        <v>104.58668905760491</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21588,13 +21588,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21602,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21645,22 +21645,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21684,15 +21684,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21707,12 +21704,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59F6847-1533-4F29-AAEA-0F534667F24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1822D8-B1CC-4318-A5E0-003A4727F273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="558">
   <si>
     <t>Sales</t>
   </si>
@@ -2496,9 +2496,6 @@
   </si>
   <si>
     <t xml:space="preserve">Taxes = </t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <r>
@@ -4992,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5354,7 +5351,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F3" s="429">
         <v>46057</v>
@@ -5362,13 +5359,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C4" s="420" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E4" s="430" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F4" s="431" t="s">
         <v>324</v>
@@ -5379,13 +5376,13 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E5" s="433" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F5" s="432" t="s">
-        <v>497</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5393,7 +5390,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5434,7 +5431,7 @@
         <v>16856.220527999998</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
@@ -5446,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5466,7 +5463,7 @@
         <v>319</v>
       </c>
       <c r="C15" s="417" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>353</v>
@@ -5481,7 +5478,7 @@
         <v>320</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
@@ -5492,7 +5489,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C17" s="456">
         <v>-0.02</v>
@@ -5501,7 +5498,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5630,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6004,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6204,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6327,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6354,7 +6351,7 @@
         <v>124</v>
       </c>
       <c r="F117" s="342" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6468,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6509,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6700,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7356,7 +7353,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -13683,7 +13680,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -14738,7 +14735,7 @@
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="451" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
@@ -16404,14 +16401,14 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
         <v>0.2269433297967331</v>
       </c>
       <c r="E17" s="308" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
@@ -16465,26 +16462,26 @@
         <v>102</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>529</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>552</v>
+      </c>
+      <c r="K20" s="121" t="s">
         <v>530</v>
-      </c>
-      <c r="J20" s="121" t="s">
-        <v>553</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>531</v>
       </c>
       <c r="L20" s="122" t="s">
         <v>419</v>
@@ -19390,7 +19387,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19556,7 +19553,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="450" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F18" s="319"/>
     </row>
@@ -19857,7 +19854,7 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
@@ -20223,7 +20220,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
@@ -20232,7 +20229,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C4" s="423" t="str">
         <f>Thesis!C4</f>
@@ -20240,7 +20237,7 @@
       </c>
       <c r="D4" s="349"/>
       <c r="E4" s="434" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F4" s="437" t="str">
         <f>Thesis!F4</f>
@@ -20256,11 +20253,11 @@
         <v>9898.HK</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F5" s="439" t="str">
         <f>Thesis!F5</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -20311,7 +20308,7 @@
         <v>16856.220527999998</v>
       </c>
       <c r="D10" s="343" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
@@ -20323,13 +20320,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
-        <v>498</v>
-      </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="B12" s="471" t="s">
+        <v>497</v>
+      </c>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20372,7 +20369,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C17" s="424">
         <f>Terminal_Growth</f>
@@ -20514,22 +20511,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
+        <v>498</v>
+      </c>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
-        <v>500</v>
-      </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20542,7 +20539,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C33" s="470"/>
       <c r="D33" s="470"/>
@@ -20568,7 +20565,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C36" s="470"/>
       <c r="D36" s="470"/>
@@ -20603,7 +20600,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C40" s="470"/>
       <c r="D40" s="470"/>
@@ -20625,7 +20622,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C43" s="470"/>
       <c r="D43" s="470"/>
@@ -20677,7 +20674,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20695,7 +20692,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C51" s="470"/>
       <c r="D51" s="470"/>
@@ -20717,12 +20714,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
-        <v>507</v>
-      </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+        <v>506</v>
+      </c>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20738,22 +20735,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
+        <v>507</v>
+      </c>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
-        <v>509</v>
-      </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20888,22 +20885,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
-        <v>510</v>
-      </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="B73" s="471" t="s">
+        <v>509</v>
+      </c>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20911,13 +20908,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
-        <v>511</v>
-      </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="B77" s="471" t="s">
+        <v>510</v>
+      </c>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20965,7 +20962,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -21009,7 +21006,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -21066,33 +21063,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
-        <v>514</v>
-      </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="B96" s="471" t="s">
+        <v>513</v>
+      </c>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
-        <v>515</v>
-      </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="B97" s="472" t="s">
+        <v>514</v>
+      </c>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
-        <v>516</v>
-      </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="B98" s="472" t="s">
+        <v>515</v>
+      </c>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21136,7 +21133,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C104" s="368">
         <v>0</v>
@@ -21155,23 +21152,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
-        <v>517</v>
-      </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="B107" s="471" t="s">
+        <v>516</v>
+      </c>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
-        <v>536</v>
-      </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="B108" s="471" t="s">
+        <v>535</v>
+      </c>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21215,13 +21212,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
-        <v>518</v>
-      </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="B114" s="471" t="s">
+        <v>517</v>
+      </c>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21364,7 +21361,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C124" s="470"/>
       <c r="D124" s="470"/>
@@ -21385,13 +21382,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
-        <v>520</v>
-      </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="B127" s="475" t="s">
+        <v>519</v>
+      </c>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21404,22 +21401,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
+        <v>520</v>
+      </c>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
-        <v>522</v>
-      </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21588,13 +21585,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
-        <v>523</v>
-      </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="B149" s="477" t="s">
+        <v>522</v>
+      </c>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21602,13 +21599,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
-        <v>524</v>
-      </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="B152" s="473" t="s">
+        <v>523</v>
+      </c>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21627,7 +21624,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
@@ -21641,30 +21638,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21684,12 +21681,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,15 +21704,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1822D8-B1CC-4318-A5E0-003A4727F273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFAE5E3-E623-4BCC-9E85-6F5A260520F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>68.849999999999994</v>
+        <v>68.55</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>16856.220527999998</v>
+        <v>16782.772944</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24435769793756101</v>
+        <v>0.24632545477758799</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5484,7 +5484,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8329950000000004</v>
+        <v>7.8334089999999996</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.46345520757713</v>
+        <v>108.46918786417346</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>60.954965501855767</v>
+        <v>60.957574813005664</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.20671250438491</v>
+        <v>76.210030013989268</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.133751684564629</v>
+        <v>93.137860625759643</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.58668905760491</v>
+        <v>104.59133596507058</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.1318367193044952</v>
+        <v>0.13242068375971852</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>9.2659404502541759E-2</v>
+        <v>9.3064916119620714E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.154474662093719</v>
+        <v>-34.156279840382496</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.759239776462362</v>
+        <v>21.760389825104983</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.833212700773796</v>
+        <v>22.834419512479677</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.437977815142434</v>
+        <v>10.438529497202163</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.266259783317711</v>
+        <v>-19.267278069624581</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.96 HKD</v>
+        <v>116.97 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1067686942008826E-2</v>
+        <v>3.1064735624094647E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4890077269998212E-2</v>
+        <v>4.4887048276317093E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8939226881700876E-2</v>
+        <v>5.8936117621068339E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3216677504590558E-2</v>
+        <v>7.3213485302592557E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.29 HKD</v>
+        <v>86.3 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1480642637012933</v>
+        <v>0.14806061370012349</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.46345520757713</v>
+        <v>108.46918786417346</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.368891764941786</v>
+        <v>49.37150107609169</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>60.954965501855767</v>
+        <v>60.957574813005664</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,11 +6607,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.768203245125655</v>
+        <v>62.771520754730012</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.20671250438491</v>
+        <v>76.210030013989268</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,11 +6654,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.742308782326418</v>
+        <v>77.746417723521432</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.133751684564629</v>
+        <v>93.137860625759643</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,11 +6675,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.920780058331943</v>
+        <v>87.925426965797612</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.58668905760491</v>
+        <v>104.59133596507058</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9992,11 +9992,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.91309214191445</v>
+        <v>115.91921853675404</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.266259783317711</v>
+        <v>-19.267278069624581</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10402,11 +10402,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8361878.8223999999</v>
+        <v>-8362320.77568</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.154474662093719</v>
+        <v>-34.156279840382496</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10419,11 +10419,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5327211.970859535</v>
+        <v>5327493.531840479</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.759239776462362</v>
+        <v>21.760389825104983</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10436,11 +10436,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5590147.6927664997</v>
+        <v>5590443.1507802997</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.833212700773792</v>
+        <v>22.834419512479677</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10453,11 +10453,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2555480.8412260348</v>
+        <v>2555615.9069407787</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.437977815142435</v>
+        <v>10.438529497202165</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14041,20 +14041,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.2659404502541759E-2</v>
+        <v>9.3064916119620714E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.2659404502541759E-2</v>
+        <v>9.3064916119620714E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.2659404502541759E-2</v>
+        <v>9.3064916119620714E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>9.6049382716049403E-2</v>
+        <v>9.6469730123997094E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15204,22 +15204,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0769581241144941</v>
+        <v>9.077437871728705</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.205075432558795</v>
+        <v>10.205614804948166</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7189821146591395</v>
+        <v>7.7193900886965876</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.823026651647146</v>
+        <v>10.823598684826507</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15261,22 +15261,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1318367193044952</v>
+        <v>0.13242068375971852</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.14822186539664192</v>
+        <v>0.1488784070743715</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.11211302998778708</v>
+        <v>0.11260962930264899</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.15719719174505659</v>
+        <v>0.15789348920242899</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15318,15 +15318,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8397065907205128E-2</v>
+        <v>1.8477578230650226E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1208490919192847E-2</v>
+        <v>2.1301307072012068E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8025462966344509E-3</v>
+        <v>5.8279403723308816E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.437977815142434</v>
+        <v>10.438529497202163</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8329950000000004</v>
+        <v>7.8334089999999996</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26099518.008781854</v>
+        <v>26100897.455654427</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.46358396643326</v>
+        <v>108.46931662983495</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18626,23 +18626,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18657,23 +18657,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.23474049005921</v>
+        <v>97.239879671504212</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.80299115716008</v>
+        <v>101.80837178594115</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.71664129058024</v>
+        <v>102.72207020882853</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.63029142400042</v>
+        <v>103.63576863171592</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.54394155742064</v>
+        <v>104.54946705460334</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18688,23 +18688,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.400130053627549</v>
+        <v>93.405066563077909</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.91736001804148</v>
+        <v>101.9227466915996</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.67061562171506</v>
+        <v>103.67609496069936</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.44047442898555</v>
+        <v>105.44604731093091</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.22693643985293</v>
+        <v>107.23260374229422</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18719,23 +18719,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>90.003505424620499</v>
+        <v>90.00826241109192</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>102.02399765056495</v>
+        <v>102.02938996027883</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.56899704311004</v>
+        <v>104.57452386455903</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.16204707708324</v>
+        <v>107.16771094990455</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.80361217775997</v>
+        <v>109.80941566613723</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18750,23 +18750,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.994840252073416</v>
+        <v>86.99943822052154</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.12342667855884</v>
+        <v>102.12882424342961</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.41502523482002</v>
+        <v>105.42059677169028</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.7993469382111</v>
+        <v>108.80509734780952</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.27818188409493</v>
+        <v>112.28411616176267</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18781,23 +18781,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.290779244506723</v>
+        <v>86.295340000974363</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.38894004127849</v>
+        <v>104.39445734611233</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.42823012211682</v>
+        <v>108.4339609169495</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.61708624602996</v>
+        <v>112.62303843592741</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.95982122666598</v>
+        <v>116.96600294464073</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18812,23 +18812,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.930157149887634</v>
+        <v>83.934593139577402</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.47538080436401</v>
+        <v>104.48090267788147</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.17852672634162</v>
+        <v>109.18429717686081</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.09801432228903</v>
+        <v>114.10404478419144</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.24215701180147</v>
+        <v>119.24845935886064</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18844,23 +18844,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.576141531614908</v>
+        <v>83.580558810394479</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.58190426114345</v>
+        <v>106.58753747147539</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.9724133449017</v>
+        <v>111.97833146167883</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.65637830361453</v>
+        <v>117.66259683696194</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.64783463602517</v>
+        <v>123.65436983789102</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.723979076167467</v>
+        <v>81.728298461962737</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.65705339689951</v>
+        <v>106.66269057911477</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.6378107865324</v>
+        <v>112.64376407179117</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.99586902191309</v>
+        <v>119.00215835182777</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.75286995702452</v>
+        <v>125.75951641705188</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.621951163284677</v>
+        <v>81.626265156563306</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.61609782061709</v>
+        <v>108.62183854488637</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.23010742489487</v>
+        <v>115.23619772170647</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.31447787808214</v>
+        <v>122.32094260758107</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.90054730136757</v>
+        <v>129.90741298002339</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.168730095334553</v>
+        <v>80.172967281016327</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.68143033739852</v>
+        <v>108.68717451470997</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.82021239516341</v>
+        <v>115.82633388099757</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.52603933955466</v>
+        <v>123.53256810413149</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.84205552794597</v>
+        <v>131.84902382180911</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.683590822293823</v>
+        <v>78.687749513394792</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.88223522592351</v>
+        <v>113.88825428317855</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.52931899961919</v>
+        <v>123.53584793753703</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.30309464246744</v>
+        <v>134.310193010484</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.34064529840009</v>
+        <v>146.34837989125421</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.675389901438834</v>
+        <v>77.679495305747039</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.82864422079899</v>
+        <v>116.83481900563</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.36292412472875</v>
+        <v>128.3697085348538</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.63149854534703</v>
+        <v>141.63898424403544</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.92231691751365</v>
+        <v>156.93061078712594</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19035,23 +19035,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.136154721560928</v>
+        <v>78.140284478831887</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.43835758397256</v>
+        <v>120.44472315423523</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.59773979686625</v>
+        <v>133.60480088451865</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>149.1146014334559</v>
+        <v>149.12248263917522</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.47913056294757</v>
+        <v>167.48798239549092</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19067,23 +19067,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.279241730320976</v>
+        <v>78.28337905021921</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.47571484784072</v>
+        <v>122.48218809925309</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.82597255819661</v>
+        <v>136.83320426875417</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>154.11465263871651</v>
+        <v>154.1227981138754</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>175.07173153519605</v>
+        <v>175.08098466211052</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.95982122666598</v>
+        <v>116.96600294464073</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.61708624602996</v>
+        <v>112.62303843592741</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.42823012211682</v>
+        <v>108.4339609169495</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.38894004127849</v>
+        <v>104.39445734611233</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.290779244506723</v>
+        <v>86.295340000974363</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.61708624602996</v>
+        <v>112.62303843592741</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.42823012211682</v>
+        <v>108.4339609169495</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.38894004127849</v>
+        <v>104.39445734611233</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.25617882668986</v>
+        <v>108.2619005280358</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.95982122666598</v>
+        <v>116.96600294464073</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.290779244506723</v>
+        <v>86.295340000974363</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>68.849999999999994</v>
+        <v>68.55</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24435769793756101</v>
+        <v>0.24632545477758799</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5292124029553048E-2</v>
+        <v>6.528897803445588E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.46345520757713</v>
+        <v>108.46918786417346</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.46358396643326</v>
+        <v>108.46931662983495</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736715E-2</v>
+        <v>9.6234974214736702E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20068,11 +20068,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.368891764941786</v>
+        <v>49.37150107609169</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>60.954965501855767</v>
+        <v>60.957574813005664</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43801379565863652</v>
+        <v>0.43801944115837266</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.768203245125655</v>
+        <v>62.771520754730012</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.20671250438491</v>
+        <v>76.210030013989268</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29739733665555212</v>
+        <v>0.29740388478412449</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20139,11 +20139,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.742308782326418</v>
+        <v>77.746417723521432</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.133751684564629</v>
+        <v>93.137860625759643</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14133519436269615</v>
+        <v>0.14134269408942113</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20164,11 +20164,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.920780058331943</v>
+        <v>87.925426965797612</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.58668905760491</v>
+        <v>104.59133596507058</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5742602359042142E-2</v>
+        <v>3.5750723089756797E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>68.849999999999994</v>
+        <v>68.55</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20305,14 +20305,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>16856.220527999998</v>
+        <v>16782.772944</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24435769793756101</v>
+        <v>0.24632545477758799</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20320,13 +20320,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8329950000000004</v>
+        <v>7.8334089999999996</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.46345520757713</v>
+        <v>108.46918786417346</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>60.954965501855767</v>
+        <v>60.957574813005664</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.20671250438491</v>
+        <v>76.210030013989268</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.133751684564629</v>
+        <v>93.137860625759643</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.58668905760491</v>
+        <v>104.59133596507058</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20511,22 +20511,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20716,10 +20716,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20735,22 +20735,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.1318367193044952</v>
+        <v>0.13242068375971852</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>9.2659404502541759E-2</v>
+        <v>9.3064916119620714E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20885,22 +20885,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20908,13 +20908,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.154474662093719</v>
+        <v>-34.156279840382496</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.759239776462362</v>
+        <v>21.760389825104983</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.833212700773796</v>
+        <v>22.834419512479677</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.437977815142434</v>
+        <v>10.438529497202163</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21063,33 +21063,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21152,23 +21152,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.266259783317711</v>
+        <v>-19.267278069624581</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21200,7 +21200,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.60466929224732</v>
+        <v>106.61030370578736</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,13 +21212,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.96 HKD</v>
+        <v>116.97 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.29 HKD</v>
+        <v>86.3 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.46345520757713</v>
+        <v>108.46918786417346</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21382,13 +21382,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21401,22 +21401,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21481,11 +21481,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.368891764941786</v>
+        <v>49.37150107609169</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>60.954965501855767</v>
+        <v>60.957574813005664</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21502,11 +21502,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.768203245125655</v>
+        <v>62.771520754730012</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.20671250438491</v>
+        <v>76.210030013989268</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21542,11 +21542,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.742308782326418</v>
+        <v>77.746417723521432</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.133751684564629</v>
+        <v>93.137860625759643</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21563,11 +21563,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.920780058331943</v>
+        <v>87.925426965797612</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.58668905760491</v>
+        <v>104.59133596507058</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21585,13 +21585,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21642,22 +21642,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21681,15 +21681,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,12 +21701,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFAE5E3-E623-4BCC-9E85-6F5A260520F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449A649F-A37C-461B-BF55-36E6CD2ABA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449A649F-A37C-461B-BF55-36E6CD2ABA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0449F7-36EF-4559-9A0B-1AE27BC4FF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>68.55</v>
+        <v>68.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>16782.772944</v>
+        <v>16819.496736000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24632545477758799</v>
+        <v>0.24509071763545984</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5484,7 +5484,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8334089999999996</v>
+        <v>7.8278480000000004</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.46918786417346</v>
+        <v>108.3921847160278</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>60.957574813005664</v>
+        <v>60.922525587632123</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.210030013989268</v>
+        <v>76.165468006960538</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.137860625759643</v>
+        <v>93.082667819031371</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.59133596507058</v>
+        <v>104.5289169978806</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.13242068375971852</v>
+        <v>0.132037754376061</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>9.3064916119620714E-2</v>
+        <v>9.2861717612809314E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.156279840382496</v>
+        <v>-34.13203202283686</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.760389825104983</v>
+        <v>21.744941949497139</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.834419512479677</v>
+        <v>22.818209174565634</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.438529497202163</v>
+        <v>10.431119101225912</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.267278069624581</v>
+        <v>-19.253600074087114</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.97 HKD</v>
+        <v>116.88 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1064735624094647E-2</v>
+        <v>3.1104404853276143E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.62 HKD</v>
+        <v>112.54 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4887048276317093E-2</v>
+        <v>4.4927761572042528E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.43 HKD</v>
+        <v>108.36 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8936117621068339E-2</v>
+        <v>5.8977909812878954E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.39 HKD</v>
+        <v>104.32 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3213485302592557E-2</v>
+        <v>7.3256392338797729E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.3 HKD</v>
+        <v>86.23 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14806061370012349</v>
+        <v>0.14810967418814222</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.46918786417346</v>
+        <v>108.3921847160278</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.37150107609169</v>
+        <v>49.336451850718149</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>60.957574813005664</v>
+        <v>60.922525587632123</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,11 +6607,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.771520754730012</v>
+        <v>62.726958747701275</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.210030013989268</v>
+        <v>76.165468006960538</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,11 +6654,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.746417723521432</v>
+        <v>77.691224916793161</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.137860625759643</v>
+        <v>93.082667819031371</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,11 +6675,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.925426965797612</v>
+        <v>87.863007998607628</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.59133596507058</v>
+        <v>104.5289169978806</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9992,11 +9992,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.91921853675404</v>
+        <v>115.83692655196393</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.267278069624581</v>
+        <v>-19.253600074087114</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10402,11 +10402,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8362320.77568</v>
+        <v>-8356384.2969599999</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.156279840382496</v>
+        <v>-34.13203202283686</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10419,11 +10419,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5327493.531840479</v>
+        <v>5323711.5013693832</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.760389825104983</v>
+        <v>21.744941949497139</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10436,11 +10436,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5590443.1507802997</v>
+        <v>5586474.4502616003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.834419512479677</v>
+        <v>22.818209174565634</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10453,11 +10453,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2555615.9069407787</v>
+        <v>2553801.6546709836</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.438529497202165</v>
+        <v>10.431119101225914</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14041,20 +14041,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.3064916119620714E-2</v>
+        <v>9.2861717612809314E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.3064916119620714E-2</v>
+        <v>9.2861717612809314E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.3064916119620714E-2</v>
+        <v>9.2861717612809314E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>9.6469730123997094E-2</v>
+        <v>9.625909752547307E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15204,22 +15204,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.077437871728705</v>
+        <v>9.0709937256353914</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.205614804948166</v>
+        <v>10.198369756983695</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7193900886965876</v>
+        <v>7.7139100316380027</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.823598684826507</v>
+        <v>10.815914925139467</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15261,22 +15261,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.13242068375971852</v>
+        <v>0.132037754376061</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.1488784070743715</v>
+        <v>0.14844788583673499</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.11260962930264899</v>
+        <v>0.11228398881569145</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.15789348920242899</v>
+        <v>0.15743689847364581</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15318,15 +15318,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8477578230650226E-2</v>
+        <v>1.8437234173378062E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1301307072012068E-2</v>
+        <v>2.1254797667924704E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8279403723308816E-3</v>
+        <v>5.815215611692604E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.438529497202163</v>
+        <v>10.431119101225912</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8334089999999996</v>
+        <v>7.8278480000000004</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26100897.455654427</v>
+        <v>26082368.218798432</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.46931662983495</v>
+        <v>108.39231339027749</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18626,23 +18626,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18657,23 +18657,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.239879671504212</v>
+        <v>97.17084829948557</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.80837178594115</v>
+        <v>101.73609720465713</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.72207020882853</v>
+        <v>102.64914698569142</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.63576863171592</v>
+        <v>103.56219676672573</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.54946705460334</v>
+        <v>104.47524654776008</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18688,23 +18688,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.405066563077909</v>
+        <v>93.338757555702301</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.9227466915996</v>
+        <v>101.8503909146509</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.67609496069936</v>
+        <v>103.60249446772416</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.44604731093091</v>
+        <v>105.37119031455858</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.23260374229422</v>
+        <v>107.15647845515412</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18719,23 +18719,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>90.00826241109192</v>
+        <v>89.94436482228123</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>102.02938996027883</v>
+        <v>101.95695847641669</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.57452386455903</v>
+        <v>104.50028556968502</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.16771094990455</v>
+        <v>107.09163173067925</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.80941566613723</v>
+        <v>109.7314610795046</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18750,23 +18750,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.99943822052154</v>
+        <v>86.937676620183254</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.12882424342961</v>
+        <v>102.05632217037078</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.42059677169028</v>
+        <v>105.34575784286029</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.80509734780952</v>
+        <v>108.72785573482199</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.28411616176267</v>
+        <v>112.20440476536098</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18781,23 +18781,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.295340000974363</v>
+        <v>86.234078245620424</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.39445734611233</v>
+        <v>104.32034688190681</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.4339609169495</v>
+        <v>108.35698277669677</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.62303843592741</v>
+        <v>112.54308643587966</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.96600294464073</v>
+        <v>116.88296783918729</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18812,23 +18812,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.934593139577402</v>
+        <v>83.875007297391818</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.48090267788147</v>
+        <v>104.40673084544025</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.18429717686081</v>
+        <v>109.1067863668673</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.10404478419144</v>
+        <v>114.02304140583539</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.24845935886064</v>
+        <v>119.16380391925644</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18844,23 +18844,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.580558810394479</v>
+        <v>83.521224300024272</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.58753747147539</v>
+        <v>106.51187012206483</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.97833146167883</v>
+        <v>111.8988371442931</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.66259683696194</v>
+        <v>117.57906721390636</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.65436983789102</v>
+        <v>123.56658660703094</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.728298461962737</v>
+        <v>81.670278886099041</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.66269057911477</v>
+        <v>106.58696987790916</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.64376407179117</v>
+        <v>112.56379735844796</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>119.00215835182777</v>
+        <v>118.91767776328778</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.75951641705188</v>
+        <v>125.67023872571787</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.626265156563306</v>
+        <v>81.568318014963069</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.62183854488637</v>
+        <v>108.54472702879573</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.23619772170647</v>
+        <v>115.15439061888186</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.32094260758107</v>
+        <v>122.23410598742748</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.90741298002339</v>
+        <v>129.81519066358598</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.172967281016327</v>
+        <v>80.116051847256941</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.68717451470997</v>
+        <v>108.6100166160893</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.82633388099757</v>
+        <v>115.744107835771</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.53256810413149</v>
+        <v>123.44487134130102</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.84902382180911</v>
+        <v>131.75542314023193</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.687749513394792</v>
+        <v>78.631888447664153</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.88825428317855</v>
+        <v>113.8074040962333</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.53584793753703</v>
+        <v>123.44814884632648</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.310193010484</v>
+        <v>134.21484512512131</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.34837989125421</v>
+        <v>146.2444860002835</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.679495305747039</v>
+        <v>77.624350007780947</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.83481900563</v>
+        <v>116.75187702870907</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.3697085348538</v>
+        <v>128.27857784715931</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.63898424403544</v>
+        <v>141.53843359088035</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.93061078712594</v>
+        <v>156.81920448540123</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19035,23 +19035,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.140284478831887</v>
+        <v>78.084812062928833</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.44472315423523</v>
+        <v>120.35921847734926</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.60480088451865</v>
+        <v>133.50995376269483</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>149.12248263917522</v>
+        <v>149.01661939037047</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.48798239549092</v>
+        <v>167.36908133082022</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19067,23 +19067,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.28337905021921</v>
+        <v>78.227805050329991</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.48218809925309</v>
+        <v>122.39523700962917</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.83320426875417</v>
+        <v>136.73606527742379</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>154.1227981138754</v>
+        <v>154.0133851009316</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>175.08098466211052</v>
+        <v>174.95669326411178</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.96600294464073</v>
+        <v>116.88296783918729</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.62303843592741</v>
+        <v>112.54308643587966</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.4339609169495</v>
+        <v>108.35698277669677</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.39445734611233</v>
+        <v>104.32034688190681</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.295340000974363</v>
+        <v>86.234078245620424</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.62303843592741</v>
+        <v>112.54308643587966</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.4339609169495</v>
+        <v>108.35698277669677</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.39445734611233</v>
+        <v>104.32034688190681</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.2619005280358</v>
+        <v>108.18504453483585</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.96600294464073</v>
+        <v>116.88296783918729</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.295340000974363</v>
+        <v>86.234078245620424</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>68.55</v>
+        <v>68.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24632545477758799</v>
+        <v>0.24509071763545984</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.528897803445588E-2</v>
+        <v>6.5331263987198365E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.46918786417346</v>
+        <v>108.3921847160278</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.46931662983495</v>
+        <v>108.39231339027749</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736702E-2</v>
+        <v>9.6234974214736715E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20068,11 +20068,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.37150107609169</v>
+        <v>49.336451850718149</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>60.957574813005664</v>
+        <v>60.922525587632123</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43801944115837266</v>
+        <v>0.43794355887151337</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.771520754730012</v>
+        <v>62.726958747701275</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.210030013989268</v>
+        <v>76.165468006960538</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29740388478412449</v>
+        <v>0.29731587008322324</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20139,11 +20139,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.746417723521432</v>
+        <v>77.691224916793161</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.137860625759643</v>
+        <v>93.082667819031371</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14134269408942113</v>
+        <v>0.14124188876813581</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20164,11 +20164,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.925426965797612</v>
+        <v>87.863007998607628</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.59133596507058</v>
+        <v>104.5289169978806</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5750723089756797E-2</v>
+        <v>3.5641570730107652E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>68.55</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20305,14 +20305,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>16782.772944</v>
+        <v>16819.496736000001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24632545477758799</v>
+        <v>0.24509071763545984</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20320,13 +20320,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8334089999999996</v>
+        <v>7.8278480000000004</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.46918786417346</v>
+        <v>108.3921847160278</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>60.957574813005664</v>
+        <v>60.922525587632123</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.210030013989268</v>
+        <v>76.165468006960538</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.137860625759643</v>
+        <v>93.082667819031371</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.59133596507058</v>
+        <v>104.5289169978806</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20511,22 +20511,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20716,10 +20716,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20735,22 +20735,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.13242068375971852</v>
+        <v>0.132037754376061</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>9.3064916119620714E-2</v>
+        <v>9.2861717612809314E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20885,22 +20885,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20908,13 +20908,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.156279840382496</v>
+        <v>-34.13203202283686</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.760389825104983</v>
+        <v>21.744941949497139</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.834419512479677</v>
+        <v>22.818209174565634</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.438529497202163</v>
+        <v>10.431119101225912</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21063,33 +21063,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21152,23 +21152,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.267278069624581</v>
+        <v>-19.253600074087114</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21200,7 +21200,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.61030370578736</v>
+        <v>106.5346201944441</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,13 +21212,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.97 HKD</v>
+        <v>116.88 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21286,7 +21286,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.62 HKD</v>
+        <v>112.54 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.43 HKD</v>
+        <v>108.36 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21330,7 +21330,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.39 HKD</v>
+        <v>104.32 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.3 HKD</v>
+        <v>86.23 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.46918786417346</v>
+        <v>108.3921847160278</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21382,13 +21382,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21401,22 +21401,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21481,11 +21481,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.37150107609169</v>
+        <v>49.336451850718149</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>60.957574813005664</v>
+        <v>60.922525587632123</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21502,11 +21502,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.771520754730012</v>
+        <v>62.726958747701275</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.210030013989268</v>
+        <v>76.165468006960538</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21542,11 +21542,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.746417723521432</v>
+        <v>77.691224916793161</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.137860625759643</v>
+        <v>93.082667819031371</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21563,11 +21563,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.925426965797612</v>
+        <v>87.863007998607628</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.59133596507058</v>
+        <v>104.5289169978806</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21585,13 +21585,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21642,22 +21642,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21681,12 +21681,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21701,15 +21704,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0449F7-36EF-4559-9A0B-1AE27BC4FF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714AC9D2-8770-4BA6-A4A3-8A181AB1A137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>68.7</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>16819.496736000001</v>
+        <v>16427.776287999997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.24509071763545984</v>
+        <v>0.25590285265179574</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5484,7 +5484,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8278480000000004</v>
+        <v>7.8331679999999997</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.3921847160278</v>
+        <v>108.46585073799056</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>60.922525587632123</v>
+        <v>60.956055866176854</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.165468006960538</v>
+        <v>76.208098806707497</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.082667819031371</v>
+        <v>93.135468705885245</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.5289169978806</v>
+        <v>104.58863088125602</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.132037754376061</v>
+        <v>0.1352780715105675</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>9.2861717612809314E-2</v>
+        <v>9.5076005961251875E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.13203202283686</v>
+        <v>-34.155228999881054</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.744941949497139</v>
+        <v>21.759720352344424</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.818209174565634</v>
+        <v>22.833716996486636</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.431119101225912</v>
+        <v>10.438208348950001</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.253600074087114</v>
+        <v>-19.266685299093286</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.88 HKD</v>
+        <v>116.96 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1104404853276143E-2</v>
+        <v>3.1066453623907291E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.54 HKD</v>
+        <v>112.62 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.4927761572042528E-2</v>
+        <v>4.488881149216762E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.36 HKD</v>
+        <v>108.43 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8977909812878954E-2</v>
+        <v>5.8937927561317022E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.32 HKD</v>
+        <v>104.39 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3256392338797729E-2</v>
+        <v>7.3215343524048487E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.23 HKD</v>
+        <v>86.29 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14810967418814222</v>
+        <v>0.14806273841219381</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.3921847160278</v>
+        <v>108.46585073799056</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.336451850718149</v>
+        <v>49.36998212926288</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>60.922525587632123</v>
+        <v>60.956055866176854</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,11 +6607,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.726958747701275</v>
+        <v>62.769589547448241</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.165468006960538</v>
+        <v>76.208098806707497</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,11 +6654,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.691224916793161</v>
+        <v>77.744025803647034</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.082667819031371</v>
+        <v>93.135468705885245</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,11 +6675,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.863007998607628</v>
+        <v>87.922721881983051</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.5289169978806</v>
+        <v>104.58863088125602</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9992,11 +9992,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.83692655196393</v>
+        <v>115.91565220545853</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.253600074087114</v>
+        <v>-19.266685299093286</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10402,11 +10402,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8356384.2969599999</v>
+        <v>-8362063.5033599995</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.13203202283686</v>
+        <v>-34.155228999881054</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10419,11 +10419,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5323711.5013693832</v>
+        <v>5327329.6279844223</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.744941949497139</v>
+        <v>21.759720352344427</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10436,11 +10436,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5586474.4502616003</v>
+        <v>5590271.1571055995</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.818209174565634</v>
+        <v>22.833716996486636</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10453,11 +10453,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2553801.6546709836</v>
+        <v>2555537.2817300223</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.431119101225914</v>
+        <v>10.43820834895001</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14041,20 +14041,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.2861717612809314E-2</v>
+        <v>9.5076005961251875E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.2861717612809314E-2</v>
+        <v>9.5076005961251875E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.2861717612809314E-2</v>
+        <v>9.5076005961251875E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>9.625909752547307E-2</v>
+        <v>9.8554396423248897E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15204,22 +15204,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0709937256353914</v>
+        <v>9.0771585983590786</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.198369756983695</v>
+        <v>10.205300822470296</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7139100316380027</v>
+        <v>7.7191525965636769</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.815914925139467</v>
+        <v>10.82326568966654</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15261,22 +15261,22 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.132037754376061</v>
+        <v>0.1352780715105675</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.14844788583673499</v>
+        <v>0.15209092134829055</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.11228398881569145</v>
+        <v>0.11503953199051681</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.15743689847364581</v>
+        <v>0.16130053188772789</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15318,15 +15318,15 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8437234173378062E-2</v>
+        <v>1.8876870159628512E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1254797667924704E-2</v>
+        <v>2.1761618476697876E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.815215611692604E-3</v>
+        <v>5.953879471285871E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>10.431119101225912</v>
+        <v>10.438208348950001</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>7.8278480000000004</v>
+        <v>7.8331679999999997</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>26082368.218798432</v>
+        <v>26100094.444310732</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>108.39231339027749</v>
+        <v>108.46597949969048</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18626,23 +18626,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18657,23 +18657,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>97.17084829948557</v>
+        <v>97.236888022402169</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>101.73609720465713</v>
+        <v>101.80523958416279</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>102.64914698569142</v>
+        <v>102.7189098965149</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>103.56219676672573</v>
+        <v>103.63258020886704</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>104.47524654776008</v>
+        <v>104.54625052121921</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18688,23 +18688,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>93.338757555702301</v>
+        <v>93.40219289453313</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>101.8503909146509</v>
+        <v>101.91961097100175</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>103.60249446772416</v>
+        <v>103.67290529718433</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>105.37119031455858</v>
+        <v>105.4428031936632</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>107.15647845515412</v>
+        <v>107.2293046604383</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18719,23 +18719,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>89.94436482228123</v>
+        <v>90.005493247469659</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>101.95695847641669</v>
+        <v>102.02625095873042</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>104.50028556968502</v>
+        <v>104.57130656028558</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>107.09163173067925</v>
+        <v>107.16441386451822</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>109.7314610795046</v>
+        <v>109.80603730696109</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18750,23 +18750,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>86.937676620183254</v>
+        <v>86.996761625362112</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>102.05632217037078</v>
+        <v>102.12568218271981</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>105.34575784286029</v>
+        <v>105.41735343742522</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>108.72785573482199</v>
+        <v>108.80174988714957</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>112.20440476536098</v>
+        <v>112.28066166679183</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18781,23 +18781,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>86.234078245620424</v>
+        <v>86.292685067861555</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>104.32034688190681</v>
+        <v>104.39124558170421</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>108.35698277669677</v>
+        <v>108.43062487454689</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>112.54308643587966</v>
+        <v>112.61957351378904</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>116.88296783918729</v>
+        <v>116.96240440833175</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18812,23 +18812,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>83.875007297391818</v>
+        <v>83.932010836400508</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>104.40673084544025</v>
+        <v>104.47768825392565</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>109.1067863668673</v>
+        <v>109.18093804986775</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>114.02304140583539</v>
+        <v>114.1005342979149</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>119.16380391925644</v>
+        <v>119.24479060127304</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18844,23 +18844,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>83.521224300024272</v>
+        <v>83.577987399317479</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>106.51187012206483</v>
+        <v>106.5842582355092</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>111.8988371442931</v>
+        <v>111.9748863743762</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>117.57906721390636</v>
+        <v>117.65897686948192</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>123.56658660703094</v>
+        <v>123.65056552955848</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18875,23 +18875,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>81.670278886099041</v>
+        <v>81.725784036898332</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>106.58696987790916</v>
+        <v>106.65940903101361</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>112.56379735844796</v>
+        <v>112.64029851201492</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>118.91767776328778</v>
+        <v>118.99849717185327</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>125.67023872571787</v>
+        <v>125.75564734249488</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18907,23 +18907,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>81.568318014963069</v>
+        <v>81.623753870620916</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>108.54472702879573</v>
+        <v>108.61849672230449</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>115.15439061888186</v>
+        <v>115.23265240399731</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>122.23410598742748</v>
+        <v>122.31717932301768</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>129.81519066358598</v>
+        <v>129.90341629268994</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18939,23 +18939,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>80.116051847256941</v>
+        <v>80.170500706742629</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>108.6100166160893</v>
+        <v>108.68383068202382</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>115.744107835771</v>
+        <v>115.82277040735981</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>123.44487134130102</v>
+        <v>123.52876754310969</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>131.75542314023193</v>
+        <v>131.84496739953613</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18971,23 +18971,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>78.631888447664153</v>
+        <v>78.685328632826341</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>113.8074040962333</v>
+        <v>113.88475043583927</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>123.44814884632648</v>
+        <v>123.532047275609</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>134.21484512512131</v>
+        <v>134.30606086871592</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>146.2444860002835</v>
+        <v>146.34387738671836</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19003,23 +19003,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>77.624350007780947</v>
+        <v>77.677105444785013</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>116.75187702870907</v>
+        <v>116.83122450528151</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>128.27857784715931</v>
+        <v>128.36575915601287</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>141.53843359088035</v>
+        <v>141.63462662716609</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>156.81920448540123</v>
+        <v>156.92578271326951</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19035,23 +19035,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>78.084812062928833</v>
+        <v>78.137880441386713</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>120.35921847734926</v>
+        <v>120.44101759280213</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>133.50995376269483</v>
+        <v>133.60069044460505</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>149.01661939037047</v>
+        <v>149.11789478753667</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>167.36908133082022</v>
+        <v>167.48282951712631</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19067,23 +19067,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>78.227805050329991</v>
+        <v>78.280970610375064</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>122.39523700962917</v>
+        <v>122.47841985386569</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>136.73606527742379</v>
+        <v>136.82899450487886</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>154.0133851009316</v>
+        <v>154.11805642422976</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>174.95669326411178</v>
+        <v>175.07559818001778</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>116.88296783918729</v>
+        <v>116.96240440833175</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>112.54308643587966</v>
+        <v>112.61957351378904</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>108.35698277669677</v>
+        <v>108.43062487454689</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>104.32034688190681</v>
+        <v>104.39124558170421</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>86.234078245620424</v>
+        <v>86.292685067861555</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>112.54308643587966</v>
+        <v>112.61957351378904</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>108.35698277669677</v>
+        <v>108.43062487454689</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>104.32034688190681</v>
+        <v>104.39124558170421</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>108.18504453483585</v>
+        <v>108.25856977918465</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>116.88296783918729</v>
+        <v>116.96240440833175</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>86.234078245620424</v>
+        <v>86.292685067861555</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>68.7</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24509071763545984</v>
+        <v>0.25590285265179574</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19811,7 +19811,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>6.5331263987198365E-2</v>
+        <v>6.5290809358296328E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>108.3921847160278</v>
+        <v>108.46585073799056</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>108.39231339027749</v>
+        <v>108.46597949969048</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>9.6234974214736715E-2</v>
+        <v>9.6234974214736771E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20068,11 +20068,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>49.336451850718149</v>
+        <v>49.36998212926288</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>60.922525587632123</v>
+        <v>60.956055866176854</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.43794355887151337</v>
+        <v>0.43801615484101142</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>62.726958747701275</v>
+        <v>62.769589547448241</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>76.165468006960538</v>
+        <v>76.208098806707497</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.29731587008322324</v>
+        <v>0.2974000730350117</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20139,11 +20139,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.691224916793161</v>
+        <v>77.744025803647034</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>93.082667819031371</v>
+        <v>93.135468705885245</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.14124188876813581</v>
+        <v>0.14133832840289329</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20164,11 +20164,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>87.863007998607628</v>
+        <v>87.922721881983051</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>104.5289169978806</v>
+        <v>104.58863088125602</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>3.5641570730107652E-2</v>
+        <v>3.5745995908890493E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>68.7</v>
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20305,14 +20305,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>16819.496736000001</v>
+        <v>16427.776287999997</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.24509071763545984</v>
+        <v>0.25590285265179574</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20320,13 +20320,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>7.8278480000000004</v>
+        <v>7.8331679999999997</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>108.3921847160278</v>
+        <v>108.46585073799056</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>60.922525587632123</v>
+        <v>60.956055866176854</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>76.165468006960538</v>
+        <v>76.208098806707497</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>93.082667819031371</v>
+        <v>93.135468705885245</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>104.5289169978806</v>
+        <v>104.58863088125602</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20511,22 +20511,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20716,10 +20716,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20735,22 +20735,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>0.132037754376061</v>
+        <v>0.1352780715105675</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>9.2861717612809314E-2</v>
+        <v>9.5076005961251875E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20885,22 +20885,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20908,13 +20908,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.13203202283686</v>
+        <v>-34.155228999881054</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.744941949497139</v>
+        <v>21.759720352344424</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.818209174565634</v>
+        <v>22.833716996486636</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>10.431119101225912</v>
+        <v>10.438208348950001</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21063,33 +21063,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21152,23 +21152,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-19.253600074087114</v>
+        <v>-19.266685299093286</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21200,7 +21200,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>106.5346201944441</v>
+        <v>106.60702376940296</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21212,13 +21212,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.88 HKD</v>
+        <v>116.96 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21286,7 +21286,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.54 HKD</v>
+        <v>112.62 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.36 HKD</v>
+        <v>108.43 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21330,7 +21330,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.32 HKD</v>
+        <v>104.39 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.23 HKD</v>
+        <v>86.29 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>108.3921847160278</v>
+        <v>108.46585073799056</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21382,13 +21382,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21401,22 +21401,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21481,11 +21481,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>49.336451850718149</v>
+        <v>49.36998212926288</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>60.922525587632123</v>
+        <v>60.956055866176854</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21502,11 +21502,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>62.726958747701275</v>
+        <v>62.769589547448241</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>76.165468006960538</v>
+        <v>76.208098806707497</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21542,11 +21542,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>77.691224916793161</v>
+        <v>77.744025803647034</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>93.082667819031371</v>
+        <v>93.135468705885245</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21563,11 +21563,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>87.863007998607628</v>
+        <v>87.922721881983051</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>104.5289169978806</v>
+        <v>104.58863088125602</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21585,13 +21585,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21642,22 +21642,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21681,15 +21681,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21704,12 +21701,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/9898.HK_Valuation.xlsx
+++ b/financial_models/opportunities/9898.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714AC9D2-8770-4BA6-A4A3-8A181AB1A137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8EF31B-C232-44DD-A179-2F86DA89CE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Other LT liabilities</t>
-  </si>
-  <si>
-    <t>Biological assets</t>
   </si>
   <si>
     <t>Intangible assets</t>
@@ -3258,10 +3255,13 @@
     <t>Sales/Total Assets g Projection</t>
   </si>
   <si>
+    <t>Biological/Mineral assets</t>
+  </si>
+  <si>
+    <t>微博</t>
+  </si>
+  <si>
     <t>9898.HK</t>
-  </si>
-  <si>
-    <t>微博</t>
   </si>
   <si>
     <t>USD</t>
@@ -5338,7 +5338,7 @@
   <sheetData>
     <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F3" s="429">
         <v>46057</v>
@@ -5359,64 +5359,64 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C4" s="420" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E4" s="430" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F4" s="431" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E5" s="433" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F5" s="432" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>67.099999999999994</v>
+        <v>68.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C9" s="48">
         <v>244825280</v>
@@ -5424,18 +5424,18 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>16427.776287999997</v>
+        <v>16770.53168</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.25590285265179574</v>
+        <v>0.24694203782500182</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5444,7 +5444,7 @@
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
       <c r="B12" s="462" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C12" s="462"/>
       <c r="D12" s="462"/>
@@ -5460,13 +5460,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" s="417" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E15" s="253" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5475,27 +5475,27 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>7.8331679999999997</v>
+        <v>7.8396470000000003</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C17" s="456">
         <v>-0.02</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E17" s="224" t="s">
         <v>557</v>
@@ -5508,10 +5508,10 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>108.46585073799056</v>
+        <v>108.55556542902379</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E18" s="418">
         <v>6</v>
@@ -5519,14 +5519,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Terminal_Growth&lt;2%, "Lower than Inflation rate", IF(Terminal_Growth&lt;5%, "Low growth", IF(Terminal_Growth&lt;8%, "Medium growth", "High growth")))</f>
         <v>Lower than Inflation rate</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E19" s="419">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5539,14 +5539,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C21" s="254" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E21" s="442">
         <v>3</v>
@@ -5554,14 +5554,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>60.956055866176854</v>
+        <v>60.996890955404538</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E22" s="79">
         <v>0.3</v>
@@ -5569,14 +5569,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>76.208098806707497</v>
+        <v>76.260017030685063</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E23" s="443">
         <v>0.2</v>
@@ -5584,14 +5584,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>93.135468705885245</v>
+        <v>93.199772643089418</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E24" s="443">
         <v>0.1174</v>
@@ -5599,14 +5599,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>104.58863088125602</v>
+        <v>104.66135386065253</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E25" s="444">
         <v>7.2499999999999995E-2</v>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="462" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C29" s="462"/>
       <c r="D29" s="462"/>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
       <c r="B30" s="466" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C30" s="466"/>
       <c r="D30" s="466"/>
@@ -5646,7 +5646,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C32" s="105">
         <f>scaling_factor</f>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
       <c r="B33" s="463" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C33" s="463"/>
       <c r="D33" s="463"/>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="285">
         <f>Normalized_FCF!C8</f>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="463" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C36" s="463"/>
       <c r="D36" s="463"/>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="285">
         <f>Normalized_FCF!C15</f>
@@ -5703,7 +5703,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
@@ -5716,7 +5716,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="463" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C40" s="463"/>
       <c r="D40" s="463"/>
@@ -5725,7 +5725,7 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="285">
         <f>Normalized_FCF!C9</f>
@@ -5738,7 +5738,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="463" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C43" s="463"/>
       <c r="D43" s="463"/>
@@ -5747,7 +5747,7 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
@@ -5762,7 +5762,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="286">
         <f>Normalized_FCF!C45</f>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
@@ -5790,12 +5790,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="285">
         <f>Normalized_FCF!C13</f>
@@ -5808,7 +5808,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="463" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C51" s="463"/>
       <c r="D51" s="463"/>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="463" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C54" s="464"/>
       <c r="D54" s="464"/>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="285">
         <f>Normalized_FCF!C17</f>
@@ -5852,7 +5852,7 @@
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
       <c r="B57" s="462" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C57" s="462"/>
       <c r="D57" s="462"/>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
       <c r="B58" s="462" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C58" s="462"/>
       <c r="D58" s="462"/>
@@ -5870,7 +5870,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
@@ -5896,24 +5896,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>0.1352780715105675</v>
+        <v>0.1326228690896413</v>
       </c>
       <c r="F62" s="257"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>9.5076005961251875E-2</v>
+        <v>9.3132846715328468E-2</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
@@ -5922,18 +5922,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C65" s="264" t="s">
+        <v>326</v>
+      </c>
+      <c r="D65" s="264" t="s">
         <v>327</v>
-      </c>
-      <c r="D65" s="264" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6002,7 +6002,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
       <c r="B73" s="462" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C73" s="462"/>
       <c r="D73" s="462"/>
@@ -6012,7 +6012,7 @@
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6021,13 +6021,13 @@
     <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
       <c r="B77" s="462" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C77" s="462"/>
       <c r="D77" s="462"/>
@@ -6037,7 +6037,7 @@
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="285">
         <f>DCF!F4</f>
@@ -6051,11 +6051,11 @@
     <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-34.155228999881054</v>
+        <v>-34.183479604067031</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6065,7 +6065,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="337">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6075,7 +6075,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C81" s="338">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6088,13 +6088,13 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
@@ -6108,7 +6108,7 @@
     <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C85" s="291">
         <f>BS!C66</f>
@@ -6122,11 +6122,11 @@
     <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>21.759720352344424</v>
+        <v>21.777718335812015</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6139,13 +6139,13 @@
     <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="285">
         <f>DCF!F6</f>
@@ -6159,11 +6159,11 @@
     <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.833716996486636</v>
+        <v>22.852603308183291</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6176,11 +6176,11 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>10.438208348950001</v>
+        <v>10.446842039928269</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6189,7 +6189,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6202,7 +6202,7 @@
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
       <c r="B96" s="462" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C96" s="462"/>
       <c r="D96" s="462"/>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="466" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C97" s="466"/>
       <c r="D97" s="466"/>
@@ -6220,7 +6220,7 @@
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="466" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C98" s="466"/>
       <c r="D98" s="466"/>
@@ -6229,12 +6229,12 @@
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6243,7 +6243,7 @@
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C102" s="263">
         <f>E25</f>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C103" s="263">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6261,7 +6261,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C104" s="211">
         <f>Terminal_Growth</f>
@@ -6270,13 +6270,13 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="462" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C107" s="462"/>
       <c r="D107" s="462"/>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="462" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C108" s="462"/>
       <c r="D108" s="462"/>
@@ -6294,16 +6294,16 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-19.266685299093286</v>
+        <v>-19.282621233832952</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6312,11 +6312,11 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>106.60702376940296</v>
+        <v>106.69520098033496</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6325,7 +6325,7 @@
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
       <c r="B114" s="462" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C114" s="462"/>
       <c r="D114" s="462"/>
@@ -6334,24 +6334,24 @@
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C117" s="342" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D117" s="342" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E117" s="342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F117" s="342" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>116.96 HKD</v>
+        <v>117.06 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>3.1066453623907291E-2</v>
+        <v>3.102030394873442E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>112.62 HKD</v>
+        <v>112.71 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>4.488881149216762E-2</v>
+        <v>4.4841447220122989E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>108.43 HKD</v>
+        <v>108.52 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8937927561317022E-2</v>
+        <v>5.8889308175475961E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>104.39 HKD</v>
+        <v>104.48 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.3215343524048487E-2</v>
+        <v>7.3165427206117101E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>86.29 HKD</v>
+        <v>86.36 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6461,12 +6461,12 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.14806273841219381</v>
+        <v>0.14800566362518783</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="463" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C124" s="463"/>
       <c r="D124" s="463"/>
@@ -6475,11 +6475,11 @@
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>108.46585073799056</v>
+        <v>108.55556542902379</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C127" s="465"/>
       <c r="D127" s="465"/>
@@ -6497,7 +6497,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6507,7 +6507,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="467" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C131" s="467"/>
       <c r="D131" s="467"/>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="462" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C132" s="462"/>
       <c r="D132" s="462"/>
@@ -6525,12 +6525,12 @@
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C135" s="202">
         <f>E21</f>
@@ -6539,7 +6539,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
@@ -6552,33 +6552,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
@@ -6586,11 +6586,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>49.36998212926288</v>
+        <v>49.410817218490564</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>60.956055866176854</v>
+        <v>60.996890955404538</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6599,7 +6599,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
@@ -6607,11 +6607,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>62.769589547448241</v>
+        <v>62.8215077714258</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>76.208098806707497</v>
+        <v>76.260017030685063</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6627,26 +6627,26 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
@@ -6654,11 +6654,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>77.744025803647034</v>
+        <v>77.808329740851207</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>93.135468705885245</v>
+        <v>93.199772643089418</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
@@ -6675,11 +6675,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>87.922721881983051</v>
+        <v>87.995444861379553</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>104.58863088125602</v>
+        <v>104.66135386065253</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6698,7 +6698,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="461" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C149" s="462"/>
       <c r="D149" s="462"/>
@@ -6707,12 +6707,12 @@
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C152" s="464"/>
       <c r="D152" s="464"/>
@@ -6721,27 +6721,27 @@
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
       <c r="B158" s="463" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C158" s="463"/>
       <c r="D158" s="463"/>
@@ -6750,12 +6750,12 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
       <c r="B161" s="460" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C161" s="460"/>
       <c r="D161" s="460"/>
@@ -6764,7 +6764,7 @@
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
       <c r="B162" s="460" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C162" s="460"/>
       <c r="D162" s="460"/>
@@ -6773,22 +6773,22 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -6907,7 +6907,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="103">
         <v>1000</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="287">
         <v>369521</v>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="287">
         <f>101294+C7</f>
@@ -7000,7 +7000,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="288">
         <v>480791</v>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="287">
         <v>308747</v>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="287"/>
       <c r="D9" s="287"/>
@@ -7060,7 +7060,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="287"/>
       <c r="D10" s="287"/>
@@ -7076,7 +7076,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="287"/>
       <c r="D11" s="287"/>
@@ -7092,7 +7092,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="287">
         <v>105397</v>
@@ -7114,7 +7114,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="287">
         <v>123336</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="287">
         <v>110550</v>
@@ -7158,7 +7158,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="289">
         <v>310105</v>
@@ -7180,7 +7180,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="287">
         <f>2556+7648</f>
@@ -7204,13 +7204,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="287"/>
       <c r="D19" s="287"/>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="287"/>
       <c r="D20" s="287"/>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="287"/>
       <c r="D21" s="287"/>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C22" s="287">
         <v>639898</v>
@@ -7280,7 +7280,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C23" s="287">
         <v>-246900</v>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C24" s="287">
         <v>-1029439</v>
@@ -7350,15 +7350,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="270">
         <f>BS!C4</f>
@@ -7380,7 +7380,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="270">
         <f>BS!C6</f>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="271">
         <f>BS!C33+BS!C42</f>
@@ -7422,7 +7422,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="271">
         <f>BS!G27</f>
@@ -7443,7 +7443,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C32" s="270">
         <f>BS!G28</f>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
@@ -7480,7 +7480,7 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -7534,7 +7534,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="270">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7583,7 +7583,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="267">
         <f>IF(C36="","",C36+C37)</f>
@@ -7632,7 +7632,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="270">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="282">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7730,7 +7730,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="282">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7779,7 +7779,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="270">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C43" s="271">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" s="290">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7926,7 +7926,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" s="285">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7975,7 +7975,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="270">
         <f>IF(C$4="","",-C14)</f>
@@ -8024,7 +8024,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="271">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -8073,7 +8073,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="270">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -8122,12 +8122,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="270">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="270">
         <f>IF(C$4="","",C13)</f>
@@ -8225,12 +8225,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" s="285">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="285">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -8328,7 +8328,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C57" s="285">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -8377,7 +8377,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="285">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -8426,13 +8426,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="270">
         <f>IF(C$4="","",-C19)</f>
@@ -8481,7 +8481,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62" s="270">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -8530,7 +8530,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="270">
         <f>IF(C$4="","",-C21)</f>
@@ -8579,7 +8579,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C64" s="270">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
@@ -8677,7 +8677,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8732,7 +8732,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="89">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8831,7 +8831,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C71" s="98">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8930,7 +8930,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C75" s="9"/>
     </row>
@@ -9001,7 +9001,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="260">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -9035,7 +9035,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" s="260">
         <f t="shared" si="40"/>
@@ -9069,7 +9069,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C79" s="259">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -9118,7 +9118,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" s="259">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -9182,7 +9182,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9210,7 +9210,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="96">
         <v>45838</v>
@@ -9226,7 +9226,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -9237,27 +9237,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="164" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="165" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="164" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="165" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>155</v>
-      </c>
       <c r="G3" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H3" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="18">
         <f>376540+452953</f>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="18">
         <v>1156292</v>
@@ -9279,7 +9279,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="18">
         <v>0</v>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="18">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="18">
         <v>0</v>
@@ -9321,7 +9321,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="18">
         <v>952876</v>
@@ -9342,7 +9342,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G8" s="18">
         <v>0</v>
@@ -9363,7 +9363,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="18">
         <v>339402</v>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
@@ -9393,7 +9393,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9416,7 +9416,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="78">
         <f>SUM(C4:C11)</f>
@@ -9427,7 +9427,7 @@
         <v>531636</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="78">
         <f>SUM(G4:G10)</f>
@@ -9445,27 +9445,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C15" s="18">
         <v>0</v>
@@ -9474,7 +9474,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="18">
         <v>0</v>
@@ -9485,7 +9485,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -9494,7 +9494,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G16" s="18">
         <v>0</v>
@@ -9505,7 +9505,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -9514,7 +9514,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="18">
         <v>0</v>
@@ -9525,7 +9525,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G18" s="18">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="18">
         <v>280622</v>
@@ -9554,7 +9554,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G19" s="18">
         <v>1419411</v>
@@ -9565,7 +9565,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>16</v>
+        <v>554</v>
       </c>
       <c r="C20" s="18">
         <v>0</v>
@@ -9574,7 +9574,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G20" s="18">
         <v>0</v>
@@ -9585,7 +9585,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="18">
         <v>0</v>
@@ -9594,7 +9594,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G21" s="18">
         <v>0</v>
@@ -9605,7 +9605,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="18">
         <v>0</v>
@@ -9617,7 +9617,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="18">
         <f>268159+1292890</f>
@@ -9630,7 +9630,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="78">
         <f>SUM(C15:C23)</f>
@@ -9641,7 +9641,7 @@
         <v>28062.2</v>
       </c>
       <c r="F24" s="77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="78">
         <f>SUM(G15:G21)</f>
@@ -9654,19 +9654,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G26" s="167" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H26" s="168" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
@@ -9677,7 +9677,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="169" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="82">
         <f>G32-G30</f>
@@ -9696,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G28" s="287">
         <v>52770</v>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="172" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9730,7 +9730,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="169" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="82">
         <f>C33+C42</f>
@@ -9740,14 +9740,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C31" s="78">
         <f>SUM(C27:C30)</f>
         <v>0</v>
       </c>
       <c r="F31" s="172" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="173">
         <f>C31+C40</f>
@@ -9764,7 +9764,7 @@
         <v>896878</v>
       </c>
       <c r="F32" s="174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G32" s="175">
         <f>G35+G40</f>
@@ -9790,24 +9790,24 @@
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" s="179" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H34" s="180" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F35" s="181" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="175">
         <f>C12+C24</f>
@@ -9827,7 +9827,7 @@
         <v>1067520</v>
       </c>
       <c r="F36" s="172" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G36" s="173">
         <f>C4+C15</f>
@@ -9843,7 +9843,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="172" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G37" s="173">
         <f>C6</f>
@@ -9859,7 +9859,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="172" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G38" s="173">
         <f>C7+C17</f>
@@ -9875,7 +9875,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" s="173">
         <f>C7+C17+C19+C20</f>
@@ -9888,14 +9888,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="78">
         <f>SUM(C36:C39)</f>
         <v>1067520</v>
       </c>
       <c r="F40" s="181" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="175">
         <f>G12+G24</f>
@@ -9915,7 +9915,7 @@
         <v>899039</v>
       </c>
       <c r="F41" s="172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G41" s="173">
         <f>C70</f>
@@ -9928,14 +9928,14 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C42" s="81">
         <f>2863437-896878</f>
         <v>1966559</v>
       </c>
       <c r="F42" s="183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="184">
         <f>C82</f>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
@@ -9959,21 +9959,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C45" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D45" s="164" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F45" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C46" s="73">
         <f>G29</f>
@@ -9992,11 +9992,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>115.91565220545853</v>
+        <v>116.01152880489303</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-19.266685299093286</v>
+        <v>-19.282621233832952</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10005,20 +10005,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C49" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" s="163"/>
       <c r="D51" s="89">
@@ -10046,19 +10046,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F53" s="223"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
@@ -10072,7 +10072,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="89">
         <f>Normalized_FCF!C9/G40</f>
@@ -10089,19 +10089,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F57" s="223"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" s="95"/>
       <c r="D58" s="22">
@@ -10112,7 +10112,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="95"/>
       <c r="D59" s="89">
@@ -10126,19 +10126,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C61" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F61" s="223"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C62" s="89">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -10149,12 +10149,12 @@
         <v>1.456552665267802E-2</v>
       </c>
       <c r="F62" s="223" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -10165,21 +10165,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D65" s="165" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C66" s="19">
         <f>G4+G5+G15</f>
@@ -10190,12 +10190,12 @@
         <v>680098.98778941319</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" s="19">
         <f>G6+G16</f>
@@ -10205,7 +10205,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C68" s="19">
         <f>G18</f>
@@ -10215,7 +10215,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C69" s="19">
         <f>G8+G20</f>
@@ -10225,7 +10225,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C70" s="78">
         <f>SUM(C66:C69)</f>
@@ -10238,19 +10238,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C72" s="209" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D72" s="164" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F72" s="223"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
@@ -10261,12 +10261,12 @@
         <v>-238096.50610529343</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
@@ -10277,12 +10277,12 @@
         <v>4.8564005365482048</v>
       </c>
       <c r="F74" s="223" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="261"/>
       <c r="D75" s="262">
@@ -10290,12 +10290,12 @@
         <v>476193.01221058686</v>
       </c>
       <c r="F75" s="223" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C76" s="230"/>
       <c r="D76" s="248">
@@ -10303,7 +10303,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="223" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10311,19 +10311,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D78" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F78" s="223"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C79" s="19">
         <f>G7+G17</f>
@@ -10337,7 +10337,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C80" s="19">
         <f>G19</f>
@@ -10351,7 +10351,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="19">
         <f>G9+G21</f>
@@ -10365,7 +10365,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="78">
         <f>SUM(C79:C81)</f>
@@ -10379,7 +10379,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
@@ -10390,23 +10390,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="215" t="s">
         <v>242</v>
-      </c>
-      <c r="D85" s="215" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-8362063.5033599995</v>
+        <v>-8368979.9654400004</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-34.155228999881054</v>
+        <v>-34.183479604067031</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10415,15 +10415,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>5327329.6279844223</v>
+        <v>5331735.9893263103</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>21.759720352344427</v>
+        <v>21.777718335812015</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10432,15 +10432,15 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5590271.1571055995</v>
+        <v>5594895.0036549</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>22.833716996486636</v>
+        <v>22.852603308183287</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10449,15 +10449,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>2555537.2817300223</v>
+        <v>2557651.0275412099</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>10.43820834895001</v>
+        <v>10.446842039928271</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10502,7 +10502,7 @@
         <v>USD</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="50"/>
       <c r="E1" s="50"/>
@@ -10555,12 +10555,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="53"/>
       <c r="E2" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="53"/>
       <c r="G2" s="35"/>
@@ -10578,7 +10578,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10588,7 +10588,7 @@
       <c r="E3" s="237"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -10655,7 +10655,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="266">
         <f>C26</f>
@@ -10710,7 +10710,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="267">
         <f>C4+C5</f>
@@ -10765,7 +10765,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="266">
         <f>C35</f>
@@ -10820,7 +10820,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="268">
         <f>C6+C7</f>
@@ -10877,7 +10877,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C9" s="300">
         <f>C61</f>
@@ -10934,7 +10934,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="266">
         <f>C48</f>
@@ -10989,7 +10989,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
@@ -11044,7 +11044,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
@@ -11099,7 +11099,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" s="266">
         <f>-C4*C79</f>
@@ -11156,7 +11156,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
@@ -11213,7 +11213,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="266">
         <f>BS!$G$39*BS!D58</f>
@@ -11268,7 +11268,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
@@ -11323,7 +11323,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="266">
         <f>-C4*C83</f>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="236" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="272"/>
@@ -11349,14 +11349,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="266">
         <v>0</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="273"/>
@@ -11374,7 +11374,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
@@ -11450,12 +11450,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="53"/>
       <c r="E21" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="35"/>
@@ -11473,7 +11473,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="26"/>
@@ -11494,7 +11494,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="274">
         <f>-C4*C29</f>
@@ -11551,7 +11551,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="266">
         <f>-C4*C30</f>
@@ -11608,7 +11608,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="266">
         <f>-C4*C31</f>
@@ -11665,7 +11665,7 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="267">
         <f>SUM(C23:C25)</f>
@@ -11726,14 +11726,14 @@
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28" s="237"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="60">
         <f>AVERAGE(G29:H29)</f>
@@ -11906,7 +11906,7 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
@@ -11965,14 +11965,14 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" s="237"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C35" s="276">
         <f>G35</f>
@@ -12033,14 +12033,14 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E37" s="237"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12099,21 +12099,21 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E40" s="237"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" s="457">
         <v>0.25</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="234" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -12167,12 +12167,12 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="53"/>
       <c r="E43" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="35"/>
@@ -12190,14 +12190,14 @@
     <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="237"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="266">
         <f>-BS!G31*Normalized_FCF!C52</f>
@@ -12252,7 +12252,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
@@ -12307,7 +12307,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C47" s="278">
         <f>BS!$C$66*C51</f>
@@ -12364,7 +12364,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
@@ -12423,17 +12423,17 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E50" s="237"/>
       <c r="G50" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C51" s="84">
         <v>6.0000000000000001E-3</v>
@@ -12457,7 +12457,7 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="79">
         <v>0.06</v>
@@ -12481,7 +12481,7 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
@@ -12540,17 +12540,17 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" s="237"/>
       <c r="G55" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="266">
         <f>BS!$C67*C64</f>
@@ -12605,7 +12605,7 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" s="266">
         <f>BS!$C68*C65</f>
@@ -12660,7 +12660,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="266">
         <f>BS!$C69*C66</f>
@@ -12715,7 +12715,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C59" s="267">
         <f>SUM(C56:C58)</f>
@@ -12770,13 +12770,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="279">
         <v>0</v>
       </c>
       <c r="E60" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G60" s="266">
         <f>Data!C58</f>
@@ -12826,7 +12826,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C61" s="267">
         <f>C59+C60</f>
@@ -12885,17 +12885,17 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="237"/>
       <c r="G63" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="158">
         <f>G64</f>
@@ -12920,7 +12920,7 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" s="158">
         <f>G65</f>
@@ -12945,7 +12945,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C66" s="158">
         <f>G66</f>
@@ -12970,7 +12970,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C67" s="68">
         <f>C59/BS!C70</f>
@@ -13000,12 +13000,12 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="51"/>
       <c r="D69" s="53"/>
       <c r="E69" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F69" s="53"/>
       <c r="G69" s="35"/>
@@ -13023,7 +13023,7 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C70" s="59"/>
       <c r="D70" s="26"/>
@@ -13044,7 +13044,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
@@ -13101,7 +13101,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
@@ -13158,7 +13158,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="74">
         <f t="shared" si="22"/>
@@ -13215,7 +13215,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
@@ -13272,7 +13272,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C75" s="74">
         <f t="shared" si="22"/>
@@ -13329,7 +13329,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
@@ -13386,7 +13386,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
@@ -13443,7 +13443,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
@@ -13558,7 +13558,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
@@ -13615,7 +13615,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C81" s="74">
         <f>ABS(C15/C$4)</f>
@@ -13672,7 +13672,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -13731,7 +13731,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C83" s="233">
         <v>0</v>
@@ -13757,7 +13757,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" s="74">
         <v>0</v>
@@ -13781,7 +13781,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
@@ -13842,7 +13842,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E87" s="237"/>
     </row>
@@ -13961,7 +13961,7 @@
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
@@ -14016,7 +14016,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C91" s="292">
         <v>0</v>
@@ -14037,24 +14037,24 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>9.5076005961251875E-2</v>
+        <v>9.3132846715328468E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>9.5076005961251875E-2</v>
+        <v>9.3132846715328468E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>9.5076005961251875E-2</v>
+        <v>9.3132846715328468E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>9.8554396423248897E-2</v>
+        <v>9.6540145985401463E-2</v>
       </c>
       <c r="J92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14096,7 +14096,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="26"/>
@@ -14117,7 +14117,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C95" s="74">
         <f>C4/G4-1</f>
@@ -14174,7 +14174,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
@@ -14234,12 +14234,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" s="51"/>
       <c r="D98" s="53"/>
       <c r="E98" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F98" s="53"/>
       <c r="G98" s="35"/>
@@ -14257,11 +14257,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" s="237"/>
       <c r="G99" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
@@ -14324,7 +14324,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C101" s="281">
         <f>BS!C4</f>
@@ -14381,7 +14381,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C102" s="281">
         <f>BS!C6+BS!C7</f>
@@ -14438,7 +14438,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C103" s="280">
         <f>BS!G30</f>
@@ -14495,7 +14495,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" s="280">
         <f>BS!G27</f>
@@ -14556,14 +14556,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C106" s="25"/>
       <c r="D106" s="25"/>
       <c r="E106" s="238"/>
       <c r="F106" s="25"/>
       <c r="G106" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -14579,7 +14579,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C107" s="91">
         <f>C101/C$4</f>
@@ -14636,7 +14636,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C108" s="91">
         <f>C102/C$4</f>
@@ -14693,7 +14693,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C109" s="91">
         <f>BS!$G$38/C$4</f>
@@ -14724,18 +14724,18 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E111" s="237"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="451" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
@@ -14785,7 +14785,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C113" s="151"/>
       <c r="E113" s="459">
@@ -14844,10 +14844,10 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C115" s="451" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
@@ -14903,7 +14903,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C116" s="22">
         <f>C77</f>
@@ -14960,7 +14960,7 @@
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C117" s="452">
         <f>G117</f>
@@ -15017,7 +15017,7 @@
     </row>
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C118" s="15">
         <f>C100/C104</f>
@@ -15077,7 +15077,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
@@ -15155,12 +15155,12 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C121" s="51"/>
       <c r="D121" s="53"/>
       <c r="E121" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F121" s="53"/>
       <c r="G121" s="35"/>
@@ -15178,7 +15178,7 @@
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C122" s="161"/>
       <c r="D122" s="26"/>
@@ -15204,22 +15204,22 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>9.0771585983590786</v>
+        <v>9.0846665326404281</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>10.205300822470296</v>
+        <v>10.213741870080762</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>7.7191525965636769</v>
+        <v>7.7255372917053027</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>10.82326568966654</v>
+        <v>10.832217870751302</v>
       </c>
       <c r="J123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15257,26 +15257,26 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1352780715105675</v>
+        <v>0.1326228690896413</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.15209092134829055</v>
+        <v>0.14910572073110601</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.11503953199051681</v>
+        <v>0.1127815663022672</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.16130053188772789</v>
+        <v>0.1581345674562234</v>
       </c>
       <c r="J124" s="74" t="str">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
@@ -15313,20 +15313,20 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8876870159628512E-2</v>
+        <v>1.8491065514030264E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1761618476697876E-2</v>
+        <v>2.1316855471334707E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.953879471285871E-3</v>
+        <v>5.8321943434055754E-3</v>
       </c>
       <c r="J125" s="22" t="str">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16075,7 +16075,7 @@
   <sheetData>
     <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -16090,22 +16090,22 @@
     </row>
     <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
@@ -16116,7 +16116,7 @@
         <v>USD</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F4" s="275">
         <f>-BS!G31</f>
@@ -16127,7 +16127,7 @@
         <v>USD</v>
       </c>
       <c r="H4" s="308" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I4" s="305">
         <f>Normalized_FCF!C4</f>
@@ -16137,14 +16137,14 @@
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="188">
         <f>Equity_Cost</f>
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
@@ -16155,7 +16155,7 @@
         <v>USD</v>
       </c>
       <c r="H5" s="308" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I5" s="305">
         <f>Normalized_FCF!C7</f>
@@ -16165,7 +16165,7 @@
     </row>
     <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -16176,7 +16176,7 @@
         <v>USD</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F6" s="284">
         <f>BS!H42</f>
@@ -16187,7 +16187,7 @@